--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BBF0FE-9036-46EA-A8C4-B0B29C11893C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48DA200-CA56-4299-8059-9F93E57F79B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="2100" windowWidth="26040" windowHeight="14730" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="1320" windowWidth="24105" windowHeight="13785" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="112">
   <si>
     <t>Source:</t>
   </si>
@@ -383,6 +383,9 @@
   <si>
     <t>passenger LDVs</t>
   </si>
+  <si>
+    <t>indicates value hardcoded during calibration</t>
+  </si>
 </sst>
 </file>
 
@@ -471,7 +474,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -499,6 +502,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,7 +650,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -691,6 +700,7 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -861,97 +871,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0" formatCode="0.0000">
-                  <c:v>0.14562875828586999</c:v>
+                  <c:v>7.5738458244009904E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14562875828586999</c:v>
+                  <c:v>7.5738458244009904E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.25157645096963099</c:v>
+                  <c:v>0.16254791306372199</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.24934859903793999</c:v>
+                  <c:v>0.13456250619976501</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.27293517554942398</c:v>
+                  <c:v>0.17887325579206301</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.45254097379320501</c:v>
+                  <c:v>0.28035657357026</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.55003277903456405</c:v>
+                  <c:v>0.32028525885620801</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.64752458427592308</c:v>
+                  <c:v>0.36021394414215602</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.74501638951728211</c:v>
+                  <c:v>0.40014262942810402</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.84250819475864114</c:v>
+                  <c:v>0.44007131471405203</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.94</c:v>
+                  <c:v>0.48</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.002</c:v>
+                  <c:v>0.504</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0640000000000001</c:v>
+                  <c:v>0.52800000000000002</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.1260000000000001</c:v>
+                  <c:v>0.55200000000000005</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.1880000000000002</c:v>
+                  <c:v>0.57600000000000007</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.25</c:v>
+                  <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.34</c:v>
+                  <c:v>0.64600000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.4300000000000002</c:v>
+                  <c:v>0.69200000000000006</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.5200000000000002</c:v>
+                  <c:v>0.7380000000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.6100000000000003</c:v>
+                  <c:v>0.78400000000000014</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.7</c:v>
+                  <c:v>0.83</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.91</c:v>
+                  <c:v>0.94399999999999995</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>1.0579999999999998</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.1719999999999997</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.2859999999999996</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.64</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.88</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>2.12</c:v>
                 </c:pt>
-                <c:pt idx="23">
-                  <c:v>2.33</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2.54</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2.75</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>3.2800000000000002</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>3.8100000000000005</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>4.3400000000000007</c:v>
-                </c:pt>
                 <c:pt idx="29">
-                  <c:v>4.870000000000001</c:v>
+                  <c:v>2.3600000000000003</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5.4</c:v>
+                  <c:v>2.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1087,97 +1097,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0" formatCode="0.0000">
-                  <c:v>3.3752550513252298E-3</c:v>
+                  <c:v>3.3111542696076198E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.3752550513252298E-3</c:v>
+                  <c:v>3.3111542696076198E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.2073136116094201E-3</c:v>
+                  <c:v>3.18875302069616E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.2731580821590001E-3</c:v>
+                  <c:v>3.2416232692108801E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.2886569653648402E-3</c:v>
+                  <c:v>3.2401040027916599E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>3.2803950897637999E-3</c:v>
+                  <c:v>3.2380317148955899E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1539,97 +1549,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0" formatCode="0.0000">
-                  <c:v>0.59151755489837199</c:v>
+                  <c:v>0.58713757439567404</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.59151755489837199</c:v>
+                  <c:v>0.58713757439567404</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.59031765788952895</c:v>
+                  <c:v>0.58625646954423505</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.58983194859159405</c:v>
+                  <c:v>0.58587879933822895</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.589580073239939</c:v>
+                  <c:v>0.58568402014887</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.58834597467789096</c:v>
+                  <c:v>0.58477756179805596</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1765,97 +1775,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0" formatCode="0.0000">
-                  <c:v>0.356961080621581</c:v>
+                  <c:v>3.0097006982601999E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.356961080621581</c:v>
+                  <c:v>3.0097006982601999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.46266979168123801</c:v>
+                  <c:v>2.1911439020317398E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.68107773418921602</c:v>
+                  <c:v>2.0681798718551799E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.1492319563763</c:v>
+                  <c:v>1.91330462605762E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.4827841473737</c:v>
+                  <c:v>2.67214247564647E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.5862273178989601</c:v>
+                  <c:v>3.097713980517176E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.6896704884242202</c:v>
+                  <c:v>3.5232854853878823E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.7931136589494803</c:v>
+                  <c:v>3.9488569902585882E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.8965568294747404</c:v>
+                  <c:v>4.3744284951292942E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2</c:v>
+                  <c:v>4.8000000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2</c:v>
+                  <c:v>5.2400000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2</c:v>
+                  <c:v>5.6800000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2</c:v>
+                  <c:v>6.1200000000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2</c:v>
+                  <c:v>6.5600000000000006E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2</c:v>
+                  <c:v>7.0000000000000007E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2</c:v>
+                  <c:v>7.46E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2</c:v>
+                  <c:v>7.9199999999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2</c:v>
+                  <c:v>8.3799999999999986E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2</c:v>
+                  <c:v>8.8399999999999979E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2</c:v>
+                  <c:v>9.2999999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2</c:v>
+                  <c:v>0.1024</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2</c:v>
+                  <c:v>0.11180000000000001</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2</c:v>
+                  <c:v>0.12120000000000002</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2</c:v>
+                  <c:v>0.13060000000000002</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2</c:v>
+                  <c:v>0.14000000000000001</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2</c:v>
+                  <c:v>0.16400000000000001</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2</c:v>
+                  <c:v>0.188</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2</c:v>
+                  <c:v>0.21199999999999999</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2</c:v>
+                  <c:v>0.23599999999999999</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2</c:v>
+                  <c:v>0.26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1991,97 +2001,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0" formatCode="0.0000">
-                  <c:v>0.171593660015216</c:v>
+                  <c:v>0.169435072322971</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.171593660015216</c:v>
+                  <c:v>0.169435072322971</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.157380451105636</c:v>
+                  <c:v>0.15875306561484401</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.157105919646333</c:v>
+                  <c:v>0.158538746497771</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.15691361174878399</c:v>
+                  <c:v>0.15840837270788899</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.15633667860209499</c:v>
+                  <c:v>0.15795852186818499</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2219,97 +2229,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0" formatCode="0.0000">
-                  <c:v>1.8305978574742698E-2</c:v>
+                  <c:v>1.5971754362172401E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.8305978574742698E-2</c:v>
+                  <c:v>1.5971754362172401E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.9637350115763199E-2</c:v>
+                  <c:v>1.7435929211407498E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.5168289481052303E-3</c:v>
+                  <c:v>6.9483671683743999E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.5865782984086399E-3</c:v>
+                  <c:v>4.5730323634844599E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.72086386734626E-2</c:v>
+                  <c:v>9.4692125755478501E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3424,9 +3434,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B89"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="56.1796875" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3795,12 +3805,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29">
+    <row r="1" spans="1:32" ht="45">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -4844,12 +4854,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29">
+    <row r="1" spans="1:32" ht="45">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -5893,12 +5903,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29">
+    <row r="1" spans="1:32" ht="45">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -6942,12 +6952,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29">
+    <row r="1" spans="1:32" ht="45">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -7991,12 +8001,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29">
+    <row r="1" spans="1:32" ht="45">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -9040,12 +9050,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29">
+    <row r="1" spans="1:32" ht="45">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -10089,12 +10099,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29">
+    <row r="1" spans="1:32" ht="45">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -11138,12 +11148,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29">
+    <row r="1" spans="1:32" ht="45">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -12184,18 +12194,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.90625" customWidth="1"/>
-    <col min="2" max="2" width="24.453125" customWidth="1"/>
-    <col min="3" max="3" width="20.90625" customWidth="1"/>
-    <col min="4" max="4" width="18.1796875" customWidth="1"/>
-    <col min="5" max="5" width="17.08984375" customWidth="1"/>
-    <col min="6" max="8" width="23.1796875" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="8" width="23.140625" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="29">
+    <row r="1" spans="1:10" ht="30">
       <c r="A1" s="23" t="s">
         <v>81</v>
       </c>
@@ -12398,19 +12408,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.90625" customWidth="1"/>
-    <col min="2" max="2" width="24.453125" customWidth="1"/>
-    <col min="3" max="3" width="20.90625" customWidth="1"/>
-    <col min="4" max="4" width="18.1796875" customWidth="1"/>
-    <col min="5" max="5" width="17.08984375" customWidth="1"/>
-    <col min="6" max="8" width="23.1796875" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="8" width="23.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="29">
+    <row r="1" spans="1:10" ht="30">
       <c r="A1" s="23" t="s">
         <v>81</v>
       </c>
@@ -12604,11 +12614,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD9F80A-1DD4-4EFC-BD0A-42EC00E11F1F}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -12648,13 +12658,13 @@
         <v>61189</v>
       </c>
       <c r="E2">
-        <v>5.54794452055479E-2</v>
+        <v>3.5339646603533899E-2</v>
       </c>
       <c r="F2">
-        <v>0.14562875828586999</v>
+        <v>7.5738458244009904E-2</v>
       </c>
       <c r="G2">
-        <v>-1.92669464702355</v>
+        <v>-2.5804692126173099</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -12671,13 +12681,13 @@
         <v>53835</v>
       </c>
       <c r="E3">
-        <v>1.4599854001459899E-3</v>
+        <v>1.6999830001699901E-3</v>
       </c>
       <c r="F3">
-        <v>3.3752550513252298E-3</v>
+        <v>3.3111542696076198E-3</v>
       </c>
       <c r="G3">
-        <v>-5.6912843867499303</v>
+        <v>-5.7104584284466897</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -12694,7 +12704,7 @@
         <v>49476</v>
       </c>
       <c r="E4">
-        <v>0.46637533624663702</v>
+        <v>0.54334456655433405</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -12717,13 +12727,13 @@
         <v>51215</v>
       </c>
       <c r="E5">
-        <v>0.26770732292677002</v>
+        <v>0.31188688113118801</v>
       </c>
       <c r="F5">
-        <v>0.59151755489837199</v>
+        <v>0.58713757439567404</v>
       </c>
       <c r="G5">
-        <v>-0.52506391739315295</v>
+        <v>-0.53249611796727703</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -12740,13 +12750,13 @@
         <v>64682</v>
       </c>
       <c r="E6">
-        <v>0.128028719712802</v>
+        <v>1.34198658013419E-2</v>
       </c>
       <c r="F6">
-        <v>0.356961080621581</v>
+        <v>3.0097006982601999E-2</v>
       </c>
       <c r="G6">
-        <v>-1.0301285210120901</v>
+        <v>-3.5033295479653201</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -12763,13 +12773,13 @@
         <v>52451</v>
       </c>
       <c r="E7">
-        <v>7.6019239807601904E-2</v>
+        <v>8.8569114308856903E-2</v>
       </c>
       <c r="F7">
-        <v>0.171593660015216</v>
+        <v>0.169435072322971</v>
       </c>
       <c r="G7">
-        <v>-1.76262603890908</v>
+        <v>-1.7752854796873601</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -12786,13 +12796,13 @@
         <v>81273</v>
       </c>
       <c r="E8">
-        <v>4.9299507004929898E-3</v>
+        <v>5.7399426005739903E-3</v>
       </c>
       <c r="F8">
-        <v>1.8305978574742698E-2</v>
+        <v>1.5971754362172401E-2</v>
       </c>
       <c r="G8">
-        <v>-4.0005275744155799</v>
+        <v>-4.1369334691773796</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -12809,13 +12819,13 @@
         <v>60642</v>
       </c>
       <c r="E9">
-        <v>9.1410914109141095E-2</v>
+        <v>7.4800000000000005E-2</v>
       </c>
       <c r="F9">
-        <v>0.25157645096963099</v>
+        <v>0.16254791306372199</v>
       </c>
       <c r="G9">
-        <v>-1.38000835563636</v>
+        <v>-1.8167824710490399</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -12832,13 +12842,13 @@
         <v>52557</v>
       </c>
       <c r="E10">
-        <v>1.3400134001340001E-3</v>
+        <v>1.6299999999999999E-3</v>
       </c>
       <c r="F10">
-        <v>3.2073136116094201E-3</v>
+        <v>3.18875302069616E-3</v>
       </c>
       <c r="G10">
-        <v>-5.7423215733392698</v>
+        <v>-5.7481253412108</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -12855,7 +12865,7 @@
         <v>50918</v>
       </c>
       <c r="E11">
-        <v>0.42979429794297902</v>
+        <v>0.52217999999999998</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -12878,13 +12888,13 @@
         <v>52541</v>
       </c>
       <c r="E12">
-        <v>0.24670246702467</v>
+        <v>0.29974000000000001</v>
       </c>
       <c r="F12">
-        <v>0.59031765788952895</v>
+        <v>0.58625646954423505</v>
       </c>
       <c r="G12">
-        <v>-0.52709448376678203</v>
+        <v>-0.53399792381262701</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -12901,13 +12911,13 @@
         <v>65467</v>
       </c>
       <c r="E13">
-        <v>0.15467154671546701</v>
+        <v>9.4699999999999993E-3</v>
       </c>
       <c r="F13">
-        <v>0.46266979168123801</v>
+        <v>2.1911439020317398E-2</v>
       </c>
       <c r="G13">
-        <v>-0.77074167225204404</v>
+        <v>-3.8207464488314899</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -12924,13 +12934,13 @@
         <v>48883</v>
       </c>
       <c r="E14">
-        <v>7.0060700607006005E-2</v>
+        <v>8.5120000000000001E-2</v>
       </c>
       <c r="F14">
-        <v>0.157380451105636</v>
+        <v>0.15875306561484401</v>
       </c>
       <c r="G14">
-        <v>-1.8490891495327499</v>
+        <v>-1.8404053304361401</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -12947,13 +12957,13 @@
         <v>70483</v>
       </c>
       <c r="E15">
-        <v>6.0200602006020001E-3</v>
+        <v>7.0600000000000003E-3</v>
       </c>
       <c r="F15">
-        <v>1.9637350115763199E-2</v>
+        <v>1.7435929211407498E-2</v>
       </c>
       <c r="G15">
-        <v>-3.9303219079813601</v>
+        <v>-4.0492223045243199</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -12970,13 +12980,13 @@
         <v>57692</v>
       </c>
       <c r="E16">
-        <v>8.9109999999999995E-2</v>
+        <v>6.5549344506554905E-2</v>
       </c>
       <c r="F16">
-        <v>0.24934859903793999</v>
+        <v>0.13456250619976501</v>
       </c>
       <c r="G16">
-        <v>-1.38890336546201</v>
+        <v>-2.0057264577840499</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -12993,13 +13003,13 @@
         <v>53849</v>
       </c>
       <c r="E17">
-        <v>1.25E-3</v>
+        <v>1.65998340016599E-3</v>
       </c>
       <c r="F17">
-        <v>3.2731580821590001E-3</v>
+        <v>3.2416232692108801E-3</v>
       </c>
       <c r="G17">
-        <v>-5.7219999857724302</v>
+        <v>-5.7316810656252999</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -13016,7 +13026,7 @@
         <v>51190</v>
       </c>
       <c r="E18">
-        <v>0.39983999999999997</v>
+        <v>0.53009469905300899</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -13039,13 +13049,13 @@
         <v>52765</v>
       </c>
       <c r="E19">
-        <v>0.22950999999999999</v>
+        <v>0.30427695723042703</v>
       </c>
       <c r="F19">
-        <v>0.58983194859159405</v>
+        <v>0.58587879933822895</v>
       </c>
       <c r="G19">
-        <v>-0.52791761555056704</v>
+        <v>-0.53464233786465998</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -13062,13 +13072,13 @@
         <v>65520</v>
       </c>
       <c r="E20">
-        <v>0.21262</v>
+        <v>9.0999090009099906E-3</v>
       </c>
       <c r="F20">
-        <v>0.68107773418921602</v>
+        <v>2.0681798718551799E-2</v>
       </c>
       <c r="G20">
-        <v>-0.384078832226183</v>
+        <v>-3.8785012544709501</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -13085,13 +13095,13 @@
         <v>49052</v>
       </c>
       <c r="E21">
-        <v>6.5180000000000002E-2</v>
+        <v>8.6409135908640897E-2</v>
       </c>
       <c r="F21">
-        <v>0.157105919646333</v>
+        <v>0.158538746497771</v>
       </c>
       <c r="G21">
-        <v>-1.85083505367722</v>
+        <v>-1.8417562581404501</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -13108,13 +13118,13 @@
         <v>69318</v>
       </c>
       <c r="E22">
-        <v>2.49E-3</v>
+        <v>2.9099709002909902E-3</v>
       </c>
       <c r="F22">
-        <v>8.5168289481052303E-3</v>
+        <v>6.9483671683743999E-3</v>
       </c>
       <c r="G22">
-        <v>-4.7657111966100203</v>
+        <v>-4.96924858681035</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -13131,13 +13141,13 @@
         <v>56381</v>
       </c>
       <c r="E23">
-        <v>8.7179999999999994E-2</v>
+        <v>8.6980869808698E-2</v>
       </c>
       <c r="F23">
-        <v>0.27293517554942398</v>
+        <v>0.17887325579206301</v>
       </c>
       <c r="G23">
-        <v>-1.29852096419332</v>
+        <v>-1.72107779214082</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -13154,13 +13164,13 @@
         <v>54241</v>
       </c>
       <c r="E24">
-        <v>1.09E-3</v>
+        <v>1.620016200162E-3</v>
       </c>
       <c r="F24">
-        <v>3.2886569653648402E-3</v>
+        <v>3.2401040027916599E-3</v>
       </c>
       <c r="G24">
-        <v>-5.7172760147625103</v>
+        <v>-5.73214985006602</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -13177,7 +13187,7 @@
         <v>51380</v>
       </c>
       <c r="E25">
-        <v>0.34822999999999998</v>
+        <v>0.51893518935189298</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -13200,13 +13210,13 @@
         <v>52929</v>
       </c>
       <c r="E26">
-        <v>0.19989000000000001</v>
+        <v>0.29787297872978702</v>
       </c>
       <c r="F26">
-        <v>0.589580073239939</v>
+        <v>0.58568402014887</v>
       </c>
       <c r="G26">
-        <v>-0.52834473576101404</v>
+        <v>-0.53497484959670505</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -13223,13 +13233,13 @@
         <v>67134</v>
       </c>
       <c r="E27">
-        <v>0.30486999999999997</v>
+        <v>8.0900809008089998E-3</v>
       </c>
       <c r="F27">
-        <v>1.1492319563763</v>
+        <v>1.91330462605762E-2</v>
       </c>
       <c r="G27">
-        <v>0.13909385523402801</v>
+        <v>-3.95633826823991</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -13246,13 +13256,13 @@
         <v>49178</v>
       </c>
       <c r="E28">
-        <v>5.6759999999999998E-2</v>
+        <v>8.4590845908459E-2</v>
       </c>
       <c r="F28">
-        <v>0.15691361174878399</v>
+        <v>0.15840837270788899</v>
       </c>
       <c r="G28">
-        <v>-1.85205986871172</v>
+        <v>-1.84257894299439</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -13269,13 +13279,13 @@
         <v>68079</v>
       </c>
       <c r="E29">
-        <v>1.98E-3</v>
+        <v>1.910019100191E-3</v>
       </c>
       <c r="F29">
-        <v>7.5865782984086399E-3</v>
+        <v>4.5730323634844599E-3</v>
       </c>
       <c r="G29">
-        <v>-4.8813746062971202</v>
+        <v>-5.3875787572517799</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -13292,13 +13302,13 @@
         <v>55161</v>
       </c>
       <c r="E30">
-        <v>0.12883</v>
+        <v>0.13181999999999999</v>
       </c>
       <c r="F30">
-        <v>0.45254097379320501</v>
+        <v>0.28035657357026</v>
       </c>
       <c r="G30">
-        <v>-0.79287697012230496</v>
+        <v>-1.27169300896036</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -13315,13 +13325,13 @@
         <v>54782</v>
       </c>
       <c r="E31">
-        <v>9.3999999999999997E-4</v>
+        <v>1.5299999999999999E-3</v>
       </c>
       <c r="F31">
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="G31">
-        <v>-5.71979140964382</v>
+        <v>-5.7327896291805898</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -13338,7 +13348,7 @@
         <v>51895</v>
       </c>
       <c r="E32">
-        <v>0.30120000000000002</v>
+        <v>0.49058000000000002</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -13361,13 +13371,13 @@
         <v>53324</v>
       </c>
       <c r="E33">
-        <v>0.17288999999999999</v>
+        <v>0.28160000000000002</v>
       </c>
       <c r="F33">
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="G33">
-        <v>-0.53044011180905404</v>
+        <v>-0.53652374030104899</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -13384,13 +13394,13 @@
         <v>67156</v>
       </c>
       <c r="E34">
-        <v>0.34314</v>
+        <v>1.0749999999999999E-2</v>
       </c>
       <c r="F34">
-        <v>1.4827841473737</v>
+        <v>2.67214247564647E-2</v>
       </c>
       <c r="G34">
-        <v>0.393921501229541</v>
+        <v>-3.62228961001126</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -13407,13 +13417,13 @@
         <v>49473</v>
       </c>
       <c r="E35">
-        <v>4.9099999999999998E-2</v>
+        <v>7.9969999999999999E-2</v>
       </c>
       <c r="F35">
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="G35">
-        <v>-1.85574340112526</v>
+        <v>-1.8454228002411299</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -13430,13 +13440,13 @@
         <v>68366</v>
       </c>
       <c r="E36">
-        <v>3.8999999999999998E-3</v>
+        <v>3.7499999999999999E-3</v>
       </c>
       <c r="F36">
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="G36">
-        <v>-4.0623437727901299</v>
+        <v>-4.6597095246026097</v>
       </c>
     </row>
   </sheetData>
@@ -13450,15 +13460,15 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AL93"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.1796875" customWidth="1"/>
-    <col min="2" max="2" width="18.90625" customWidth="1"/>
-    <col min="3" max="3" width="24.08984375" customWidth="1"/>
-    <col min="4" max="4" width="14.81640625" customWidth="1"/>
-    <col min="5" max="5" width="16.1796875" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="18" style="6" customWidth="1"/>
-    <col min="8" max="9" width="9.08984375" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38">
@@ -13514,7 +13524,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="15" thickBot="1">
+    <row r="4" spans="1:38" ht="15.75" thickBot="1">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -13536,7 +13546,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="29">
+    <row r="6" spans="1:38" ht="30">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -13564,7 +13574,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:38" ht="43.5">
+    <row r="8" spans="1:38" ht="45">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -13577,6 +13587,13 @@
       <c r="F8" s="25" t="s">
         <v>84</v>
       </c>
+      <c r="R8" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="31"/>
     </row>
     <row r="9" spans="1:38">
       <c r="A9" s="11" t="s">
@@ -13742,122 +13759,122 @@
       </c>
       <c r="H10" s="20">
         <f>I10</f>
-        <v>0.14562875828586999</v>
+        <v>7.5738458244009904E-2</v>
       </c>
       <c r="I10" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!I$9,recalculated_shareweights!$C:$C,Data!$C10)</f>
-        <v>0.14562875828586999</v>
+        <v>7.5738458244009904E-2</v>
       </c>
       <c r="J10" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!J$9,recalculated_shareweights!$C:$C,Data!$C10)</f>
-        <v>0.25157645096963099</v>
+        <v>0.16254791306372199</v>
       </c>
       <c r="K10" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!K$9,recalculated_shareweights!$C:$C,Data!$C10)</f>
-        <v>0.24934859903793999</v>
+        <v>0.13456250619976501</v>
       </c>
       <c r="L10" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!L$9,recalculated_shareweights!$C:$C,Data!$C10)</f>
-        <v>0.27293517554942398</v>
+        <v>0.17887325579206301</v>
       </c>
       <c r="M10" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!M$9,recalculated_shareweights!$C:$C,Data!$C10)</f>
-        <v>0.45254097379320501</v>
+        <v>0.28035657357026</v>
       </c>
       <c r="N10">
         <f>M10+($R$10-$M$10)/($R$9-$M$9)</f>
-        <v>0.55003277903456405</v>
+        <v>0.32028525885620801</v>
       </c>
       <c r="O10">
         <f t="shared" ref="O10:Q10" si="1">N10+($R$10-$M$10)/($R$9-$M$9)</f>
-        <v>0.64752458427592308</v>
+        <v>0.36021394414215602</v>
       </c>
       <c r="P10">
         <f t="shared" si="1"/>
-        <v>0.74501638951728211</v>
+        <v>0.40014262942810402</v>
       </c>
       <c r="Q10">
         <f t="shared" si="1"/>
-        <v>0.84250819475864114</v>
-      </c>
-      <c r="R10">
-        <v>0.94</v>
+        <v>0.44007131471405203</v>
+      </c>
+      <c r="R10" s="31">
+        <v>0.48</v>
       </c>
       <c r="S10">
         <f>R10+($W$10-$R$10)/($W$9-$R$9)</f>
-        <v>1.002</v>
+        <v>0.504</v>
       </c>
       <c r="T10">
         <f t="shared" ref="T10:V10" si="2">S10+($W$10-$R$10)/($W$9-$R$9)</f>
-        <v>1.0640000000000001</v>
+        <v>0.52800000000000002</v>
       </c>
       <c r="U10">
         <f t="shared" si="2"/>
-        <v>1.1260000000000001</v>
+        <v>0.55200000000000005</v>
       </c>
       <c r="V10">
         <f t="shared" si="2"/>
-        <v>1.1880000000000002</v>
-      </c>
-      <c r="W10">
-        <v>1.25</v>
+        <v>0.57600000000000007</v>
+      </c>
+      <c r="W10" s="31">
+        <v>0.6</v>
       </c>
       <c r="X10">
         <f t="shared" ref="X10" si="3">W10+($AB$10-$W$10)/($AB$9-$W$9)</f>
-        <v>1.34</v>
+        <v>0.64600000000000002</v>
       </c>
       <c r="Y10">
         <f>X10+($AB$10-$W$10)/($AB$9-$W$9)</f>
-        <v>1.4300000000000002</v>
+        <v>0.69200000000000006</v>
       </c>
       <c r="Z10">
         <f t="shared" ref="Z10:AA10" si="4">Y10+($AB$10-$W$10)/($AB$9-$W$9)</f>
-        <v>1.5200000000000002</v>
+        <v>0.7380000000000001</v>
       </c>
       <c r="AA10">
         <f t="shared" si="4"/>
-        <v>1.6100000000000003</v>
-      </c>
-      <c r="AB10">
-        <v>1.7</v>
+        <v>0.78400000000000014</v>
+      </c>
+      <c r="AB10" s="31">
+        <v>0.83</v>
       </c>
       <c r="AC10">
         <f t="shared" ref="AC10" si="5">AB10+($AG$10-$AB$10)/($AG$9-$AB$9)</f>
-        <v>1.91</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="AD10">
         <f>AC10+($AG$10-$AB$10)/($AG$9-$AB$9)</f>
-        <v>2.12</v>
+        <v>1.0579999999999998</v>
       </c>
       <c r="AE10">
         <f t="shared" ref="AE10:AF10" si="6">AD10+($AG$10-$AB$10)/($AG$9-$AB$9)</f>
-        <v>2.33</v>
+        <v>1.1719999999999997</v>
       </c>
       <c r="AF10">
         <f t="shared" si="6"/>
-        <v>2.54</v>
-      </c>
-      <c r="AG10">
-        <v>2.75</v>
+        <v>1.2859999999999996</v>
+      </c>
+      <c r="AG10" s="31">
+        <v>1.4</v>
       </c>
       <c r="AH10">
         <f t="shared" ref="AH10" si="7">AG10+($AL$10-$AG$10)/($AL$9-$AG$9)</f>
-        <v>3.2800000000000002</v>
+        <v>1.64</v>
       </c>
       <c r="AI10">
         <f>AH10+($AL$10-$AG$10)/($AL$9-$AG$9)</f>
-        <v>3.8100000000000005</v>
+        <v>1.88</v>
       </c>
       <c r="AJ10">
         <f t="shared" ref="AJ10:AK10" si="8">AI10+($AL$10-$AG$10)/($AL$9-$AG$9)</f>
-        <v>4.3400000000000007</v>
+        <v>2.12</v>
       </c>
       <c r="AK10">
         <f t="shared" si="8"/>
-        <v>4.870000000000001</v>
-      </c>
-      <c r="AL10">
-        <v>5.4</v>
+        <v>2.3600000000000003</v>
+      </c>
+      <c r="AL10" s="31">
+        <v>2.6</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -13878,127 +13895,127 @@
       </c>
       <c r="H11" s="20">
         <f t="shared" ref="H11:H16" si="9">I11</f>
-        <v>3.3752550513252298E-3</v>
+        <v>3.3111542696076198E-3</v>
       </c>
       <c r="I11" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!I$9,recalculated_shareweights!$C:$C,Data!$C11)</f>
-        <v>3.3752550513252298E-3</v>
+        <v>3.3111542696076198E-3</v>
       </c>
       <c r="J11" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!J$9,recalculated_shareweights!$C:$C,Data!$C11)</f>
-        <v>3.2073136116094201E-3</v>
+        <v>3.18875302069616E-3</v>
       </c>
       <c r="K11" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!K$9,recalculated_shareweights!$C:$C,Data!$C11)</f>
-        <v>3.2731580821590001E-3</v>
+        <v>3.2416232692108801E-3</v>
       </c>
       <c r="L11" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!L$9,recalculated_shareweights!$C:$C,Data!$C11)</f>
-        <v>3.2886569653648402E-3</v>
+        <v>3.2401040027916599E-3</v>
       </c>
       <c r="M11" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!M$9,recalculated_shareweights!$C:$C,Data!$C11)</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="N11">
         <f t="shared" ref="N11:AL11" si="10">M11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="O11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="P11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="Q11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="R11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="S11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="T11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="U11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="V11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="W11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="X11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="Y11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="Z11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AA11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AB11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AC11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AD11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AE11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AF11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AG11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AH11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AI11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AJ11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AK11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AL11">
         <f t="shared" si="10"/>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -14160,127 +14177,127 @@
       </c>
       <c r="H13" s="20">
         <f t="shared" si="9"/>
-        <v>0.59151755489837199</v>
+        <v>0.58713757439567404</v>
       </c>
       <c r="I13" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!I$9,recalculated_shareweights!$C:$C,Data!$C13)</f>
-        <v>0.59151755489837199</v>
+        <v>0.58713757439567404</v>
       </c>
       <c r="J13" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!J$9,recalculated_shareweights!$C:$C,Data!$C13)</f>
-        <v>0.59031765788952895</v>
+        <v>0.58625646954423505</v>
       </c>
       <c r="K13" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!K$9,recalculated_shareweights!$C:$C,Data!$C13)</f>
-        <v>0.58983194859159405</v>
+        <v>0.58587879933822895</v>
       </c>
       <c r="L13" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!L$9,recalculated_shareweights!$C:$C,Data!$C13)</f>
-        <v>0.589580073239939</v>
+        <v>0.58568402014887</v>
       </c>
       <c r="M13" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!M$9,recalculated_shareweights!$C:$C,Data!$C13)</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="N13">
         <f t="shared" ref="N13:AL13" si="13">M13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="O13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="P13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="Q13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="R13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="S13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="T13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="U13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="V13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="W13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="X13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="Y13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="Z13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AA13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AB13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AC13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AD13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AE13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AF13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AG13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AH13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AI13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AJ13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AK13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AL13">
         <f t="shared" si="13"/>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -14300,126 +14317,122 @@
       </c>
       <c r="H14" s="20">
         <f t="shared" si="9"/>
-        <v>0.356961080621581</v>
+        <v>3.0097006982601999E-2</v>
       </c>
       <c r="I14" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!I$9,recalculated_shareweights!$C:$C,Data!$C14)</f>
-        <v>0.356961080621581</v>
+        <v>3.0097006982601999E-2</v>
       </c>
       <c r="J14" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!J$9,recalculated_shareweights!$C:$C,Data!$C14)</f>
-        <v>0.46266979168123801</v>
+        <v>2.1911439020317398E-2</v>
       </c>
       <c r="K14" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!K$9,recalculated_shareweights!$C:$C,Data!$C14)</f>
-        <v>0.68107773418921602</v>
+        <v>2.0681798718551799E-2</v>
       </c>
       <c r="L14" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!L$9,recalculated_shareweights!$C:$C,Data!$C14)</f>
-        <v>1.1492319563763</v>
+        <v>1.91330462605762E-2</v>
       </c>
       <c r="M14" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!M$9,recalculated_shareweights!$C:$C,Data!$C14)</f>
-        <v>1.4827841473737</v>
+        <v>2.67214247564647E-2</v>
       </c>
       <c r="N14">
         <f>M14+($R$14-$M$14)/($R$9-$M$9)</f>
-        <v>1.5862273178989601</v>
+        <v>3.097713980517176E-2</v>
       </c>
       <c r="O14">
         <f t="shared" ref="O14:Q14" si="14">N14+($R$14-$M$14)/($R$9-$M$9)</f>
-        <v>1.6896704884242202</v>
+        <v>3.5232854853878823E-2</v>
       </c>
       <c r="P14">
         <f t="shared" si="14"/>
-        <v>1.7931136589494803</v>
+        <v>3.9488569902585882E-2</v>
       </c>
       <c r="Q14">
         <f t="shared" si="14"/>
-        <v>1.8965568294747404</v>
-      </c>
-      <c r="R14">
-        <v>2</v>
+        <v>4.3744284951292942E-2</v>
+      </c>
+      <c r="R14" s="31">
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="S14">
-        <f t="shared" ref="S14:AL14" si="15">R14</f>
-        <v>2</v>
+        <f>R14+($W$14-$R$14)/($W$9-$R$9)</f>
+        <v>5.2400000000000002E-2</v>
       </c>
       <c r="T14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <f t="shared" ref="T14:V14" si="15">S14+($W$14-$R$14)/($W$9-$R$9)</f>
+        <v>5.6800000000000003E-2</v>
       </c>
       <c r="U14">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>6.1200000000000004E-2</v>
       </c>
       <c r="V14">
         <f t="shared" si="15"/>
-        <v>2</v>
-      </c>
-      <c r="W14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <v>6.5600000000000006E-2</v>
+      </c>
+      <c r="W14" s="31">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="X14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <f>W14+($AB$14-$W$14)/($AB$9-$W$9)</f>
+        <v>7.46E-2</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <f t="shared" ref="Y14:AA14" si="16">X14+($AB$14-$W$14)/($AB$9-$W$9)</f>
+        <v>7.9199999999999993E-2</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <f t="shared" si="16"/>
+        <v>8.3799999999999986E-2</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="15"/>
-        <v>2</v>
-      </c>
-      <c r="AB14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <f t="shared" si="16"/>
+        <v>8.8399999999999979E-2</v>
+      </c>
+      <c r="AB14" s="31">
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <f t="shared" ref="AC14" si="17">AB14+($AG$14-$AB$14)/($AG$9-$AB$9)</f>
+        <v>0.1024</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <f>AC14+($AG$14-$AB$14)/($AG$9-$AB$9)</f>
+        <v>0.11180000000000001</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <f t="shared" ref="AE14:AF14" si="18">AD14+($AG$14-$AB$14)/($AG$9-$AB$9)</f>
+        <v>0.12120000000000002</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="15"/>
-        <v>2</v>
-      </c>
-      <c r="AG14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <f t="shared" si="18"/>
+        <v>0.13060000000000002</v>
+      </c>
+      <c r="AG14" s="31">
+        <v>0.14000000000000001</v>
       </c>
       <c r="AH14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <f t="shared" ref="AH14" si="19">AG14+($AL$14-$AG$14)/($AL$9-$AG$9)</f>
+        <v>0.16400000000000001</v>
       </c>
       <c r="AI14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <f>AH14+($AL$14-$AG$14)/($AL$9-$AG$9)</f>
+        <v>0.188</v>
       </c>
       <c r="AJ14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <f t="shared" ref="AJ14:AK14" si="20">AI14+($AL$14-$AG$14)/($AL$9-$AG$9)</f>
+        <v>0.21199999999999999</v>
       </c>
       <c r="AK14">
-        <f t="shared" si="15"/>
-        <v>2</v>
-      </c>
-      <c r="AL14">
-        <f t="shared" si="15"/>
-        <v>2</v>
+        <f t="shared" si="20"/>
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="AL14" s="31">
+        <v>0.26</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -14440,130 +14453,130 @@
       </c>
       <c r="H15" s="20">
         <f t="shared" si="9"/>
-        <v>0.171593660015216</v>
+        <v>0.169435072322971</v>
       </c>
       <c r="I15" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!I$9,recalculated_shareweights!$C:$C,Data!$C15)</f>
-        <v>0.171593660015216</v>
+        <v>0.169435072322971</v>
       </c>
       <c r="J15" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!J$9,recalculated_shareweights!$C:$C,Data!$C15)</f>
-        <v>0.157380451105636</v>
+        <v>0.15875306561484401</v>
       </c>
       <c r="K15" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!K$9,recalculated_shareweights!$C:$C,Data!$C15)</f>
-        <v>0.157105919646333</v>
+        <v>0.158538746497771</v>
       </c>
       <c r="L15" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!L$9,recalculated_shareweights!$C:$C,Data!$C15)</f>
-        <v>0.15691361174878399</v>
+        <v>0.15840837270788899</v>
       </c>
       <c r="M15" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!M$9,recalculated_shareweights!$C:$C,Data!$C15)</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="N15">
-        <f t="shared" ref="N15:AL15" si="16">M15</f>
-        <v>0.15633667860209499</v>
+        <f t="shared" ref="N15:AL15" si="21">M15</f>
+        <v>0.15795852186818499</v>
       </c>
       <c r="O15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="P15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="R15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="S15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="T15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="U15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="V15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="W15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="X15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="Z15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AD15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AE15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AF15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AG15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AH15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AI15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AJ15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AK15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AL15">
-        <f t="shared" si="16"/>
-        <v>0.15633667860209499</v>
-      </c>
-    </row>
-    <row r="16" spans="1:38" ht="15" thickBot="1">
+        <f t="shared" si="21"/>
+        <v>0.15795852186818499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" ht="15.75" thickBot="1">
       <c r="A16" s="21"/>
       <c r="B16" s="21"/>
       <c r="C16" s="21" t="s">
@@ -14583,127 +14596,127 @@
       </c>
       <c r="H16" s="20">
         <f t="shared" si="9"/>
-        <v>1.8305978574742698E-2</v>
+        <v>1.5971754362172401E-2</v>
       </c>
       <c r="I16" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!I$9,recalculated_shareweights!$C:$C,Data!$C16)</f>
-        <v>1.8305978574742698E-2</v>
+        <v>1.5971754362172401E-2</v>
       </c>
       <c r="J16" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!J$9,recalculated_shareweights!$C:$C,Data!$C16)</f>
-        <v>1.9637350115763199E-2</v>
+        <v>1.7435929211407498E-2</v>
       </c>
       <c r="K16" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!K$9,recalculated_shareweights!$C:$C,Data!$C16)</f>
-        <v>8.5168289481052303E-3</v>
+        <v>6.9483671683743999E-3</v>
       </c>
       <c r="L16" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!L$9,recalculated_shareweights!$C:$C,Data!$C16)</f>
-        <v>7.5865782984086399E-3</v>
+        <v>4.5730323634844599E-3</v>
       </c>
       <c r="M16" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!M$9,recalculated_shareweights!$C:$C,Data!$C16)</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="N16">
-        <f t="shared" ref="N16:AL16" si="17">M16</f>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" ref="N16:AL16" si="22">M16</f>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="O16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="P16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="R16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="S16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="T16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="U16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="V16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="W16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="X16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="Y16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="Z16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AC16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AD16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AE16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AF16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AG16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AH16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AI16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AJ16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AK16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AL16">
-        <f t="shared" si="17"/>
-        <v>1.72086386734626E-2</v>
+        <f t="shared" si="22"/>
+        <v>9.4692125755478501E-3</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -14729,7 +14742,7 @@
         <v>s-curve</v>
       </c>
       <c r="H17" s="20">
-        <f t="shared" ref="H17:H40" si="18">D17</f>
+        <f t="shared" ref="H17:H40" si="23">D17</f>
         <v>5.3683612196023132E-3</v>
       </c>
       <c r="I17">
@@ -14869,7 +14882,7 @@
         <v>76</v>
       </c>
       <c r="H18" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>6.1283704210113928E-4</v>
       </c>
       <c r="I18">
@@ -15002,7 +15015,7 @@
         <v>1.9186119393907859E-2</v>
       </c>
       <c r="E19" s="20">
-        <f t="shared" ref="E19:E20" si="19">D19</f>
+        <f t="shared" ref="E19:E20" si="24">D19</f>
         <v>1.9186119393907859E-2</v>
       </c>
       <c r="F19" s="6" t="str">
@@ -15010,7 +15023,7 @@
         <v>n/a</v>
       </c>
       <c r="H19" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>1.9186119393907859E-2</v>
       </c>
       <c r="I19">
@@ -15142,7 +15155,7 @@
         <v>3</v>
       </c>
       <c r="E20" s="20">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
       <c r="F20" s="6" t="str">
@@ -15150,7 +15163,7 @@
         <v>n/a</v>
       </c>
       <c r="H20" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>3</v>
       </c>
       <c r="I20">
@@ -15291,7 +15304,7 @@
         <v>s-curve</v>
       </c>
       <c r="H21" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I21">
@@ -15432,7 +15445,7 @@
         <v>n/a</v>
       </c>
       <c r="H22" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>4.237817368977314E-2</v>
       </c>
       <c r="I22">
@@ -15556,7 +15569,7 @@
         <v>4.237817368977314E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:38" ht="15" thickBot="1">
+    <row r="23" spans="1:38" ht="15.75" thickBot="1">
       <c r="A23" s="21"/>
       <c r="B23" s="21"/>
       <c r="C23" s="21" t="s">
@@ -15575,7 +15588,7 @@
         <v>s-curve</v>
       </c>
       <c r="H23" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I23">
@@ -15721,7 +15734,7 @@
         <v>s-curve</v>
       </c>
       <c r="H24" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>7.2747216149611415E-3</v>
       </c>
       <c r="I24">
@@ -15862,7 +15875,7 @@
         <v>n/a</v>
       </c>
       <c r="H25" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>2.155996206658648E-3</v>
       </c>
       <c r="I25">
@@ -15995,7 +16008,7 @@
         <v>2.0708630477691714</v>
       </c>
       <c r="E26" s="20">
-        <f t="shared" ref="E26:E29" si="20">D26</f>
+        <f t="shared" ref="E26:E29" si="25">D26</f>
         <v>2.0708630477691714</v>
       </c>
       <c r="F26" s="6" t="str">
@@ -16003,7 +16016,7 @@
         <v>n/a</v>
       </c>
       <c r="H26" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>2.0708630477691714</v>
       </c>
       <c r="I26">
@@ -16136,7 +16149,7 @@
         <v>1.1886920057569821</v>
       </c>
       <c r="E27" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>1.1886920057569821</v>
       </c>
       <c r="F27" s="6" t="str">
@@ -16144,7 +16157,7 @@
         <v>n/a</v>
       </c>
       <c r="H27" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>1.1886920057569821</v>
       </c>
       <c r="I27">
@@ -16277,7 +16290,7 @@
         <v>4.0868310546055435E-2</v>
       </c>
       <c r="E28" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>4.0868310546055435E-2</v>
       </c>
       <c r="F28" s="6" t="str">
@@ -16285,7 +16298,7 @@
         <v>n/a</v>
       </c>
       <c r="H28" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>4.0868310546055435E-2</v>
       </c>
       <c r="I28">
@@ -16418,7 +16431,7 @@
         <v>0.11252178195802712</v>
       </c>
       <c r="E29" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0.11252178195802712</v>
       </c>
       <c r="F29" s="6" t="str">
@@ -16426,7 +16439,7 @@
         <v>n/a</v>
       </c>
       <c r="H29" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0.11252178195802712</v>
       </c>
       <c r="I29">
@@ -16550,7 +16563,7 @@
         <v>0.11252178195802712</v>
       </c>
     </row>
-    <row r="30" spans="1:38" ht="15" thickBot="1">
+    <row r="30" spans="1:38" ht="15.75" thickBot="1">
       <c r="A30" s="21"/>
       <c r="B30" s="21"/>
       <c r="C30" s="21" t="s">
@@ -16569,7 +16582,7 @@
         <v>s-curve</v>
       </c>
       <c r="H30" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>6.6083849891288092E-4</v>
       </c>
       <c r="I30">
@@ -16716,7 +16729,7 @@
         <v>s-curve</v>
       </c>
       <c r="H31" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>5.3709944550863111E-3</v>
       </c>
       <c r="I31">
@@ -16857,7 +16870,7 @@
         <v>n/a</v>
       </c>
       <c r="H32" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I32">
@@ -16990,7 +17003,7 @@
         <v>1.9195530379555355E-2</v>
       </c>
       <c r="E33" s="20">
-        <f t="shared" ref="E33:E36" si="21">D33</f>
+        <f t="shared" ref="E33:E36" si="26">D33</f>
         <v>1.9195530379555355E-2</v>
       </c>
       <c r="F33" s="6" t="str">
@@ -16998,7 +17011,7 @@
         <v>n/a</v>
       </c>
       <c r="H33" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>1.9195530379555355E-2</v>
       </c>
       <c r="I33">
@@ -17131,7 +17144,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="20">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>3</v>
       </c>
       <c r="F34" s="6" t="str">
@@ -17139,7 +17152,7 @@
         <v>n/a</v>
       </c>
       <c r="H34" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>3</v>
       </c>
       <c r="I34">
@@ -17272,7 +17285,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="20">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="F35" s="6" t="str">
@@ -17280,7 +17293,7 @@
         <v>n/a</v>
       </c>
       <c r="H35" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I35">
@@ -17413,7 +17426,7 @@
         <v>4.2398960612661157E-2</v>
       </c>
       <c r="E36" s="20">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>4.2398960612661157E-2</v>
       </c>
       <c r="F36" s="6" t="str">
@@ -17421,7 +17434,7 @@
         <v>n/a</v>
       </c>
       <c r="H36" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>4.2398960612661157E-2</v>
       </c>
       <c r="I36">
@@ -17545,7 +17558,7 @@
         <v>4.2398960612661157E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:38" ht="15" thickBot="1">
+    <row r="37" spans="1:38" ht="15.75" thickBot="1">
       <c r="A37" s="21"/>
       <c r="B37" s="21"/>
       <c r="C37" s="21" t="s">
@@ -17564,7 +17577,7 @@
         <v>s-curve</v>
       </c>
       <c r="H37" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I37">
@@ -17709,7 +17722,7 @@
         <v>n/a</v>
       </c>
       <c r="H38" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I38">
@@ -17848,7 +17861,7 @@
         <v>n/a</v>
       </c>
       <c r="H39" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I39">
@@ -17987,7 +18000,7 @@
         <v>n/a</v>
       </c>
       <c r="H40" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I40">
@@ -18126,7 +18139,7 @@
         <v>n/a</v>
       </c>
       <c r="H41" s="20">
-        <f t="shared" ref="H41:H72" si="22">D41</f>
+        <f t="shared" ref="H41:H72" si="27">D41</f>
         <v>1</v>
       </c>
       <c r="I41">
@@ -18265,7 +18278,7 @@
         <v>n/a</v>
       </c>
       <c r="H42" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I42">
@@ -18404,7 +18417,7 @@
         <v>n/a</v>
       </c>
       <c r="H43" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I43">
@@ -18528,7 +18541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" ht="15" thickBot="1">
+    <row r="44" spans="1:38" ht="15.75" thickBot="1">
       <c r="A44" s="21"/>
       <c r="B44" s="21"/>
       <c r="C44" s="21" t="s">
@@ -18545,7 +18558,7 @@
         <v>n/a</v>
       </c>
       <c r="H44" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I44">
@@ -18690,7 +18703,7 @@
         <v>n/a</v>
       </c>
       <c r="H45" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I45">
@@ -18829,7 +18842,7 @@
         <v>n/a</v>
       </c>
       <c r="H46" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I46">
@@ -18968,7 +18981,7 @@
         <v>n/a</v>
       </c>
       <c r="H47" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I47">
@@ -19107,7 +19120,7 @@
         <v>n/a</v>
       </c>
       <c r="H48" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="I48">
@@ -19246,7 +19259,7 @@
         <v>n/a</v>
       </c>
       <c r="H49" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I49">
@@ -19385,7 +19398,7 @@
         <v>n/a</v>
       </c>
       <c r="H50" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I50">
@@ -19509,7 +19522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:38" ht="15" thickBot="1">
+    <row r="51" spans="1:38" ht="15.75" thickBot="1">
       <c r="A51" s="21"/>
       <c r="B51" s="21"/>
       <c r="C51" s="21" t="s">
@@ -19526,7 +19539,7 @@
         <v>n/a</v>
       </c>
       <c r="H51" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I51">
@@ -19673,7 +19686,7 @@
         <v>n/a</v>
       </c>
       <c r="H52" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0.76226911968156119</v>
       </c>
       <c r="I52">
@@ -19806,7 +19819,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="20">
-        <f t="shared" ref="E53:E58" si="23">D53</f>
+        <f t="shared" ref="E53:E58" si="28">D53</f>
         <v>0</v>
       </c>
       <c r="F53" s="6" t="str">
@@ -19814,7 +19827,7 @@
         <v>n/a</v>
       </c>
       <c r="H53" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I53">
@@ -19947,7 +19960,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F54" s="6" t="str">
@@ -19955,7 +19968,7 @@
         <v>n/a</v>
       </c>
       <c r="H54" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I54">
@@ -20088,7 +20101,7 @@
         <v>0.48773088031843881</v>
       </c>
       <c r="E55" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0.48773088031843881</v>
       </c>
       <c r="F55" s="6" t="str">
@@ -20096,7 +20109,7 @@
         <v>n/a</v>
       </c>
       <c r="H55" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0.48773088031843881</v>
       </c>
       <c r="I55">
@@ -20229,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="E56" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F56" s="6" t="str">
@@ -20237,7 +20250,7 @@
         <v>n/a</v>
       </c>
       <c r="H56" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I56">
@@ -20370,7 +20383,7 @@
         <v>0</v>
       </c>
       <c r="E57" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F57" s="6" t="str">
@@ -20378,7 +20391,7 @@
         <v>n/a</v>
       </c>
       <c r="H57" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I57">
@@ -20502,7 +20515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:38" ht="15" thickBot="1">
+    <row r="58" spans="1:38" ht="15.75" thickBot="1">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21" t="s">
@@ -20513,7 +20526,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F58" s="7" t="str">
@@ -20521,7 +20534,7 @@
         <v>n/a</v>
       </c>
       <c r="H58" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I58">
@@ -20668,7 +20681,7 @@
         <v>n/a</v>
       </c>
       <c r="H59" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0.50990675990675993</v>
       </c>
       <c r="I59">
@@ -20801,7 +20814,7 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <f t="shared" ref="E60:E65" si="24">D60</f>
+        <f t="shared" ref="E60:E65" si="29">D60</f>
         <v>0</v>
       </c>
       <c r="F60" s="6" t="str">
@@ -20809,7 +20822,7 @@
         <v>n/a</v>
       </c>
       <c r="H60" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I60">
@@ -20942,7 +20955,7 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F61" s="6" t="str">
@@ -20950,7 +20963,7 @@
         <v>n/a</v>
       </c>
       <c r="H61" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I61">
@@ -21083,7 +21096,7 @@
         <v>0.74009324009324007</v>
       </c>
       <c r="E62">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>0.74009324009324007</v>
       </c>
       <c r="F62" s="6" t="str">
@@ -21091,7 +21104,7 @@
         <v>n/a</v>
       </c>
       <c r="H62" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0.74009324009324007</v>
       </c>
       <c r="I62">
@@ -21224,7 +21237,7 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F63" s="6" t="str">
@@ -21232,7 +21245,7 @@
         <v>n/a</v>
       </c>
       <c r="H63" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I63">
@@ -21365,7 +21378,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F64" s="6" t="str">
@@ -21373,7 +21386,7 @@
         <v>n/a</v>
       </c>
       <c r="H64" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I64">
@@ -21497,7 +21510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:38" ht="15" thickBot="1">
+    <row r="65" spans="1:38" ht="15.75" thickBot="1">
       <c r="A65" s="21"/>
       <c r="B65" s="21"/>
       <c r="C65" s="21" t="s">
@@ -21508,7 +21521,7 @@
         <v>0</v>
       </c>
       <c r="E65" s="21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F65" s="7" t="str">
@@ -21516,7 +21529,7 @@
         <v>n/a</v>
       </c>
       <c r="H65" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I65">
@@ -21661,7 +21674,7 @@
         <v>n/a</v>
       </c>
       <c r="H66" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I66">
@@ -21800,7 +21813,7 @@
         <v>n/a</v>
       </c>
       <c r="H67" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I67">
@@ -21939,7 +21952,7 @@
         <v>n/a</v>
       </c>
       <c r="H68" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I68">
@@ -22078,7 +22091,7 @@
         <v>n/a</v>
       </c>
       <c r="H69" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="I69">
@@ -22217,7 +22230,7 @@
         <v>n/a</v>
       </c>
       <c r="H70" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I70">
@@ -22356,7 +22369,7 @@
         <v>n/a</v>
       </c>
       <c r="H71" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I71">
@@ -22480,7 +22493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:38" ht="15" thickBot="1">
+    <row r="72" spans="1:38" ht="15.75" thickBot="1">
       <c r="A72" s="21"/>
       <c r="B72" s="21"/>
       <c r="C72" s="21" t="s">
@@ -22497,7 +22510,7 @@
         <v>n/a</v>
       </c>
       <c r="H72" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I72">
@@ -22644,7 +22657,7 @@
         <v>n/a</v>
       </c>
       <c r="H73" s="20">
-        <f t="shared" ref="H73:H93" si="25">D73</f>
+        <f t="shared" ref="H73:H93" si="30">D73</f>
         <v>0</v>
       </c>
       <c r="I73">
@@ -22777,7 +22790,7 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <f t="shared" ref="E74:E79" si="26">D74</f>
+        <f t="shared" ref="E74:E79" si="31">D74</f>
         <v>0</v>
       </c>
       <c r="F74" s="6" t="str">
@@ -22785,7 +22798,7 @@
         <v>n/a</v>
       </c>
       <c r="H74" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I74">
@@ -22918,7 +22931,7 @@
         <v>4.1666444445629626E-3</v>
       </c>
       <c r="E75">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>4.1666444445629626E-3</v>
       </c>
       <c r="F75" s="6" t="str">
@@ -22926,7 +22939,7 @@
         <v>n/a</v>
       </c>
       <c r="H75" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>4.1666444445629626E-3</v>
       </c>
       <c r="I75">
@@ -23059,7 +23072,7 @@
         <v>1</v>
       </c>
       <c r="E76">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F76" s="6" t="str">
@@ -23067,7 +23080,7 @@
         <v>n/a</v>
       </c>
       <c r="H76" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="I76">
@@ -23200,7 +23213,7 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="F77" s="6" t="str">
@@ -23208,7 +23221,7 @@
         <v>n/a</v>
       </c>
       <c r="H77" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I77">
@@ -23341,7 +23354,7 @@
         <v>1.6666577778251849E-3</v>
       </c>
       <c r="E78">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>1.6666577778251849E-3</v>
       </c>
       <c r="F78" s="6" t="str">
@@ -23349,7 +23362,7 @@
         <v>n/a</v>
       </c>
       <c r="H78" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>1.6666577778251849E-3</v>
       </c>
       <c r="I78">
@@ -23473,7 +23486,7 @@
         <v>1.6666577778251849E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:38" ht="15" thickBot="1">
+    <row r="79" spans="1:38" ht="15.75" thickBot="1">
       <c r="A79" s="21"/>
       <c r="B79" s="21"/>
       <c r="C79" s="21" t="s">
@@ -23484,7 +23497,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="21">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="F79" s="7" t="str">
@@ -23492,7 +23505,7 @@
         <v>n/a</v>
       </c>
       <c r="H79" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I79">
@@ -23637,7 +23650,7 @@
         <v>s-curve</v>
       </c>
       <c r="H80" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I80">
@@ -23777,7 +23790,7 @@
         <v>n/a</v>
       </c>
       <c r="H81" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I81">
@@ -23916,7 +23929,7 @@
         <v>n/a</v>
       </c>
       <c r="H82" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>3</v>
       </c>
       <c r="I82">
@@ -24056,7 +24069,7 @@
         <v>n/a</v>
       </c>
       <c r="H83" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I83">
@@ -24196,7 +24209,7 @@
         <v>n/a</v>
       </c>
       <c r="H84" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I84">
@@ -24336,7 +24349,7 @@
         <v>n/a</v>
       </c>
       <c r="H85" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I85">
@@ -24460,7 +24473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:38" ht="15" thickBot="1">
+    <row r="86" spans="1:38" ht="15.75" thickBot="1">
       <c r="A86" s="21"/>
       <c r="B86" s="21"/>
       <c r="C86" s="21" t="s">
@@ -24478,7 +24491,7 @@
         <v>n/a</v>
       </c>
       <c r="H86" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I86">
@@ -24625,7 +24638,7 @@
         <v>s-curve</v>
       </c>
       <c r="H87" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I87">
@@ -24754,11 +24767,11 @@
         <v>2</v>
       </c>
       <c r="D88" s="20">
-        <f t="shared" ref="D88:E93" si="27">D81</f>
+        <f t="shared" ref="D88:E93" si="32">D81</f>
         <v>0</v>
       </c>
       <c r="E88" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="F88" s="6" t="str">
@@ -24766,7 +24779,7 @@
         <v>n/a</v>
       </c>
       <c r="H88" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I88">
@@ -24895,11 +24908,11 @@
         <v>3</v>
       </c>
       <c r="D89" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>3</v>
       </c>
       <c r="E89" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>3</v>
       </c>
       <c r="F89" s="6" t="str">
@@ -24907,7 +24920,7 @@
         <v>n/a</v>
       </c>
       <c r="H89" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>3</v>
       </c>
       <c r="I89">
@@ -25036,11 +25049,11 @@
         <v>4</v>
       </c>
       <c r="D90" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="E90" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="F90" s="6" t="str">
@@ -25048,7 +25061,7 @@
         <v>n/a</v>
       </c>
       <c r="H90" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I90">
@@ -25177,11 +25190,11 @@
         <v>5</v>
       </c>
       <c r="D91" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="E91" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="F91" s="6" t="str">
@@ -25189,7 +25202,7 @@
         <v>n/a</v>
       </c>
       <c r="H91" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I91">
@@ -25318,11 +25331,11 @@
         <v>78</v>
       </c>
       <c r="D92" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="E92" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="F92" s="6" t="str">
@@ -25330,7 +25343,7 @@
         <v>n/a</v>
       </c>
       <c r="H92" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I92">
@@ -25454,14 +25467,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:38" ht="15" thickBot="1">
+    <row r="93" spans="1:38" ht="15.75" thickBot="1">
       <c r="A93" s="21"/>
       <c r="B93" s="21"/>
       <c r="C93" s="21" t="s">
         <v>79</v>
       </c>
       <c r="D93" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="E93" s="21">
@@ -25472,7 +25485,7 @@
         <v>n/a</v>
       </c>
       <c r="H93" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I93">
@@ -25610,12 +25623,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29">
+    <row r="1" spans="1:32" ht="45">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -25750,127 +25763,127 @@
       </c>
       <c r="B2">
         <f>Data!H10</f>
-        <v>0.14562875828586999</v>
+        <v>7.5738458244009904E-2</v>
       </c>
       <c r="C2">
         <f>Data!I10</f>
-        <v>0.14562875828586999</v>
+        <v>7.5738458244009904E-2</v>
       </c>
       <c r="D2">
         <f>Data!J10</f>
-        <v>0.25157645096963099</v>
+        <v>0.16254791306372199</v>
       </c>
       <c r="E2">
         <f>Data!K10</f>
-        <v>0.24934859903793999</v>
+        <v>0.13456250619976501</v>
       </c>
       <c r="F2">
         <f>Data!L10</f>
-        <v>0.27293517554942398</v>
+        <v>0.17887325579206301</v>
       </c>
       <c r="G2">
         <f>Data!M10</f>
-        <v>0.45254097379320501</v>
+        <v>0.28035657357026</v>
       </c>
       <c r="H2">
         <f>Data!N10</f>
-        <v>0.55003277903456405</v>
+        <v>0.32028525885620801</v>
       </c>
       <c r="I2">
         <f>Data!O10</f>
-        <v>0.64752458427592308</v>
+        <v>0.36021394414215602</v>
       </c>
       <c r="J2">
         <f>Data!P10</f>
-        <v>0.74501638951728211</v>
+        <v>0.40014262942810402</v>
       </c>
       <c r="K2">
         <f>Data!Q10</f>
-        <v>0.84250819475864114</v>
+        <v>0.44007131471405203</v>
       </c>
       <c r="L2">
         <f>Data!R10</f>
-        <v>0.94</v>
+        <v>0.48</v>
       </c>
       <c r="M2">
         <f>Data!S10</f>
-        <v>1.002</v>
+        <v>0.504</v>
       </c>
       <c r="N2">
         <f>Data!T10</f>
-        <v>1.0640000000000001</v>
+        <v>0.52800000000000002</v>
       </c>
       <c r="O2">
         <f>Data!U10</f>
-        <v>1.1260000000000001</v>
+        <v>0.55200000000000005</v>
       </c>
       <c r="P2">
         <f>Data!V10</f>
-        <v>1.1880000000000002</v>
+        <v>0.57600000000000007</v>
       </c>
       <c r="Q2">
         <f>Data!W10</f>
-        <v>1.25</v>
+        <v>0.6</v>
       </c>
       <c r="R2">
         <f>Data!X10</f>
-        <v>1.34</v>
+        <v>0.64600000000000002</v>
       </c>
       <c r="S2">
         <f>Data!Y10</f>
-        <v>1.4300000000000002</v>
+        <v>0.69200000000000006</v>
       </c>
       <c r="T2">
         <f>Data!Z10</f>
-        <v>1.5200000000000002</v>
+        <v>0.7380000000000001</v>
       </c>
       <c r="U2">
         <f>Data!AA10</f>
-        <v>1.6100000000000003</v>
+        <v>0.78400000000000014</v>
       </c>
       <c r="V2">
         <f>Data!AB10</f>
-        <v>1.7</v>
+        <v>0.83</v>
       </c>
       <c r="W2">
         <f>Data!AC10</f>
-        <v>1.91</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="X2">
         <f>Data!AD10</f>
-        <v>2.12</v>
+        <v>1.0579999999999998</v>
       </c>
       <c r="Y2">
         <f>Data!AE10</f>
-        <v>2.33</v>
+        <v>1.1719999999999997</v>
       </c>
       <c r="Z2">
         <f>Data!AF10</f>
-        <v>2.54</v>
+        <v>1.2859999999999996</v>
       </c>
       <c r="AA2">
         <f>Data!AG10</f>
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="AB2">
         <f>Data!AH10</f>
-        <v>3.2800000000000002</v>
+        <v>1.64</v>
       </c>
       <c r="AC2">
         <f>Data!AI10</f>
-        <v>3.8100000000000005</v>
+        <v>1.88</v>
       </c>
       <c r="AD2">
         <f>Data!AJ10</f>
-        <v>4.3400000000000007</v>
+        <v>2.12</v>
       </c>
       <c r="AE2">
         <f>Data!AK10</f>
-        <v>4.870000000000001</v>
+        <v>2.3600000000000003</v>
       </c>
       <c r="AF2">
         <f>Data!AL10</f>
-        <v>5.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -25879,127 +25892,127 @@
       </c>
       <c r="B3">
         <f>Data!H11</f>
-        <v>3.3752550513252298E-3</v>
+        <v>3.3111542696076198E-3</v>
       </c>
       <c r="C3">
         <f>Data!I11</f>
-        <v>3.3752550513252298E-3</v>
+        <v>3.3111542696076198E-3</v>
       </c>
       <c r="D3">
         <f>Data!J11</f>
-        <v>3.2073136116094201E-3</v>
+        <v>3.18875302069616E-3</v>
       </c>
       <c r="E3">
         <f>Data!K11</f>
-        <v>3.2731580821590001E-3</v>
+        <v>3.2416232692108801E-3</v>
       </c>
       <c r="F3">
         <f>Data!L11</f>
-        <v>3.2886569653648402E-3</v>
+        <v>3.2401040027916599E-3</v>
       </c>
       <c r="G3">
         <f>Data!M11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="H3">
         <f>Data!N11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="I3">
         <f>Data!O11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="J3">
         <f>Data!P11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="K3">
         <f>Data!Q11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="L3">
         <f>Data!R11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="M3">
         <f>Data!S11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="N3">
         <f>Data!T11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="O3">
         <f>Data!U11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="P3">
         <f>Data!V11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="Q3">
         <f>Data!W11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="R3">
         <f>Data!X11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="S3">
         <f>Data!Y11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="T3">
         <f>Data!Z11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="U3">
         <f>Data!AA11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="V3">
         <f>Data!AB11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="W3">
         <f>Data!AC11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="X3">
         <f>Data!AD11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="Y3">
         <f>Data!AE11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="Z3">
         <f>Data!AF11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AA3">
         <f>Data!AG11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AB3">
         <f>Data!AH11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AC3">
         <f>Data!AI11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AD3">
         <f>Data!AJ11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AE3">
         <f>Data!AK11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
       <c r="AF3">
         <f>Data!AL11</f>
-        <v>3.2803950897637999E-3</v>
+        <v>3.2380317148955899E-3</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -26137,127 +26150,127 @@
       </c>
       <c r="B5">
         <f>Data!H13</f>
-        <v>0.59151755489837199</v>
+        <v>0.58713757439567404</v>
       </c>
       <c r="C5">
         <f>Data!I13</f>
-        <v>0.59151755489837199</v>
+        <v>0.58713757439567404</v>
       </c>
       <c r="D5">
         <f>Data!J13</f>
-        <v>0.59031765788952895</v>
+        <v>0.58625646954423505</v>
       </c>
       <c r="E5">
         <f>Data!K13</f>
-        <v>0.58983194859159405</v>
+        <v>0.58587879933822895</v>
       </c>
       <c r="F5">
         <f>Data!L13</f>
-        <v>0.589580073239939</v>
+        <v>0.58568402014887</v>
       </c>
       <c r="G5">
         <f>Data!M13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="H5">
         <f>Data!N13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="I5">
         <f>Data!O13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="J5">
         <f>Data!P13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="K5">
         <f>Data!Q13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="L5">
         <f>Data!R13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="M5">
         <f>Data!S13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="N5">
         <f>Data!T13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="O5">
         <f>Data!U13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="P5">
         <f>Data!V13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="Q5">
         <f>Data!W13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="R5">
         <f>Data!X13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="S5">
         <f>Data!Y13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="T5">
         <f>Data!Z13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="U5">
         <f>Data!AA13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="V5">
         <f>Data!AB13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="W5">
         <f>Data!AC13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="X5">
         <f>Data!AD13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="Y5">
         <f>Data!AE13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="Z5">
         <f>Data!AF13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AA5">
         <f>Data!AG13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AB5">
         <f>Data!AH13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AC5">
         <f>Data!AI13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AD5">
         <f>Data!AJ13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AE5">
         <f>Data!AK13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
       <c r="AF5">
         <f>Data!AL13</f>
-        <v>0.58834597467789096</v>
+        <v>0.58477756179805596</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -26266,127 +26279,127 @@
       </c>
       <c r="B6">
         <f>Data!H14</f>
-        <v>0.356961080621581</v>
+        <v>3.0097006982601999E-2</v>
       </c>
       <c r="C6">
         <f>Data!I14</f>
-        <v>0.356961080621581</v>
+        <v>3.0097006982601999E-2</v>
       </c>
       <c r="D6">
         <f>Data!J14</f>
-        <v>0.46266979168123801</v>
+        <v>2.1911439020317398E-2</v>
       </c>
       <c r="E6">
         <f>Data!K14</f>
-        <v>0.68107773418921602</v>
+        <v>2.0681798718551799E-2</v>
       </c>
       <c r="F6">
         <f>Data!L14</f>
-        <v>1.1492319563763</v>
+        <v>1.91330462605762E-2</v>
       </c>
       <c r="G6">
         <f>Data!M14</f>
-        <v>1.4827841473737</v>
+        <v>2.67214247564647E-2</v>
       </c>
       <c r="H6">
         <f>Data!N14</f>
-        <v>1.5862273178989601</v>
+        <v>3.097713980517176E-2</v>
       </c>
       <c r="I6">
         <f>Data!O14</f>
-        <v>1.6896704884242202</v>
+        <v>3.5232854853878823E-2</v>
       </c>
       <c r="J6">
         <f>Data!P14</f>
-        <v>1.7931136589494803</v>
+        <v>3.9488569902585882E-2</v>
       </c>
       <c r="K6">
         <f>Data!Q14</f>
-        <v>1.8965568294747404</v>
+        <v>4.3744284951292942E-2</v>
       </c>
       <c r="L6">
         <f>Data!R14</f>
-        <v>2</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="M6">
         <f>Data!S14</f>
-        <v>2</v>
+        <v>5.2400000000000002E-2</v>
       </c>
       <c r="N6">
         <f>Data!T14</f>
-        <v>2</v>
+        <v>5.6800000000000003E-2</v>
       </c>
       <c r="O6">
         <f>Data!U14</f>
-        <v>2</v>
+        <v>6.1200000000000004E-2</v>
       </c>
       <c r="P6">
         <f>Data!V14</f>
-        <v>2</v>
+        <v>6.5600000000000006E-2</v>
       </c>
       <c r="Q6">
         <f>Data!W14</f>
-        <v>2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="R6">
         <f>Data!X14</f>
-        <v>2</v>
+        <v>7.46E-2</v>
       </c>
       <c r="S6">
         <f>Data!Y14</f>
-        <v>2</v>
+        <v>7.9199999999999993E-2</v>
       </c>
       <c r="T6">
         <f>Data!Z14</f>
-        <v>2</v>
+        <v>8.3799999999999986E-2</v>
       </c>
       <c r="U6">
         <f>Data!AA14</f>
-        <v>2</v>
+        <v>8.8399999999999979E-2</v>
       </c>
       <c r="V6">
         <f>Data!AB14</f>
-        <v>2</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="W6">
         <f>Data!AC14</f>
-        <v>2</v>
+        <v>0.1024</v>
       </c>
       <c r="X6">
         <f>Data!AD14</f>
-        <v>2</v>
+        <v>0.11180000000000001</v>
       </c>
       <c r="Y6">
         <f>Data!AE14</f>
-        <v>2</v>
+        <v>0.12120000000000002</v>
       </c>
       <c r="Z6">
         <f>Data!AF14</f>
-        <v>2</v>
+        <v>0.13060000000000002</v>
       </c>
       <c r="AA6">
         <f>Data!AG14</f>
-        <v>2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AB6">
         <f>Data!AH14</f>
-        <v>2</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="AC6">
         <f>Data!AI14</f>
-        <v>2</v>
+        <v>0.188</v>
       </c>
       <c r="AD6">
         <f>Data!AJ14</f>
-        <v>2</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="AE6">
         <f>Data!AK14</f>
-        <v>2</v>
+        <v>0.23599999999999999</v>
       </c>
       <c r="AF6">
         <f>Data!AL14</f>
-        <v>2</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="7" spans="1:32">
@@ -26395,127 +26408,127 @@
       </c>
       <c r="B7">
         <f>Data!H15</f>
-        <v>0.171593660015216</v>
+        <v>0.169435072322971</v>
       </c>
       <c r="C7">
         <f>Data!I15</f>
-        <v>0.171593660015216</v>
+        <v>0.169435072322971</v>
       </c>
       <c r="D7">
         <f>Data!J15</f>
-        <v>0.157380451105636</v>
+        <v>0.15875306561484401</v>
       </c>
       <c r="E7">
         <f>Data!K15</f>
-        <v>0.157105919646333</v>
+        <v>0.158538746497771</v>
       </c>
       <c r="F7">
         <f>Data!L15</f>
-        <v>0.15691361174878399</v>
+        <v>0.15840837270788899</v>
       </c>
       <c r="G7">
         <f>Data!M15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="H7">
         <f>Data!N15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="I7">
         <f>Data!O15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="J7">
         <f>Data!P15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="K7">
         <f>Data!Q15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="L7">
         <f>Data!R15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="M7">
         <f>Data!S15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="N7">
         <f>Data!T15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="O7">
         <f>Data!U15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="P7">
         <f>Data!V15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="Q7">
         <f>Data!W15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="R7">
         <f>Data!X15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="S7">
         <f>Data!Y15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="T7">
         <f>Data!Z15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="U7">
         <f>Data!AA15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="V7">
         <f>Data!AB15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="W7">
         <f>Data!AC15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="X7">
         <f>Data!AD15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="Y7">
         <f>Data!AE15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="Z7">
         <f>Data!AF15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AA7">
         <f>Data!AG15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AB7">
         <f>Data!AH15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AC7">
         <f>Data!AI15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AD7">
         <f>Data!AJ15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AE7">
         <f>Data!AK15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
       <c r="AF7">
         <f>Data!AL15</f>
-        <v>0.15633667860209499</v>
+        <v>0.15795852186818499</v>
       </c>
     </row>
     <row r="8" spans="1:32">
@@ -26524,127 +26537,127 @@
       </c>
       <c r="B8">
         <f>Data!H16</f>
-        <v>1.8305978574742698E-2</v>
+        <v>1.5971754362172401E-2</v>
       </c>
       <c r="C8">
         <f>Data!I16</f>
-        <v>1.8305978574742698E-2</v>
+        <v>1.5971754362172401E-2</v>
       </c>
       <c r="D8">
         <f>Data!J16</f>
-        <v>1.9637350115763199E-2</v>
+        <v>1.7435929211407498E-2</v>
       </c>
       <c r="E8">
         <f>Data!K16</f>
-        <v>8.5168289481052303E-3</v>
+        <v>6.9483671683743999E-3</v>
       </c>
       <c r="F8">
         <f>Data!L16</f>
-        <v>7.5865782984086399E-3</v>
+        <v>4.5730323634844599E-3</v>
       </c>
       <c r="G8">
         <f>Data!M16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="H8">
         <f>Data!N16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="I8">
         <f>Data!O16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="J8">
         <f>Data!P16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="K8">
         <f>Data!Q16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="L8">
         <f>Data!R16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="M8">
         <f>Data!S16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="N8">
         <f>Data!T16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="O8">
         <f>Data!U16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="P8">
         <f>Data!V16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="Q8">
         <f>Data!W16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="R8">
         <f>Data!X16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="S8">
         <f>Data!Y16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="T8">
         <f>Data!Z16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="U8">
         <f>Data!AA16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="V8">
         <f>Data!AB16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="W8">
         <f>Data!AC16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="X8">
         <f>Data!AD16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="Y8">
         <f>Data!AE16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="Z8">
         <f>Data!AF16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AA8">
         <f>Data!AG16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AB8">
         <f>Data!AH16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AC8">
         <f>Data!AI16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AD8">
         <f>Data!AJ16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AE8">
         <f>Data!AK16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
       <c r="AF8">
         <f>Data!AL16</f>
-        <v>1.72086386734626E-2</v>
+        <v>9.4692125755478501E-3</v>
       </c>
     </row>
   </sheetData>
@@ -26659,12 +26672,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29">
+    <row r="1" spans="1:32" ht="45">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -27708,12 +27721,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29">
+    <row r="1" spans="1:32" ht="45">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -28757,12 +28770,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="29">
+    <row r="1" spans="1:32" ht="45">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -8,28 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48DA200-CA56-4299-8059-9F93E57F79B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3C9C14-9940-445D-BC30-CC5F930CFE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="1320" windowWidth="24105" windowHeight="13785" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27810" yWindow="1095" windowWidth="27045" windowHeight="14940" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="SYVbT-passenger" sheetId="6" r:id="rId2"/>
     <sheet name="SYVbT-freight" sheetId="19" r:id="rId3"/>
-    <sheet name="recalculated_shareweights" sheetId="20" r:id="rId4"/>
-    <sheet name="Data" sheetId="3" r:id="rId5"/>
-    <sheet name="TTS-LDVs-psgr" sheetId="2" r:id="rId6"/>
-    <sheet name="TTS-LDVs-frgt" sheetId="8" r:id="rId7"/>
-    <sheet name="TTS-HDVs-psgr" sheetId="9" r:id="rId8"/>
-    <sheet name="TTS-HDVs-frgt" sheetId="10" r:id="rId9"/>
-    <sheet name="TTS-aircraft-psgr" sheetId="11" r:id="rId10"/>
-    <sheet name="TTS-aircraft-frgt" sheetId="12" r:id="rId11"/>
-    <sheet name="TTS-rail-psgr" sheetId="13" r:id="rId12"/>
-    <sheet name="TTS-rail-frgt" sheetId="14" r:id="rId13"/>
-    <sheet name="TTS-ships-psgr" sheetId="15" r:id="rId14"/>
-    <sheet name="TTS-ships-frgt" sheetId="16" r:id="rId15"/>
-    <sheet name="TTS-motorbikes-psgr" sheetId="17" r:id="rId16"/>
-    <sheet name="TTS-motorbikes-frgt" sheetId="18" r:id="rId17"/>
+    <sheet name="Sheet1" sheetId="21" r:id="rId4"/>
+    <sheet name="recalculated_shareweights" sheetId="20" r:id="rId5"/>
+    <sheet name="Data" sheetId="3" r:id="rId6"/>
+    <sheet name="TTS-LDVs-psgr" sheetId="2" r:id="rId7"/>
+    <sheet name="TTS-LDVs-frgt" sheetId="8" r:id="rId8"/>
+    <sheet name="TTS-HDVs-psgr" sheetId="9" r:id="rId9"/>
+    <sheet name="TTS-HDVs-frgt" sheetId="10" r:id="rId10"/>
+    <sheet name="TTS-aircraft-psgr" sheetId="11" r:id="rId11"/>
+    <sheet name="TTS-aircraft-frgt" sheetId="12" r:id="rId12"/>
+    <sheet name="TTS-rail-psgr" sheetId="13" r:id="rId13"/>
+    <sheet name="TTS-rail-frgt" sheetId="14" r:id="rId14"/>
+    <sheet name="TTS-ships-psgr" sheetId="15" r:id="rId15"/>
+    <sheet name="TTS-ships-frgt" sheetId="16" r:id="rId16"/>
+    <sheet name="TTS-motorbikes-psgr" sheetId="17" r:id="rId17"/>
+    <sheet name="TTS-motorbikes-frgt" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="138">
   <si>
     <t>Source:</t>
   </si>
@@ -386,6 +387,84 @@
   <si>
     <t>indicates value hardcoded during calibration</t>
   </si>
+  <si>
+    <t>Time (Year)</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,passenger,battery electric vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,passenger,natural gas vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,passenger,gasoline vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,passenger,diesel vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,passenger,plugin hybrid vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,passenger,LPG vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,passenger,hydrogen vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,freight,battery electric vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,freight,natural gas vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,freight,gasoline vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,freight,diesel vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,freight,plugin hybrid vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,freight,LPG vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t>NPV of Lifetime Vehicle Cost[rail,freight,hydrogen vehicle] : NoSettings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      TTS Transportation Technology Shareweights[Vehicle Type,Cargo Type,Vehicle Technology</t>
+  </si>
+  <si>
+    <t>]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      * exp(MAX(1, NPV of Lifetime Vehicle Cost[Vehicle Type,Cargo Type,Vehicle Technology</t>
+  </si>
+  <si>
+    <t>]* Vehicle Allocation Unit Correction)/1e+06*TTLE Transportation Technology Logit Exponents</t>
+  </si>
+  <si>
+    <t>[Vehicle Type,Cargo Type])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      SUM(TTS Transportation Technology Shareweights[Vehicle Type,Cargo Type,Vehicle Technology</t>
+  </si>
+  <si>
+    <t>!]</t>
+  </si>
+  <si>
+    <t>!]* Vehicle Allocation Unit Correction)/1e+06*TTLE Transportation Technology Logit Exponents</t>
+  </si>
 </sst>
 </file>
 
@@ -650,7 +729,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -701,6 +780,7 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -871,34 +951,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0" formatCode="0.0000">
-                  <c:v>7.5738458244009904E-2</c:v>
+                  <c:v>7.3490200174101794E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.5738458244009904E-2</c:v>
+                  <c:v>7.3490200174101794E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.16254791306372199</c:v>
+                  <c:v>0.157825313074512</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.13456250619976501</c:v>
+                  <c:v>0.13005309903783399</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.17887325579206301</c:v>
+                  <c:v>0.17042213170193199</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.28035657357026</c:v>
+                  <c:v>0.26665968836382897</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.32028525885620801</c:v>
+                  <c:v>0.30932775069106316</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.36021394414215602</c:v>
+                  <c:v>0.35199581301829735</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.40014262942810402</c:v>
+                  <c:v>0.39466387534553155</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.44007131471405203</c:v>
+                  <c:v>0.43733193767276574</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.48</c:v>
@@ -1097,97 +1177,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0" formatCode="0.0000">
-                  <c:v>3.3111542696076198E-3</c:v>
+                  <c:v>3.3619455883161201E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.3111542696076198E-3</c:v>
+                  <c:v>3.3619455883161201E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.18875302069616E-3</c:v>
+                  <c:v>3.2366567758692999E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.2416232692108801E-3</c:v>
+                  <c:v>3.3102715104686301E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.2401040027916599E-3</c:v>
+                  <c:v>3.31078535598989E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>3.2380317148955899E-3</c:v>
+                  <c:v>3.30901198145427E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1549,97 +1629,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0" formatCode="0.0000">
-                  <c:v>0.58713757439567404</c:v>
+                  <c:v>0.59258194130892095</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.58713757439567404</c:v>
+                  <c:v>0.59258194130892095</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.58625646954423505</c:v>
+                  <c:v>0.59256250147626899</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.58587879933822895</c:v>
+                  <c:v>0.592196165783894</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.58568402014887</c:v>
+                  <c:v>0.592014678526816</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.58477756179805596</c:v>
+                  <c:v>0.59122138352735099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1775,34 +1855,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0" formatCode="0.0000">
-                  <c:v>3.0097006982601999E-2</c:v>
+                  <c:v>2.68592624324243E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.0097006982601999E-2</c:v>
+                  <c:v>2.68592624324243E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.1911439020317398E-2</c:v>
+                  <c:v>1.94058745124292E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.0681798718551799E-2</c:v>
+                  <c:v>1.8171220012969998E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.91330462605762E-2</c:v>
+                  <c:v>1.64374786444835E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.67214247564647E-2</c:v>
+                  <c:v>2.2877517710931699E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.097713980517176E-2</c:v>
+                  <c:v>2.7902014168745361E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.5232854853878823E-2</c:v>
+                  <c:v>3.2926510626559019E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.9488569902585882E-2</c:v>
+                  <c:v>3.7951007084372677E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.3744284951292942E-2</c:v>
+                  <c:v>4.2975503542186336E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>4.8000000000000001E-2</c:v>
@@ -2001,97 +2081,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0" formatCode="0.0000">
-                  <c:v>0.169435072322971</c:v>
+                  <c:v>0.171228650249552</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.169435072322971</c:v>
+                  <c:v>0.171228650249552</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.15875306561484401</c:v>
+                  <c:v>0.160575453689589</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.158538746497771</c:v>
+                  <c:v>0.16035867432016401</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.15840837270788899</c:v>
+                  <c:v>0.16022472098401899</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.15795852186818499</c:v>
+                  <c:v>0.15979463806628899</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2229,97 +2309,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0" formatCode="0.0000">
-                  <c:v>1.5971754362172401E-2</c:v>
+                  <c:v>1.3775185340645301E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.5971754362172401E-2</c:v>
+                  <c:v>1.3775185340645301E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.7435929211407498E-2</c:v>
+                  <c:v>1.50499244982964E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.9483671683743999E-3</c:v>
+                  <c:v>5.9981476236627097E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.5730323634844599E-3</c:v>
+                  <c:v>3.9475989042041899E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9.4692125755478501E-3</c:v>
+                  <c:v>8.1683077230845901E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3109,16 +3189,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>333000</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>86471</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>469071</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>59257</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>459441</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>78440</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>595512</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>51226</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3800,6 +3880,1055 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AF8"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" ht="45">
+      <c r="A1" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1">
+        <f>Data!H9</f>
+        <v>2020</v>
+      </c>
+      <c r="C1">
+        <f>Data!I9</f>
+        <v>2021</v>
+      </c>
+      <c r="D1">
+        <f>Data!J9</f>
+        <v>2022</v>
+      </c>
+      <c r="E1">
+        <f>Data!K9</f>
+        <v>2023</v>
+      </c>
+      <c r="F1">
+        <f>Data!L9</f>
+        <v>2024</v>
+      </c>
+      <c r="G1">
+        <f>Data!M9</f>
+        <v>2025</v>
+      </c>
+      <c r="H1">
+        <f>Data!N9</f>
+        <v>2026</v>
+      </c>
+      <c r="I1">
+        <f>Data!O9</f>
+        <v>2027</v>
+      </c>
+      <c r="J1">
+        <f>Data!P9</f>
+        <v>2028</v>
+      </c>
+      <c r="K1">
+        <f>Data!Q9</f>
+        <v>2029</v>
+      </c>
+      <c r="L1">
+        <f>Data!R9</f>
+        <v>2030</v>
+      </c>
+      <c r="M1">
+        <f>Data!S9</f>
+        <v>2031</v>
+      </c>
+      <c r="N1">
+        <f>Data!T9</f>
+        <v>2032</v>
+      </c>
+      <c r="O1">
+        <f>Data!U9</f>
+        <v>2033</v>
+      </c>
+      <c r="P1">
+        <f>Data!V9</f>
+        <v>2034</v>
+      </c>
+      <c r="Q1">
+        <f>Data!W9</f>
+        <v>2035</v>
+      </c>
+      <c r="R1">
+        <f>Data!X9</f>
+        <v>2036</v>
+      </c>
+      <c r="S1">
+        <f>Data!Y9</f>
+        <v>2037</v>
+      </c>
+      <c r="T1">
+        <f>Data!Z9</f>
+        <v>2038</v>
+      </c>
+      <c r="U1">
+        <f>Data!AA9</f>
+        <v>2039</v>
+      </c>
+      <c r="V1">
+        <f>Data!AB9</f>
+        <v>2040</v>
+      </c>
+      <c r="W1">
+        <f>Data!AC9</f>
+        <v>2041</v>
+      </c>
+      <c r="X1">
+        <f>Data!AD9</f>
+        <v>2042</v>
+      </c>
+      <c r="Y1">
+        <f>Data!AE9</f>
+        <v>2043</v>
+      </c>
+      <c r="Z1">
+        <f>Data!AF9</f>
+        <v>2044</v>
+      </c>
+      <c r="AA1">
+        <f>Data!AG9</f>
+        <v>2045</v>
+      </c>
+      <c r="AB1">
+        <f>Data!AH9</f>
+        <v>2046</v>
+      </c>
+      <c r="AC1">
+        <f>Data!AI9</f>
+        <v>2047</v>
+      </c>
+      <c r="AD1">
+        <f>Data!AJ9</f>
+        <v>2048</v>
+      </c>
+      <c r="AE1">
+        <f>Data!AK9</f>
+        <v>2049</v>
+      </c>
+      <c r="AF1">
+        <f>Data!AL9</f>
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>Data!H31</f>
+        <v>5.3709944550863111E-3</v>
+      </c>
+      <c r="C2">
+        <f>Data!I31</f>
+        <v>1.2678659059418999E-2</v>
+      </c>
+      <c r="D2">
+        <f>Data!J31</f>
+        <v>1.5184585150040118E-2</v>
+      </c>
+      <c r="E2">
+        <f>Data!K31</f>
+        <v>1.8526638938495932E-2</v>
+      </c>
+      <c r="F2">
+        <f>Data!L31</f>
+        <v>2.2965536431060245E-2</v>
+      </c>
+      <c r="G2">
+        <f>Data!M31</f>
+        <v>2.8829206942005366E-2</v>
+      </c>
+      <c r="H2">
+        <f>Data!N31</f>
+        <v>3.651944293738426E-2</v>
+      </c>
+      <c r="I2">
+        <f>Data!O31</f>
+        <v>4.6510622610364066E-2</v>
+      </c>
+      <c r="J2">
+        <f>Data!P31</f>
+        <v>5.933344663118359E-2</v>
+      </c>
+      <c r="K2">
+        <f>Data!Q31</f>
+        <v>7.5534645622301611E-2</v>
+      </c>
+      <c r="L2">
+        <f>Data!R31</f>
+        <v>9.5603949881434322E-2</v>
+      </c>
+      <c r="M2">
+        <f>Data!S31</f>
+        <v>0.11986535060126081</v>
+      </c>
+      <c r="N2">
+        <f>Data!T31</f>
+        <v>0.1483437545239433</v>
+      </c>
+      <c r="O2">
+        <f>Data!U31</f>
+        <v>0.18063966332773254</v>
+      </c>
+      <c r="P2">
+        <f>Data!V31</f>
+        <v>0.21586406916673176</v>
+      </c>
+      <c r="Q2">
+        <f>Data!W31</f>
+        <v>0.25268549722754313</v>
+      </c>
+      <c r="R2">
+        <f>Data!X31</f>
+        <v>0.28950692528835459</v>
+      </c>
+      <c r="S2">
+        <f>Data!Y31</f>
+        <v>0.32473133112735375</v>
+      </c>
+      <c r="T2">
+        <f>Data!Z31</f>
+        <v>0.35702723993114299</v>
+      </c>
+      <c r="U2">
+        <f>Data!AA31</f>
+        <v>0.38550564385382546</v>
+      </c>
+      <c r="V2">
+        <f>Data!AB31</f>
+        <v>0.40976704457365198</v>
+      </c>
+      <c r="W2">
+        <f>Data!AC31</f>
+        <v>0.42983634883278476</v>
+      </c>
+      <c r="X2">
+        <f>Data!AD31</f>
+        <v>0.4460375478239027</v>
+      </c>
+      <c r="Y2">
+        <f>Data!AE31</f>
+        <v>0.45886037184472228</v>
+      </c>
+      <c r="Z2">
+        <f>Data!AF31</f>
+        <v>0.46885155151770208</v>
+      </c>
+      <c r="AA2">
+        <f>Data!AG31</f>
+        <v>0.47654178751308102</v>
+      </c>
+      <c r="AB2">
+        <f>Data!AH31</f>
+        <v>0.48240545802402607</v>
+      </c>
+      <c r="AC2">
+        <f>Data!AI31</f>
+        <v>0.48684435551659033</v>
+      </c>
+      <c r="AD2">
+        <f>Data!AJ31</f>
+        <v>0.4901864093050462</v>
+      </c>
+      <c r="AE2">
+        <f>Data!AK31</f>
+        <v>0.49269233539566731</v>
+      </c>
+      <c r="AF2">
+        <f>Data!AL31</f>
+        <v>0.4945655394926507</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>Data!H32</f>
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f>Data!I32</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>Data!J32</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f>Data!K32</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f>Data!L32</f>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f>Data!M32</f>
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <f>Data!N32</f>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f>Data!O32</f>
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f>Data!P32</f>
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <f>Data!Q32</f>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f>Data!R32</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f>Data!S32</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f>Data!T32</f>
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <f>Data!U32</f>
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <f>Data!V32</f>
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <f>Data!W32</f>
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <f>Data!X32</f>
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <f>Data!Y32</f>
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <f>Data!Z32</f>
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <f>Data!AA32</f>
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <f>Data!AB32</f>
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <f>Data!AC32</f>
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <f>Data!AD32</f>
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <f>Data!AE32</f>
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <f>Data!AF32</f>
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <f>Data!AG32</f>
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <f>Data!AH32</f>
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <f>Data!AI32</f>
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <f>Data!AJ32</f>
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <f>Data!AK32</f>
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <f>Data!AL32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f>Data!H33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="C4">
+        <f>Data!I33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="D4">
+        <f>Data!J33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="E4">
+        <f>Data!K33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="F4">
+        <f>Data!L33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="G4">
+        <f>Data!M33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="H4">
+        <f>Data!N33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="I4">
+        <f>Data!O33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="J4">
+        <f>Data!P33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="K4">
+        <f>Data!Q33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="L4">
+        <f>Data!R33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="M4">
+        <f>Data!S33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="N4">
+        <f>Data!T33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="O4">
+        <f>Data!U33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="P4">
+        <f>Data!V33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="Q4">
+        <f>Data!W33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="R4">
+        <f>Data!X33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="S4">
+        <f>Data!Y33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="T4">
+        <f>Data!Z33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="U4">
+        <f>Data!AA33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="V4">
+        <f>Data!AB33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="W4">
+        <f>Data!AC33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="X4">
+        <f>Data!AD33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="Y4">
+        <f>Data!AE33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="Z4">
+        <f>Data!AF33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="AA4">
+        <f>Data!AG33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="AB4">
+        <f>Data!AH33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="AC4">
+        <f>Data!AI33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="AD4">
+        <f>Data!AJ33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="AE4">
+        <f>Data!AK33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+      <c r="AF4">
+        <f>Data!AL33</f>
+        <v>1.9195530379555355E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f>Data!H34</f>
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <f>Data!I34</f>
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <f>Data!J34</f>
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <f>Data!K34</f>
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <f>Data!L34</f>
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <f>Data!M34</f>
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <f>Data!N34</f>
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <f>Data!O34</f>
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <f>Data!P34</f>
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <f>Data!Q34</f>
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <f>Data!R34</f>
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <f>Data!S34</f>
+        <v>3</v>
+      </c>
+      <c r="N5">
+        <f>Data!T34</f>
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <f>Data!U34</f>
+        <v>3</v>
+      </c>
+      <c r="P5">
+        <f>Data!V34</f>
+        <v>3</v>
+      </c>
+      <c r="Q5">
+        <f>Data!W34</f>
+        <v>3</v>
+      </c>
+      <c r="R5">
+        <f>Data!X34</f>
+        <v>3</v>
+      </c>
+      <c r="S5">
+        <f>Data!Y34</f>
+        <v>3</v>
+      </c>
+      <c r="T5">
+        <f>Data!Z34</f>
+        <v>3</v>
+      </c>
+      <c r="U5">
+        <f>Data!AA34</f>
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <f>Data!AB34</f>
+        <v>3</v>
+      </c>
+      <c r="W5">
+        <f>Data!AC34</f>
+        <v>3</v>
+      </c>
+      <c r="X5">
+        <f>Data!AD34</f>
+        <v>3</v>
+      </c>
+      <c r="Y5">
+        <f>Data!AE34</f>
+        <v>3</v>
+      </c>
+      <c r="Z5">
+        <f>Data!AF34</f>
+        <v>3</v>
+      </c>
+      <c r="AA5">
+        <f>Data!AG34</f>
+        <v>3</v>
+      </c>
+      <c r="AB5">
+        <f>Data!AH34</f>
+        <v>3</v>
+      </c>
+      <c r="AC5">
+        <f>Data!AI34</f>
+        <v>3</v>
+      </c>
+      <c r="AD5">
+        <f>Data!AJ34</f>
+        <v>3</v>
+      </c>
+      <c r="AE5">
+        <f>Data!AK34</f>
+        <v>3</v>
+      </c>
+      <c r="AF5">
+        <f>Data!AL34</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f>Data!H35</f>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <f>Data!I35</f>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f>Data!J35</f>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f>Data!K35</f>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f>Data!L35</f>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f>Data!M35</f>
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f>Data!N35</f>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f>Data!O35</f>
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f>Data!P35</f>
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f>Data!Q35</f>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f>Data!R35</f>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f>Data!S35</f>
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f>Data!T35</f>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f>Data!U35</f>
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <f>Data!V35</f>
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <f>Data!W35</f>
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <f>Data!X35</f>
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <f>Data!Y35</f>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <f>Data!Z35</f>
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <f>Data!AA35</f>
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <f>Data!AB35</f>
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <f>Data!AC35</f>
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <f>Data!AD35</f>
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <f>Data!AE35</f>
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <f>Data!AF35</f>
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <f>Data!AG35</f>
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <f>Data!AH35</f>
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <f>Data!AI35</f>
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <f>Data!AJ35</f>
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <f>Data!AK35</f>
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <f>Data!AL35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7">
+        <f>Data!H36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="C7">
+        <f>Data!I36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="D7">
+        <f>Data!J36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="E7">
+        <f>Data!K36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="F7">
+        <f>Data!L36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="G7">
+        <f>Data!M36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="H7">
+        <f>Data!N36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="I7">
+        <f>Data!O36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="J7">
+        <f>Data!P36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="K7">
+        <f>Data!Q36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="L7">
+        <f>Data!R36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="M7">
+        <f>Data!S36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="N7">
+        <f>Data!T36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="O7">
+        <f>Data!U36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="P7">
+        <f>Data!V36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="Q7">
+        <f>Data!W36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="R7">
+        <f>Data!X36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="S7">
+        <f>Data!Y36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="T7">
+        <f>Data!Z36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="U7">
+        <f>Data!AA36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="V7">
+        <f>Data!AB36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="W7">
+        <f>Data!AC36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="X7">
+        <f>Data!AD36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="Y7">
+        <f>Data!AE36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="Z7">
+        <f>Data!AF36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="AA7">
+        <f>Data!AG36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="AB7">
+        <f>Data!AH36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="AC7">
+        <f>Data!AI36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="AD7">
+        <f>Data!AJ36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="AE7">
+        <f>Data!AK36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+      <c r="AF7">
+        <f>Data!AL36</f>
+        <v>4.2398960612661157E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8">
+        <f>Data!H37</f>
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <f>Data!I37</f>
+        <v>6.2640358785329186E-4</v>
+      </c>
+      <c r="D8">
+        <f>Data!J37</f>
+        <v>8.4120834136230764E-4</v>
+      </c>
+      <c r="E8">
+        <f>Data!K37</f>
+        <v>1.1276848830807375E-3</v>
+      </c>
+      <c r="F8">
+        <f>Data!L37</f>
+        <v>1.5081814529160165E-3</v>
+      </c>
+      <c r="G8">
+        <f>Data!M37</f>
+        <v>2.0108077288767171E-3</v>
+      </c>
+      <c r="H8">
+        <f>Data!N37</f>
+        <v>2.6700048431076819E-3</v>
+      </c>
+      <c r="I8">
+        <f>Data!O37</f>
+        <v>3.5264358826946353E-3</v>
+      </c>
+      <c r="J8">
+        <f>Data!P37</f>
+        <v>4.6255918248393289E-3</v>
+      </c>
+      <c r="K8">
+        <f>Data!Q37</f>
+        <v>6.0143377135798244E-3</v>
+      </c>
+      <c r="L8">
+        <f>Data!R37</f>
+        <v>7.7346525986097831E-3</v>
+      </c>
+      <c r="M8">
+        <f>Data!S37</f>
+        <v>9.8143085872323659E-3</v>
+      </c>
+      <c r="N8">
+        <f>Data!T37</f>
+        <v>1.2255440653272574E-2</v>
+      </c>
+      <c r="O8">
+        <f>Data!U37</f>
+        <v>1.5023804315677364E-2</v>
+      </c>
+      <c r="P8">
+        <f>Data!V37</f>
+        <v>1.8043194968125682E-2</v>
+      </c>
+      <c r="Q8">
+        <f>Data!W37</f>
+        <v>2.1199480306330579E-2</v>
+      </c>
+      <c r="R8">
+        <f>Data!X37</f>
+        <v>2.4355765644535475E-2</v>
+      </c>
+      <c r="S8">
+        <f>Data!Y37</f>
+        <v>2.7375156296983789E-2</v>
+      </c>
+      <c r="T8">
+        <f>Data!Z37</f>
+        <v>3.014351995938858E-2</v>
+      </c>
+      <c r="U8">
+        <f>Data!AA37</f>
+        <v>3.258465202542879E-2</v>
+      </c>
+      <c r="V8">
+        <f>Data!AB37</f>
+        <v>3.4664308014051376E-2</v>
+      </c>
+      <c r="W8">
+        <f>Data!AC37</f>
+        <v>3.6384622899081336E-2</v>
+      </c>
+      <c r="X8">
+        <f>Data!AD37</f>
+        <v>3.777336878782183E-2</v>
+      </c>
+      <c r="Y8">
+        <f>Data!AE37</f>
+        <v>3.8872524729966523E-2</v>
+      </c>
+      <c r="Z8">
+        <f>Data!AF37</f>
+        <v>3.972895576955348E-2</v>
+      </c>
+      <c r="AA8">
+        <f>Data!AG37</f>
+        <v>4.0388152883784445E-2</v>
+      </c>
+      <c r="AB8">
+        <f>Data!AH37</f>
+        <v>4.0890779159745143E-2</v>
+      </c>
+      <c r="AC8">
+        <f>Data!AI37</f>
+        <v>4.127127572958042E-2</v>
+      </c>
+      <c r="AD8">
+        <f>Data!AJ37</f>
+        <v>4.1557752271298855E-2</v>
+      </c>
+      <c r="AE8">
+        <f>Data!AK37</f>
+        <v>4.1772557024807866E-2</v>
+      </c>
+      <c r="AF8">
+        <f>Data!AL37</f>
+        <v>4.1933125664813074E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -4848,7 +5977,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -5897,7 +7026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -6043,127 +7172,127 @@
       </c>
       <c r="B2">
         <f>Data!H52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <f>Data!I52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <f>Data!J52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <f>Data!K52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <f>Data!L52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <f>Data!M52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <f>Data!N52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <f>Data!O52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <f>Data!P52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <f>Data!Q52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <f>Data!R52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <f>Data!S52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="N2">
         <f>Data!T52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="O2">
         <f>Data!U52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="P2">
         <f>Data!V52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="Q2">
         <f>Data!W52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="R2">
         <f>Data!X52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="S2">
         <f>Data!Y52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="T2">
         <f>Data!Z52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="U2">
         <f>Data!AA52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="V2">
         <f>Data!AB52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="W2">
         <f>Data!AC52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="X2">
         <f>Data!AD52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="Y2">
         <f>Data!AE52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="Z2">
         <f>Data!AF52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AA2">
         <f>Data!AG52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AB2">
         <f>Data!AH52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AC2">
         <f>Data!AI52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AD2">
         <f>Data!AJ52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AE2">
         <f>Data!AK52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AF2">
         <f>Data!AL52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -6430,127 +7559,127 @@
       </c>
       <c r="B5">
         <f>Data!H55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="C5">
         <f>Data!I55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="D5">
         <f>Data!J55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="E5">
         <f>Data!K55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="F5">
         <f>Data!L55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="G5">
         <f>Data!M55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="H5">
         <f>Data!N55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="I5">
         <f>Data!O55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="J5">
         <f>Data!P55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="K5">
         <f>Data!Q55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="L5">
         <f>Data!R55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="M5">
         <f>Data!S55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="N5">
         <f>Data!T55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="O5">
         <f>Data!U55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="P5">
         <f>Data!V55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="Q5">
         <f>Data!W55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="R5">
         <f>Data!X55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="S5">
         <f>Data!Y55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="T5">
         <f>Data!Z55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="U5">
         <f>Data!AA55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="V5">
         <f>Data!AB55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="W5">
         <f>Data!AC55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="X5">
         <f>Data!AD55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="Y5">
         <f>Data!AE55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="Z5">
         <f>Data!AF55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AA5">
         <f>Data!AG55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AB5">
         <f>Data!AH55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AC5">
         <f>Data!AI55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AD5">
         <f>Data!AJ55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AE5">
         <f>Data!AK55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AF5">
         <f>Data!AL55</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -6946,7 +8075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -7092,127 +8221,127 @@
       </c>
       <c r="B2">
         <f>Data!H59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="C2">
         <f>Data!I59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="D2">
         <f>Data!J59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="E2">
         <f>Data!K59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="F2">
         <f>Data!L59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="G2">
         <f>Data!M59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="H2">
         <f>Data!N59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="I2">
         <f>Data!O59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
         <f>Data!P59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="K2">
         <f>Data!Q59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="L2">
         <f>Data!R59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="M2">
         <f>Data!S59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="N2">
         <f>Data!T59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="O2">
         <f>Data!U59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="P2">
         <f>Data!V59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="Q2">
         <f>Data!W59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="R2">
         <f>Data!X59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="S2">
         <f>Data!Y59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="T2">
         <f>Data!Z59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="U2">
         <f>Data!AA59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="V2">
         <f>Data!AB59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="W2">
         <f>Data!AC59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="X2">
         <f>Data!AD59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="Y2">
         <f>Data!AE59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="Z2">
         <f>Data!AF59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AA2">
         <f>Data!AG59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AB2">
         <f>Data!AH59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AC2">
         <f>Data!AI59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AD2">
         <f>Data!AJ59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AE2">
         <f>Data!AK59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AF2">
         <f>Data!AL59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -7479,127 +8608,127 @@
       </c>
       <c r="B5">
         <f>Data!H62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <f>Data!I62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <f>Data!J62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <f>Data!K62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <f>Data!L62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <f>Data!M62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <f>Data!N62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <f>Data!O62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <f>Data!P62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <f>Data!Q62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <f>Data!R62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <f>Data!S62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="N5">
         <f>Data!T62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <f>Data!U62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="P5">
         <f>Data!V62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="Q5">
         <f>Data!W62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="R5">
         <f>Data!X62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="S5">
         <f>Data!Y62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="T5">
         <f>Data!Z62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="U5">
         <f>Data!AA62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="V5">
         <f>Data!AB62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="W5">
         <f>Data!AC62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="X5">
         <f>Data!AD62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="Y5">
         <f>Data!AE62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="Z5">
         <f>Data!AF62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AA5">
         <f>Data!AG62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AB5">
         <f>Data!AH62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AC5">
         <f>Data!AI62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AD5">
         <f>Data!AJ62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AE5">
         <f>Data!AK62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AF5">
         <f>Data!AL62</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -7995,7 +9124,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -9044,7 +10173,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -10093,7 +11222,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -11142,7 +12271,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -12612,6 +13741,1509 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C98A0B0-4AA3-4C7F-A6AE-244E743CFDDD}">
+  <dimension ref="B2:AF35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="74.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:32">
+      <c r="B2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2">
+        <v>2021</v>
+      </c>
+      <c r="D2">
+        <v>2022</v>
+      </c>
+      <c r="E2">
+        <v>2023</v>
+      </c>
+      <c r="F2">
+        <v>2024</v>
+      </c>
+      <c r="G2">
+        <v>2025</v>
+      </c>
+      <c r="H2">
+        <v>2026</v>
+      </c>
+      <c r="I2">
+        <v>2027</v>
+      </c>
+      <c r="J2">
+        <v>2028</v>
+      </c>
+      <c r="K2">
+        <v>2029</v>
+      </c>
+      <c r="L2">
+        <v>2030</v>
+      </c>
+      <c r="M2">
+        <v>2031</v>
+      </c>
+      <c r="N2">
+        <v>2032</v>
+      </c>
+      <c r="O2">
+        <v>2033</v>
+      </c>
+      <c r="P2">
+        <v>2034</v>
+      </c>
+      <c r="Q2">
+        <v>2035</v>
+      </c>
+      <c r="R2">
+        <v>2036</v>
+      </c>
+      <c r="S2">
+        <v>2037</v>
+      </c>
+      <c r="T2">
+        <v>2038</v>
+      </c>
+      <c r="U2">
+        <v>2039</v>
+      </c>
+      <c r="V2">
+        <v>2040</v>
+      </c>
+      <c r="W2">
+        <v>2041</v>
+      </c>
+      <c r="X2">
+        <v>2042</v>
+      </c>
+      <c r="Y2">
+        <v>2043</v>
+      </c>
+      <c r="Z2">
+        <v>2044</v>
+      </c>
+      <c r="AA2">
+        <v>2045</v>
+      </c>
+      <c r="AB2">
+        <v>2046</v>
+      </c>
+      <c r="AC2">
+        <v>2047</v>
+      </c>
+      <c r="AD2">
+        <v>2048</v>
+      </c>
+      <c r="AE2">
+        <v>2049</v>
+      </c>
+      <c r="AF2">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="3" spans="2:32">
+      <c r="B3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="32">
+        <v>49233500</v>
+      </c>
+      <c r="D3" s="32">
+        <v>49235000</v>
+      </c>
+      <c r="E3" s="32">
+        <v>49827200</v>
+      </c>
+      <c r="F3" s="32">
+        <v>53422400</v>
+      </c>
+      <c r="G3" s="32">
+        <v>54626000</v>
+      </c>
+      <c r="H3" s="32">
+        <v>56242500</v>
+      </c>
+      <c r="I3" s="32">
+        <v>55110700</v>
+      </c>
+      <c r="J3" s="32">
+        <v>53945200</v>
+      </c>
+      <c r="K3" s="32">
+        <v>53056900</v>
+      </c>
+      <c r="L3" s="32">
+        <v>52838500</v>
+      </c>
+      <c r="M3" s="32">
+        <v>52446900</v>
+      </c>
+      <c r="N3" s="32">
+        <v>51692900</v>
+      </c>
+      <c r="O3" s="32">
+        <v>53332800</v>
+      </c>
+      <c r="P3" s="32">
+        <v>52977500</v>
+      </c>
+      <c r="Q3" s="32">
+        <v>52958600</v>
+      </c>
+      <c r="R3" s="32">
+        <v>52732200</v>
+      </c>
+      <c r="S3" s="32">
+        <v>54927200</v>
+      </c>
+      <c r="T3" s="32">
+        <v>56761300</v>
+      </c>
+      <c r="U3" s="32">
+        <v>56864400</v>
+      </c>
+      <c r="V3" s="32">
+        <v>56747500</v>
+      </c>
+      <c r="W3" s="32">
+        <v>56851800</v>
+      </c>
+      <c r="X3" s="32">
+        <v>56830700</v>
+      </c>
+      <c r="Y3" s="32">
+        <v>56722200</v>
+      </c>
+      <c r="Z3" s="32">
+        <v>56637500</v>
+      </c>
+      <c r="AA3" s="32">
+        <v>56401400</v>
+      </c>
+      <c r="AB3" s="32">
+        <v>56093800</v>
+      </c>
+      <c r="AC3" s="32">
+        <v>55766000</v>
+      </c>
+      <c r="AD3" s="32">
+        <v>55692800</v>
+      </c>
+      <c r="AE3" s="32">
+        <v>55626600</v>
+      </c>
+      <c r="AF3" s="32">
+        <v>55552800</v>
+      </c>
+    </row>
+    <row r="4" spans="2:32">
+      <c r="B4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="D4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="E4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="F4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="G4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="H4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="I4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="J4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="K4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="L4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="M4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="N4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="O4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="P4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Q4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="R4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="S4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="T4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="U4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="V4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="W4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="X4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Y4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Z4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AA4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AB4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AC4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AD4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AE4" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AF4" s="32">
+        <v>1042500000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:32">
+      <c r="B5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="D5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="E5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="F5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="G5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="H5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="I5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="J5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="K5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="L5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="M5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="N5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="O5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="P5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Q5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="R5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="S5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="T5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="U5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="V5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="W5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="X5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Y5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Z5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AA5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AB5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AC5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AD5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AE5" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AF5" s="32">
+        <v>1042500000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:32">
+      <c r="B6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="32">
+        <v>46244200</v>
+      </c>
+      <c r="D6" s="32">
+        <v>46573700</v>
+      </c>
+      <c r="E6" s="32">
+        <v>46593600</v>
+      </c>
+      <c r="F6" s="32">
+        <v>46612900</v>
+      </c>
+      <c r="G6" s="32">
+        <v>46633700</v>
+      </c>
+      <c r="H6" s="32">
+        <v>46653800</v>
+      </c>
+      <c r="I6" s="32">
+        <v>46675300</v>
+      </c>
+      <c r="J6" s="32">
+        <v>46699700</v>
+      </c>
+      <c r="K6" s="32">
+        <v>46721300</v>
+      </c>
+      <c r="L6" s="32">
+        <v>46743700</v>
+      </c>
+      <c r="M6" s="32">
+        <v>46766100</v>
+      </c>
+      <c r="N6" s="32">
+        <v>46788500</v>
+      </c>
+      <c r="O6" s="32">
+        <v>46816200</v>
+      </c>
+      <c r="P6" s="32">
+        <v>46839500</v>
+      </c>
+      <c r="Q6" s="32">
+        <v>46863400</v>
+      </c>
+      <c r="R6" s="32">
+        <v>46888200</v>
+      </c>
+      <c r="S6" s="32">
+        <v>46913000</v>
+      </c>
+      <c r="T6" s="32">
+        <v>46938500</v>
+      </c>
+      <c r="U6" s="32">
+        <v>46968100</v>
+      </c>
+      <c r="V6" s="32">
+        <v>46994400</v>
+      </c>
+      <c r="W6" s="32">
+        <v>47020800</v>
+      </c>
+      <c r="X6" s="32">
+        <v>47047900</v>
+      </c>
+      <c r="Y6" s="32">
+        <v>47075800</v>
+      </c>
+      <c r="Z6" s="32">
+        <v>47103700</v>
+      </c>
+      <c r="AA6" s="32">
+        <v>47136800</v>
+      </c>
+      <c r="AB6" s="32">
+        <v>47166300</v>
+      </c>
+      <c r="AC6" s="32">
+        <v>47195800</v>
+      </c>
+      <c r="AD6" s="32">
+        <v>47226100</v>
+      </c>
+      <c r="AE6" s="32">
+        <v>47256400</v>
+      </c>
+      <c r="AF6" s="32">
+        <v>47287500</v>
+      </c>
+    </row>
+    <row r="7" spans="2:32">
+      <c r="B7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="D7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="E7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="F7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="G7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="H7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="I7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="J7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="K7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="L7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="M7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="N7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="O7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="P7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Q7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="R7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="S7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="T7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="U7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="V7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="W7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="X7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Y7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Z7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AA7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AB7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AC7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AD7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AE7" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AF7" s="32">
+        <v>1042500000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:32">
+      <c r="B8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="D8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="E8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="F8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="G8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="H8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="I8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="J8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="K8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="L8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="M8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="N8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="O8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="P8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Q8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="R8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="S8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="T8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="U8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="V8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="W8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="X8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Y8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Z8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AA8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AB8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AC8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AD8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AE8" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AF8" s="32">
+        <v>1042500000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:32">
+      <c r="B9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="32">
+        <v>35312800</v>
+      </c>
+      <c r="D9" s="32">
+        <v>35076200</v>
+      </c>
+      <c r="E9" s="32">
+        <v>35025300</v>
+      </c>
+      <c r="F9" s="32">
+        <v>34820700</v>
+      </c>
+      <c r="G9" s="32">
+        <v>34621000</v>
+      </c>
+      <c r="H9" s="32">
+        <v>34427000</v>
+      </c>
+      <c r="I9" s="32">
+        <v>34134300</v>
+      </c>
+      <c r="J9" s="32">
+        <v>33850300</v>
+      </c>
+      <c r="K9" s="32">
+        <v>33598700</v>
+      </c>
+      <c r="L9" s="32">
+        <v>33364700</v>
+      </c>
+      <c r="M9" s="32">
+        <v>33294400</v>
+      </c>
+      <c r="N9" s="32">
+        <v>33238700</v>
+      </c>
+      <c r="O9" s="32">
+        <v>33194300</v>
+      </c>
+      <c r="P9" s="32">
+        <v>33155000</v>
+      </c>
+      <c r="Q9" s="32">
+        <v>33114200</v>
+      </c>
+      <c r="R9" s="32">
+        <v>33070700</v>
+      </c>
+      <c r="S9" s="32">
+        <v>33030700</v>
+      </c>
+      <c r="T9" s="32">
+        <v>32986500</v>
+      </c>
+      <c r="U9" s="32">
+        <v>32950700</v>
+      </c>
+      <c r="V9" s="32">
+        <v>32923500</v>
+      </c>
+      <c r="W9" s="32">
+        <v>32896900</v>
+      </c>
+      <c r="X9" s="32">
+        <v>32873600</v>
+      </c>
+      <c r="Y9" s="32">
+        <v>32853400</v>
+      </c>
+      <c r="Z9" s="32">
+        <v>32831400</v>
+      </c>
+      <c r="AA9" s="32">
+        <v>32812300</v>
+      </c>
+      <c r="AB9" s="32">
+        <v>32797800</v>
+      </c>
+      <c r="AC9" s="32">
+        <v>32787600</v>
+      </c>
+      <c r="AD9" s="32">
+        <v>32777800</v>
+      </c>
+      <c r="AE9" s="32">
+        <v>32768500</v>
+      </c>
+      <c r="AF9" s="32">
+        <v>32759300</v>
+      </c>
+    </row>
+    <row r="10" spans="2:32">
+      <c r="B10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="32">
+        <v>43448100</v>
+      </c>
+      <c r="D10" s="32">
+        <v>43376300</v>
+      </c>
+      <c r="E10" s="32">
+        <v>43602100</v>
+      </c>
+      <c r="F10" s="32">
+        <v>45461100</v>
+      </c>
+      <c r="G10" s="32">
+        <v>45986800</v>
+      </c>
+      <c r="H10" s="32">
+        <v>46712100</v>
+      </c>
+      <c r="I10" s="32">
+        <v>46125100</v>
+      </c>
+      <c r="J10" s="32">
+        <v>45445100</v>
+      </c>
+      <c r="K10" s="32">
+        <v>44915700</v>
+      </c>
+      <c r="L10" s="32">
+        <v>44807100</v>
+      </c>
+      <c r="M10" s="32">
+        <v>44522200</v>
+      </c>
+      <c r="N10" s="32">
+        <v>44076900</v>
+      </c>
+      <c r="O10" s="32">
+        <v>44876200</v>
+      </c>
+      <c r="P10" s="32">
+        <v>44624300</v>
+      </c>
+      <c r="Q10" s="32">
+        <v>44527000</v>
+      </c>
+      <c r="R10" s="32">
+        <v>44418800</v>
+      </c>
+      <c r="S10" s="32">
+        <v>45383800</v>
+      </c>
+      <c r="T10" s="32">
+        <v>46162300</v>
+      </c>
+      <c r="U10" s="32">
+        <v>46108500</v>
+      </c>
+      <c r="V10" s="32">
+        <v>46054200</v>
+      </c>
+      <c r="W10" s="32">
+        <v>46015200</v>
+      </c>
+      <c r="X10" s="32">
+        <v>45919600</v>
+      </c>
+      <c r="Y10" s="32">
+        <v>45857400</v>
+      </c>
+      <c r="Z10" s="32">
+        <v>45735200</v>
+      </c>
+      <c r="AA10" s="32">
+        <v>45547200</v>
+      </c>
+      <c r="AB10" s="32">
+        <v>45330500</v>
+      </c>
+      <c r="AC10" s="32">
+        <v>45173000</v>
+      </c>
+      <c r="AD10" s="32">
+        <v>45064600</v>
+      </c>
+      <c r="AE10" s="32">
+        <v>44961200</v>
+      </c>
+      <c r="AF10" s="32">
+        <v>44856100</v>
+      </c>
+    </row>
+    <row r="11" spans="2:32">
+      <c r="B11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="D11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="E11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="F11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="G11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="H11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="I11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="J11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="K11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="L11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="M11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="N11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="O11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="P11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Q11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="R11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="S11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="T11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="U11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="V11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="W11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="X11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Y11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Z11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AA11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AB11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AC11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AD11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AE11" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AF11" s="32">
+        <v>1042500000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:32">
+      <c r="B12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="D12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="E12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="F12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="G12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="H12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="I12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="J12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="K12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="L12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="M12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="N12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="O12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="P12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Q12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="R12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="S12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="T12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="U12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="V12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="W12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="X12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Y12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Z12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AA12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AB12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AC12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AD12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AE12" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AF12" s="32">
+        <v>1042500000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:32">
+      <c r="B13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="32">
+        <v>45539700</v>
+      </c>
+      <c r="D13" s="32">
+        <v>45612800</v>
+      </c>
+      <c r="E13" s="32">
+        <v>45614800</v>
+      </c>
+      <c r="F13" s="32">
+        <v>45616600</v>
+      </c>
+      <c r="G13" s="32">
+        <v>45618800</v>
+      </c>
+      <c r="H13" s="32">
+        <v>45620700</v>
+      </c>
+      <c r="I13" s="32">
+        <v>45623000</v>
+      </c>
+      <c r="J13" s="32">
+        <v>45625100</v>
+      </c>
+      <c r="K13" s="32">
+        <v>45627300</v>
+      </c>
+      <c r="L13" s="32">
+        <v>45627100</v>
+      </c>
+      <c r="M13" s="32">
+        <v>45629500</v>
+      </c>
+      <c r="N13" s="32">
+        <v>45631800</v>
+      </c>
+      <c r="O13" s="32">
+        <v>45634400</v>
+      </c>
+      <c r="P13" s="32">
+        <v>45636900</v>
+      </c>
+      <c r="Q13" s="32">
+        <v>45639400</v>
+      </c>
+      <c r="R13" s="32">
+        <v>45642100</v>
+      </c>
+      <c r="S13" s="32">
+        <v>45644800</v>
+      </c>
+      <c r="T13" s="32">
+        <v>45647600</v>
+      </c>
+      <c r="U13" s="32">
+        <v>45647800</v>
+      </c>
+      <c r="V13" s="32">
+        <v>45650700</v>
+      </c>
+      <c r="W13" s="32">
+        <v>45653600</v>
+      </c>
+      <c r="X13" s="32">
+        <v>45656600</v>
+      </c>
+      <c r="Y13" s="32">
+        <v>45659700</v>
+      </c>
+      <c r="Z13" s="32">
+        <v>45662800</v>
+      </c>
+      <c r="AA13" s="32">
+        <v>45663500</v>
+      </c>
+      <c r="AB13" s="32">
+        <v>45666800</v>
+      </c>
+      <c r="AC13" s="32">
+        <v>45670100</v>
+      </c>
+      <c r="AD13" s="32">
+        <v>45673500</v>
+      </c>
+      <c r="AE13" s="32">
+        <v>45676900</v>
+      </c>
+      <c r="AF13" s="32">
+        <v>45677800</v>
+      </c>
+    </row>
+    <row r="14" spans="2:32">
+      <c r="B14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="D14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="E14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="F14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="G14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="H14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="I14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="J14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="K14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="L14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="M14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="N14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="O14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="P14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Q14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="R14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="S14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="T14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="U14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="V14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="W14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="X14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Y14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Z14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AA14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AB14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AC14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AD14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AE14" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AF14" s="32">
+        <v>1042500000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:32">
+      <c r="B15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="D15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="E15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="F15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="G15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="H15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="I15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="J15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="K15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="L15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="M15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="N15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="O15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="P15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Q15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="R15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="S15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="T15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="U15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="V15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="W15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="X15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Y15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="Z15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AA15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AB15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AC15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AD15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AE15" s="32">
+        <v>1042500000</v>
+      </c>
+      <c r="AF15" s="32">
+        <v>1042500000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:32">
+      <c r="B16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="32">
+        <v>39699000</v>
+      </c>
+      <c r="D16" s="32">
+        <v>39030400</v>
+      </c>
+      <c r="E16" s="32">
+        <v>38884700</v>
+      </c>
+      <c r="F16" s="32">
+        <v>38306200</v>
+      </c>
+      <c r="G16" s="32">
+        <v>37741600</v>
+      </c>
+      <c r="H16" s="32">
+        <v>37193100</v>
+      </c>
+      <c r="I16" s="32">
+        <v>36645600</v>
+      </c>
+      <c r="J16" s="32">
+        <v>36104900</v>
+      </c>
+      <c r="K16" s="32">
+        <v>35595500</v>
+      </c>
+      <c r="L16" s="32">
+        <v>35102000</v>
+      </c>
+      <c r="M16" s="32">
+        <v>35030200</v>
+      </c>
+      <c r="N16" s="32">
+        <v>34952800</v>
+      </c>
+      <c r="O16" s="32">
+        <v>34886900</v>
+      </c>
+      <c r="P16" s="32">
+        <v>34822000</v>
+      </c>
+      <c r="Q16" s="32">
+        <v>34759800</v>
+      </c>
+      <c r="R16" s="32">
+        <v>34703400</v>
+      </c>
+      <c r="S16" s="32">
+        <v>34650100</v>
+      </c>
+      <c r="T16" s="32">
+        <v>34598600</v>
+      </c>
+      <c r="U16" s="32">
+        <v>34550700</v>
+      </c>
+      <c r="V16" s="32">
+        <v>34506900</v>
+      </c>
+      <c r="W16" s="32">
+        <v>34464600</v>
+      </c>
+      <c r="X16" s="32">
+        <v>34425100</v>
+      </c>
+      <c r="Y16" s="32">
+        <v>34387600</v>
+      </c>
+      <c r="Z16" s="32">
+        <v>34351600</v>
+      </c>
+      <c r="AA16" s="32">
+        <v>34317400</v>
+      </c>
+      <c r="AB16" s="32">
+        <v>34284900</v>
+      </c>
+      <c r="AC16" s="32">
+        <v>34255200</v>
+      </c>
+      <c r="AD16" s="32">
+        <v>34227000</v>
+      </c>
+      <c r="AE16" s="32">
+        <v>34199900</v>
+      </c>
+      <c r="AF16" s="32">
+        <v>34173100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD9F80A-1DD4-4EFC-BD0A-42EC00E11F1F}">
   <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12655,16 +15287,16 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>61189</v>
+        <v>58414</v>
       </c>
       <c r="E2">
         <v>3.5339646603533899E-2</v>
       </c>
       <c r="F2">
-        <v>7.5738458244009904E-2</v>
+        <v>7.3490200174101794E-2</v>
       </c>
       <c r="G2">
-        <v>-2.5804692126173099</v>
+        <v>-2.6106032126173</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -12678,16 +15310,16 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>53835</v>
+        <v>54549</v>
       </c>
       <c r="E3">
         <v>1.6999830001699901E-3</v>
       </c>
       <c r="F3">
-        <v>3.3111542696076198E-3</v>
+        <v>3.3619455883161201E-3</v>
       </c>
       <c r="G3">
-        <v>-5.7104584284466897</v>
+        <v>-5.69523542844669</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -12701,7 +15333,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>49476</v>
+        <v>49019</v>
       </c>
       <c r="E4">
         <v>0.54334456655433405</v>
@@ -12724,16 +15356,16 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>51215</v>
+        <v>51468</v>
       </c>
       <c r="E5">
         <v>0.31188688113118801</v>
       </c>
       <c r="F5">
-        <v>0.58713757439567404</v>
+        <v>0.59258194130892095</v>
       </c>
       <c r="G5">
-        <v>-0.53249611796727703</v>
+        <v>-0.52326611796727696</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -12747,16 +15379,16 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>64682</v>
+        <v>55470</v>
       </c>
       <c r="E6">
         <v>1.34198658013419E-2</v>
       </c>
       <c r="F6">
-        <v>3.0097006982601999E-2</v>
+        <v>2.68592624324243E-2</v>
       </c>
       <c r="G6">
-        <v>-3.5033295479653201</v>
+        <v>-3.6171445479653199</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -12770,16 +15402,16 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>52451</v>
+        <v>52804</v>
       </c>
       <c r="E7">
         <v>8.8569114308856903E-2</v>
       </c>
       <c r="F7">
-        <v>0.169435072322971</v>
+        <v>0.171228650249552</v>
       </c>
       <c r="G7">
-        <v>-1.7752854796873601</v>
+        <v>-1.7647554796873599</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -12793,16 +15425,16 @@
         <v>79</v>
       </c>
       <c r="D8">
-        <v>81273</v>
+        <v>69435</v>
       </c>
       <c r="E8">
         <v>5.7399426005739903E-3</v>
       </c>
       <c r="F8">
-        <v>1.5971754362172401E-2</v>
+        <v>1.3775185340645301E-2</v>
       </c>
       <c r="G8">
-        <v>-4.1369334691773796</v>
+        <v>-4.2848864691773798</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -12816,16 +15448,16 @@
         <v>1</v>
       </c>
       <c r="D9">
-        <v>60642</v>
+        <v>57856</v>
       </c>
       <c r="E9">
         <v>7.4800000000000005E-2</v>
       </c>
       <c r="F9">
-        <v>0.16254791306372199</v>
+        <v>0.157825313074512</v>
       </c>
       <c r="G9">
-        <v>-1.8167824710490399</v>
+        <v>-1.84626647104904</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -12839,16 +15471,16 @@
         <v>2</v>
       </c>
       <c r="D10">
-        <v>52557</v>
+        <v>53186</v>
       </c>
       <c r="E10">
         <v>1.6299999999999999E-3</v>
       </c>
       <c r="F10">
-        <v>3.18875302069616E-3</v>
+        <v>3.2366567758692999E-3</v>
       </c>
       <c r="G10">
-        <v>-5.7481253412108</v>
+        <v>-5.7332143412108003</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -12862,7 +15494,7 @@
         <v>3</v>
       </c>
       <c r="D11">
-        <v>50918</v>
+        <v>50400</v>
       </c>
       <c r="E11">
         <v>0.52217999999999998</v>
@@ -12885,16 +15517,16 @@
         <v>4</v>
       </c>
       <c r="D12">
-        <v>52541</v>
+        <v>52846</v>
       </c>
       <c r="E12">
         <v>0.29974000000000001</v>
       </c>
       <c r="F12">
-        <v>0.58625646954423505</v>
+        <v>0.59256250147626899</v>
       </c>
       <c r="G12">
-        <v>-0.53399792381262701</v>
+        <v>-0.52329892381262699</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -12908,16 +15540,16 @@
         <v>5</v>
       </c>
       <c r="D13">
-        <v>65467</v>
+        <v>55608</v>
       </c>
       <c r="E13">
         <v>9.4699999999999993E-3</v>
       </c>
       <c r="F13">
-        <v>2.1911439020317398E-2</v>
+        <v>1.94058745124292E-2</v>
       </c>
       <c r="G13">
-        <v>-3.8207464488314899</v>
+        <v>-3.9421794488314901</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -12931,16 +15563,16 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>48883</v>
+        <v>49243</v>
       </c>
       <c r="E14">
         <v>8.5120000000000001E-2</v>
       </c>
       <c r="F14">
-        <v>0.15875306561484401</v>
+        <v>0.160575453689589</v>
       </c>
       <c r="G14">
-        <v>-1.8404053304361401</v>
+        <v>-1.82899133043614</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -12954,16 +15586,16 @@
         <v>79</v>
       </c>
       <c r="D15">
-        <v>70483</v>
+        <v>58645</v>
       </c>
       <c r="E15">
         <v>7.0600000000000003E-3</v>
       </c>
       <c r="F15">
-        <v>1.7435929211407498E-2</v>
+        <v>1.50499244982964E-2</v>
       </c>
       <c r="G15">
-        <v>-4.0492223045243199</v>
+        <v>-4.1963823045243203</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -12977,16 +15609,16 @@
         <v>1</v>
       </c>
       <c r="D16">
-        <v>57692</v>
+        <v>54552</v>
       </c>
       <c r="E16">
         <v>6.5549344506554905E-2</v>
       </c>
       <c r="F16">
-        <v>0.13456250619976501</v>
+        <v>0.13005309903783399</v>
       </c>
       <c r="G16">
-        <v>-2.0057264577840499</v>
+        <v>-2.0398124577840502</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -13000,16 +15632,16 @@
         <v>2</v>
       </c>
       <c r="D17">
-        <v>53849</v>
+        <v>54943</v>
       </c>
       <c r="E17">
         <v>1.65998340016599E-3</v>
       </c>
       <c r="F17">
-        <v>3.2416232692108801E-3</v>
+        <v>3.3102715104686301E-3</v>
       </c>
       <c r="G17">
-        <v>-5.7316810656252999</v>
+        <v>-5.7107250656252999</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -13023,7 +15655,7 @@
         <v>3</v>
       </c>
       <c r="D18">
-        <v>51190</v>
+        <v>50672</v>
       </c>
       <c r="E18">
         <v>0.53009469905300899</v>
@@ -13046,16 +15678,16 @@
         <v>4</v>
       </c>
       <c r="D19">
-        <v>52765</v>
+        <v>53072</v>
       </c>
       <c r="E19">
         <v>0.30427695723042703</v>
       </c>
       <c r="F19">
-        <v>0.58587879933822895</v>
+        <v>0.592196165783894</v>
       </c>
       <c r="G19">
-        <v>-0.53464233786465998</v>
+        <v>-0.52391733786465899</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -13069,16 +15701,16 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>65520</v>
+        <v>55047</v>
       </c>
       <c r="E20">
         <v>9.0999090009099906E-3</v>
       </c>
       <c r="F20">
-        <v>2.0681798718551799E-2</v>
+        <v>1.8171220012969998E-2</v>
       </c>
       <c r="G20">
-        <v>-3.8785012544709501</v>
+        <v>-4.0079162544709499</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -13092,16 +15724,16 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>49052</v>
+        <v>49412</v>
       </c>
       <c r="E21">
         <v>8.6409135908640897E-2</v>
       </c>
       <c r="F21">
-        <v>0.158538746497771</v>
+        <v>0.16035867432016401</v>
       </c>
       <c r="G21">
-        <v>-1.8417562581404501</v>
+        <v>-1.83034225814045</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -13115,16 +15747,16 @@
         <v>79</v>
       </c>
       <c r="D22">
-        <v>69318</v>
+        <v>57488</v>
       </c>
       <c r="E22">
         <v>2.9099709002909902E-3</v>
       </c>
       <c r="F22">
-        <v>6.9483671683743999E-3</v>
+        <v>5.9981476236627097E-3</v>
       </c>
       <c r="G22">
-        <v>-4.96924858681035</v>
+        <v>-5.1163045868103598</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -13138,16 +15770,16 @@
         <v>1</v>
       </c>
       <c r="D23">
-        <v>56381</v>
+        <v>52141</v>
       </c>
       <c r="E23">
         <v>8.6980869808698E-2</v>
       </c>
       <c r="F23">
-        <v>0.17887325579206301</v>
+        <v>0.17042213170193199</v>
       </c>
       <c r="G23">
-        <v>-1.72107779214082</v>
+        <v>-1.7694767921408201</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -13161,16 +15793,16 @@
         <v>2</v>
       </c>
       <c r="D24">
-        <v>54241</v>
+        <v>55384</v>
       </c>
       <c r="E24">
         <v>1.620016200162E-3</v>
       </c>
       <c r="F24">
-        <v>3.2401040027916599E-3</v>
+        <v>3.31078535598989E-3</v>
       </c>
       <c r="G24">
-        <v>-5.73214985006602</v>
+        <v>-5.7105698500660198</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -13184,7 +15816,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>51380</v>
+        <v>50863</v>
       </c>
       <c r="E25">
         <v>0.51893518935189298</v>
@@ -13207,16 +15839,16 @@
         <v>4</v>
       </c>
       <c r="D26">
-        <v>52929</v>
+        <v>53239</v>
       </c>
       <c r="E26">
         <v>0.29787297872978702</v>
       </c>
       <c r="F26">
-        <v>0.58568402014887</v>
+        <v>0.592014678526816</v>
       </c>
       <c r="G26">
-        <v>-0.53497484959670505</v>
+        <v>-0.52422384959670598</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -13230,16 +15862,16 @@
         <v>5</v>
       </c>
       <c r="D27">
-        <v>67134</v>
+        <v>54936</v>
       </c>
       <c r="E27">
         <v>8.0900809008089998E-3</v>
       </c>
       <c r="F27">
-        <v>1.91330462605762E-2</v>
+        <v>1.64374786444835E-2</v>
       </c>
       <c r="G27">
-        <v>-3.95633826823991</v>
+        <v>-4.10819126823991</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -13253,16 +15885,16 @@
         <v>78</v>
       </c>
       <c r="D28">
-        <v>49178</v>
+        <v>49538</v>
       </c>
       <c r="E28">
         <v>8.4590845908459E-2</v>
       </c>
       <c r="F28">
-        <v>0.15840837270788899</v>
+        <v>0.16022472098401899</v>
       </c>
       <c r="G28">
-        <v>-1.84257894299439</v>
+        <v>-1.83117794299439</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -13276,16 +15908,16 @@
         <v>79</v>
       </c>
       <c r="D29">
-        <v>68079</v>
+        <v>56249</v>
       </c>
       <c r="E29">
         <v>1.910019100191E-3</v>
       </c>
       <c r="F29">
-        <v>4.5730323634844599E-3</v>
+        <v>3.9475989042041899E-3</v>
       </c>
       <c r="G29">
-        <v>-5.3875787572517799</v>
+        <v>-5.53464775725178</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -13299,16 +15931,16 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>55161</v>
+        <v>50779</v>
       </c>
       <c r="E30">
         <v>0.13181999999999999</v>
       </c>
       <c r="F30">
-        <v>0.28035657357026</v>
+        <v>0.26665968836382897</v>
       </c>
       <c r="G30">
-        <v>-1.27169300896036</v>
+        <v>-1.32178200896036</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -13322,16 +15954,16 @@
         <v>2</v>
       </c>
       <c r="D31">
-        <v>54782</v>
+        <v>55921</v>
       </c>
       <c r="E31">
         <v>1.5299999999999999E-3</v>
       </c>
       <c r="F31">
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="G31">
-        <v>-5.7327896291805898</v>
+        <v>-5.7111056291805902</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -13345,7 +15977,7 @@
         <v>3</v>
       </c>
       <c r="D32">
-        <v>51895</v>
+        <v>51366</v>
       </c>
       <c r="E32">
         <v>0.49058000000000002</v>
@@ -13368,16 +16000,16 @@
         <v>4</v>
       </c>
       <c r="D33">
-        <v>53324</v>
+        <v>53638</v>
       </c>
       <c r="E33">
         <v>0.28160000000000002</v>
       </c>
       <c r="F33">
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="G33">
-        <v>-0.53652374030104899</v>
+        <v>-0.52556474030104905</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -13391,16 +16023,16 @@
         <v>5</v>
       </c>
       <c r="D34">
-        <v>67156</v>
+        <v>54680</v>
       </c>
       <c r="E34">
         <v>1.0749999999999999E-2</v>
       </c>
       <c r="F34">
-        <v>2.67214247564647E-2</v>
+        <v>2.2877517710931699E-2</v>
       </c>
       <c r="G34">
-        <v>-3.62228961001126</v>
+        <v>-3.7776006100112598</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -13414,16 +16046,16 @@
         <v>78</v>
       </c>
       <c r="D35">
-        <v>49473</v>
+        <v>49833</v>
       </c>
       <c r="E35">
         <v>7.9969999999999999E-2</v>
       </c>
       <c r="F35">
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="G35">
-        <v>-1.8454228002411299</v>
+        <v>-1.8338658002411301</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -13437,16 +16069,16 @@
         <v>79</v>
       </c>
       <c r="D36">
-        <v>68366</v>
+        <v>56469</v>
       </c>
       <c r="E36">
         <v>3.7499999999999999E-3</v>
       </c>
       <c r="F36">
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="G36">
-        <v>-4.6597095246026097</v>
+        <v>-4.8074935246026103</v>
       </c>
     </row>
   </sheetData>
@@ -13454,7 +16086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -13759,43 +16391,43 @@
       </c>
       <c r="H10" s="20">
         <f>I10</f>
-        <v>7.5738458244009904E-2</v>
+        <v>7.3490200174101794E-2</v>
       </c>
       <c r="I10" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!I$9,recalculated_shareweights!$C:$C,Data!$C10)</f>
-        <v>7.5738458244009904E-2</v>
+        <v>7.3490200174101794E-2</v>
       </c>
       <c r="J10" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!J$9,recalculated_shareweights!$C:$C,Data!$C10)</f>
-        <v>0.16254791306372199</v>
+        <v>0.157825313074512</v>
       </c>
       <c r="K10" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!K$9,recalculated_shareweights!$C:$C,Data!$C10)</f>
-        <v>0.13456250619976501</v>
+        <v>0.13005309903783399</v>
       </c>
       <c r="L10" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!L$9,recalculated_shareweights!$C:$C,Data!$C10)</f>
-        <v>0.17887325579206301</v>
+        <v>0.17042213170193199</v>
       </c>
       <c r="M10" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!M$9,recalculated_shareweights!$C:$C,Data!$C10)</f>
-        <v>0.28035657357026</v>
+        <v>0.26665968836382897</v>
       </c>
       <c r="N10">
         <f>M10+($R$10-$M$10)/($R$9-$M$9)</f>
-        <v>0.32028525885620801</v>
+        <v>0.30932775069106316</v>
       </c>
       <c r="O10">
         <f t="shared" ref="O10:Q10" si="1">N10+($R$10-$M$10)/($R$9-$M$9)</f>
-        <v>0.36021394414215602</v>
+        <v>0.35199581301829735</v>
       </c>
       <c r="P10">
         <f t="shared" si="1"/>
-        <v>0.40014262942810402</v>
+        <v>0.39466387534553155</v>
       </c>
       <c r="Q10">
         <f t="shared" si="1"/>
-        <v>0.44007131471405203</v>
+        <v>0.43733193767276574</v>
       </c>
       <c r="R10" s="31">
         <v>0.48</v>
@@ -13895,127 +16527,127 @@
       </c>
       <c r="H11" s="20">
         <f t="shared" ref="H11:H16" si="9">I11</f>
-        <v>3.3111542696076198E-3</v>
+        <v>3.3619455883161201E-3</v>
       </c>
       <c r="I11" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!I$9,recalculated_shareweights!$C:$C,Data!$C11)</f>
-        <v>3.3111542696076198E-3</v>
+        <v>3.3619455883161201E-3</v>
       </c>
       <c r="J11" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!J$9,recalculated_shareweights!$C:$C,Data!$C11)</f>
-        <v>3.18875302069616E-3</v>
+        <v>3.2366567758692999E-3</v>
       </c>
       <c r="K11" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!K$9,recalculated_shareweights!$C:$C,Data!$C11)</f>
-        <v>3.2416232692108801E-3</v>
+        <v>3.3102715104686301E-3</v>
       </c>
       <c r="L11" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!L$9,recalculated_shareweights!$C:$C,Data!$C11)</f>
-        <v>3.2401040027916599E-3</v>
+        <v>3.31078535598989E-3</v>
       </c>
       <c r="M11" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!M$9,recalculated_shareweights!$C:$C,Data!$C11)</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="N11">
         <f t="shared" ref="N11:AL11" si="10">M11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="O11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="P11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="Q11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="R11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="S11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="T11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="U11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="V11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="W11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="X11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="Y11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="Z11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AA11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AB11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AC11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AD11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AE11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AF11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AG11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AH11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AI11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AJ11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AK11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AL11">
         <f t="shared" si="10"/>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -14177,127 +16809,127 @@
       </c>
       <c r="H13" s="20">
         <f t="shared" si="9"/>
-        <v>0.58713757439567404</v>
+        <v>0.59258194130892095</v>
       </c>
       <c r="I13" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!I$9,recalculated_shareweights!$C:$C,Data!$C13)</f>
-        <v>0.58713757439567404</v>
+        <v>0.59258194130892095</v>
       </c>
       <c r="J13" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!J$9,recalculated_shareweights!$C:$C,Data!$C13)</f>
-        <v>0.58625646954423505</v>
+        <v>0.59256250147626899</v>
       </c>
       <c r="K13" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!K$9,recalculated_shareweights!$C:$C,Data!$C13)</f>
-        <v>0.58587879933822895</v>
+        <v>0.592196165783894</v>
       </c>
       <c r="L13" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!L$9,recalculated_shareweights!$C:$C,Data!$C13)</f>
-        <v>0.58568402014887</v>
+        <v>0.592014678526816</v>
       </c>
       <c r="M13" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!M$9,recalculated_shareweights!$C:$C,Data!$C13)</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="N13">
         <f t="shared" ref="N13:AL13" si="13">M13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="O13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="P13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="Q13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="R13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="S13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="T13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="U13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="V13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="W13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="X13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="Y13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="Z13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AA13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AB13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AC13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AD13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AE13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AF13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AG13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AH13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AI13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AJ13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AK13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AL13">
         <f t="shared" si="13"/>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -14317,43 +16949,43 @@
       </c>
       <c r="H14" s="20">
         <f t="shared" si="9"/>
-        <v>3.0097006982601999E-2</v>
+        <v>2.68592624324243E-2</v>
       </c>
       <c r="I14" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!I$9,recalculated_shareweights!$C:$C,Data!$C14)</f>
-        <v>3.0097006982601999E-2</v>
+        <v>2.68592624324243E-2</v>
       </c>
       <c r="J14" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!J$9,recalculated_shareweights!$C:$C,Data!$C14)</f>
-        <v>2.1911439020317398E-2</v>
+        <v>1.94058745124292E-2</v>
       </c>
       <c r="K14" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!K$9,recalculated_shareweights!$C:$C,Data!$C14)</f>
-        <v>2.0681798718551799E-2</v>
+        <v>1.8171220012969998E-2</v>
       </c>
       <c r="L14" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!L$9,recalculated_shareweights!$C:$C,Data!$C14)</f>
-        <v>1.91330462605762E-2</v>
+        <v>1.64374786444835E-2</v>
       </c>
       <c r="M14" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!M$9,recalculated_shareweights!$C:$C,Data!$C14)</f>
-        <v>2.67214247564647E-2</v>
+        <v>2.2877517710931699E-2</v>
       </c>
       <c r="N14">
         <f>M14+($R$14-$M$14)/($R$9-$M$9)</f>
-        <v>3.097713980517176E-2</v>
+        <v>2.7902014168745361E-2</v>
       </c>
       <c r="O14">
         <f t="shared" ref="O14:Q14" si="14">N14+($R$14-$M$14)/($R$9-$M$9)</f>
-        <v>3.5232854853878823E-2</v>
+        <v>3.2926510626559019E-2</v>
       </c>
       <c r="P14">
         <f t="shared" si="14"/>
-        <v>3.9488569902585882E-2</v>
+        <v>3.7951007084372677E-2</v>
       </c>
       <c r="Q14">
         <f t="shared" si="14"/>
-        <v>4.3744284951292942E-2</v>
+        <v>4.2975503542186336E-2</v>
       </c>
       <c r="R14" s="31">
         <v>4.8000000000000001E-2</v>
@@ -14453,127 +17085,127 @@
       </c>
       <c r="H15" s="20">
         <f t="shared" si="9"/>
-        <v>0.169435072322971</v>
+        <v>0.171228650249552</v>
       </c>
       <c r="I15" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!I$9,recalculated_shareweights!$C:$C,Data!$C15)</f>
-        <v>0.169435072322971</v>
+        <v>0.171228650249552</v>
       </c>
       <c r="J15" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!J$9,recalculated_shareweights!$C:$C,Data!$C15)</f>
-        <v>0.15875306561484401</v>
+        <v>0.160575453689589</v>
       </c>
       <c r="K15" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!K$9,recalculated_shareweights!$C:$C,Data!$C15)</f>
-        <v>0.158538746497771</v>
+        <v>0.16035867432016401</v>
       </c>
       <c r="L15" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!L$9,recalculated_shareweights!$C:$C,Data!$C15)</f>
-        <v>0.15840837270788899</v>
+        <v>0.16022472098401899</v>
       </c>
       <c r="M15" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!M$9,recalculated_shareweights!$C:$C,Data!$C15)</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="N15">
         <f t="shared" ref="N15:AL15" si="21">M15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="O15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="P15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="Q15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="R15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="S15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="T15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="U15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="V15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="W15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="X15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="Y15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="Z15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AA15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AB15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AC15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AD15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AE15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AF15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AG15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AH15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AI15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AJ15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AK15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AL15">
         <f t="shared" si="21"/>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
     </row>
     <row r="16" spans="1:38" ht="15.75" thickBot="1">
@@ -14596,127 +17228,127 @@
       </c>
       <c r="H16" s="20">
         <f t="shared" si="9"/>
-        <v>1.5971754362172401E-2</v>
+        <v>1.3775185340645301E-2</v>
       </c>
       <c r="I16" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!I$9,recalculated_shareweights!$C:$C,Data!$C16)</f>
-        <v>1.5971754362172401E-2</v>
+        <v>1.3775185340645301E-2</v>
       </c>
       <c r="J16" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!J$9,recalculated_shareweights!$C:$C,Data!$C16)</f>
-        <v>1.7435929211407498E-2</v>
+        <v>1.50499244982964E-2</v>
       </c>
       <c r="K16" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!K$9,recalculated_shareweights!$C:$C,Data!$C16)</f>
-        <v>6.9483671683743999E-3</v>
+        <v>5.9981476236627097E-3</v>
       </c>
       <c r="L16" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!L$9,recalculated_shareweights!$C:$C,Data!$C16)</f>
-        <v>4.5730323634844599E-3</v>
+        <v>3.9475989042041899E-3</v>
       </c>
       <c r="M16" s="30">
         <f>SUMIFS(recalculated_shareweights!$F:$F,recalculated_shareweights!$A:$A,Data!M$9,recalculated_shareweights!$C:$C,Data!$C16)</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="N16">
         <f t="shared" ref="N16:AL16" si="22">M16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="O16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="P16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="Q16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="R16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="S16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="T16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="U16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="V16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="W16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="X16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="Y16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="Z16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AA16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AB16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AC16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AD16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AE16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AF16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AG16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AH16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AI16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AJ16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AK16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AL16">
         <f t="shared" si="22"/>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -14730,12 +17362,10 @@
         <v>1</v>
       </c>
       <c r="D17" s="20">
-        <f>MIN(1.25*INDEX('SYVbT-freight'!$B$2:$H$2,MATCH(Data!$C10,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-freight'!$B$2:$H$2),1)</f>
-        <v>5.3683612196023132E-3</v>
+        <v>0.05</v>
       </c>
       <c r="E17">
-        <f>E10</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="6" t="str">
         <f>IF(D17=E17,"n/a",IF(OR(C17="battery electric vehicle",C17="natural gas vehicle",C17="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -14743,127 +17373,127 @@
       </c>
       <c r="H17" s="20">
         <f t="shared" ref="H17:H40" si="23">D17</f>
-        <v>5.3683612196023132E-3</v>
+        <v>0.05</v>
       </c>
       <c r="I17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,I$9))</f>
-        <v>2.0063080574076027E-2</v>
+        <v>5.6648314261972879E-2</v>
       </c>
       <c r="J17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,J$9))</f>
-        <v>2.5102157025791948E-2</v>
+        <v>5.8928137580334883E-2</v>
       </c>
       <c r="K17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,K$9))</f>
-        <v>3.1822572527592123E-2</v>
+        <v>6.1968647109589645E-2</v>
       </c>
       <c r="L17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,L$9))</f>
-        <v>4.0748591499212138E-2</v>
+        <v>6.6007035172686288E-2</v>
       </c>
       <c r="M17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,M$9))</f>
-        <v>5.2539635178796867E-2</v>
+        <v>7.1341642929905053E-2</v>
       </c>
       <c r="N17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,N$9))</f>
-        <v>6.8003653554074228E-2</v>
+        <v>7.833801022564843E-2</v>
       </c>
       <c r="O17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,O$9))</f>
-        <v>8.8094556635136961E-2</v>
+        <v>8.7427713422265074E-2</v>
       </c>
       <c r="P17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,P$9))</f>
-        <v>0.11387951127112682</v>
+        <v>9.9093569538025811E-2</v>
       </c>
       <c r="Q17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,Q$9))</f>
-        <v>0.14645791836431907</v>
+        <v>0.11383297920521952</v>
       </c>
       <c r="R17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,R$9))</f>
-        <v>0.186814558918491</v>
+        <v>0.13209148571286036</v>
       </c>
       <c r="S17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,S$9))</f>
-        <v>0.23560093514502178</v>
+        <v>0.15416384742544209</v>
       </c>
       <c r="T17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,T$9))</f>
-        <v>0.29286713111398371</v>
+        <v>0.18007272381874823</v>
       </c>
       <c r="U17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,U$9))</f>
-        <v>0.35780981004973877</v>
+        <v>0.20945466219839204</v>
       </c>
       <c r="V17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,V$9))</f>
-        <v>0.4286412981184835</v>
+        <v>0.24150086743475346</v>
       </c>
       <c r="W17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,W$9))</f>
-        <v>0.50268418060980113</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="X17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,X$9))</f>
-        <v>0.57672706310111888</v>
+        <v>0.30849913256524658</v>
       </c>
       <c r="Y17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,Y$9))</f>
-        <v>0.64755855116986349</v>
+        <v>0.34054533780160795</v>
       </c>
       <c r="Z17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,Z$9))</f>
-        <v>0.71250123010561861</v>
+        <v>0.36992727618125176</v>
       </c>
       <c r="AA17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AA$9))</f>
-        <v>0.76976742607458049</v>
+        <v>0.3958361525745579</v>
       </c>
       <c r="AB17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AB$9))</f>
-        <v>0.8185538023011113</v>
+        <v>0.4179085142871396</v>
       </c>
       <c r="AC17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AC$9))</f>
-        <v>0.85891044285528328</v>
+        <v>0.43616702079478054</v>
       </c>
       <c r="AD17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AD$9))</f>
-        <v>0.89148884994847555</v>
+        <v>0.45090643046197421</v>
       </c>
       <c r="AE17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AE$9))</f>
-        <v>0.91727380458446539</v>
+        <v>0.46257228657773497</v>
       </c>
       <c r="AF17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AF$9))</f>
-        <v>0.93736470766552815</v>
+        <v>0.47166198977435159</v>
       </c>
       <c r="AG17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AG$9))</f>
-        <v>0.95282872604080548</v>
+        <v>0.47865835707009496</v>
       </c>
       <c r="AH17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AH$9))</f>
-        <v>0.96461976972039021</v>
+        <v>0.48399296482731374</v>
       </c>
       <c r="AI17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AI$9))</f>
-        <v>0.97354578869201014</v>
+        <v>0.48803135289041033</v>
       </c>
       <c r="AJ17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AJ$9))</f>
-        <v>0.98026620419381039</v>
+        <v>0.49107186241966516</v>
       </c>
       <c r="AK17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AK$9))</f>
-        <v>0.98530528064552625</v>
+        <v>0.49335168573802712</v>
       </c>
       <c r="AL17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AL$9))</f>
-        <v>0.98907203924614695</v>
+        <v>0.49505587581623306</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -15723,11 +18353,10 @@
         <v>1</v>
       </c>
       <c r="D24" s="20">
-        <f>MIN(1.25*INDEX('SYVbT-passenger'!$B$3:$H$3,MATCH(Data!$C10,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-passenger'!$B$3:$H$3),1)</f>
-        <v>7.2747216149611415E-3</v>
+        <v>0.05</v>
       </c>
       <c r="E24" s="26">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F24" s="6" t="str">
         <f>IF(D24=E24,"n/a",IF(OR(C24="battery electric vehicle",C24="natural gas vehicle",C24="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -15735,127 +18364,127 @@
       </c>
       <c r="H24" s="20">
         <f t="shared" si="23"/>
-        <v>7.2747216149611415E-3</v>
+        <v>0.05</v>
       </c>
       <c r="I24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,I$9))</f>
-        <v>1.8986470001880411E-2</v>
+        <v>6.4035330108609401E-2</v>
       </c>
       <c r="J24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,J$9))</f>
-        <v>2.3002633501252021E-2</v>
+        <v>6.8848290447373631E-2</v>
       </c>
       <c r="K24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,K$9))</f>
-        <v>2.8358830752387227E-2</v>
+        <v>7.5267143898022582E-2</v>
       </c>
       <c r="L24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,L$9))</f>
-        <v>3.5472902533598569E-2</v>
+        <v>8.3792629809004371E-2</v>
       </c>
       <c r="M24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,M$9))</f>
-        <v>4.4870410132301322E-2</v>
+        <v>9.505457951868844E-2</v>
       </c>
       <c r="N24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,N$9))</f>
-        <v>5.7195292826083877E-2</v>
+        <v>0.10982468825414668</v>
       </c>
       <c r="O24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,O$9))</f>
-        <v>7.3207820597140094E-2</v>
+        <v>0.12901406166922624</v>
       </c>
       <c r="P24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,P$9))</f>
-        <v>9.3758529568176208E-2</v>
+        <v>0.15364198013583227</v>
       </c>
       <c r="Q24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,Q$9))</f>
-        <v>0.11972364652741456</v>
+        <v>0.18475851165546342</v>
       </c>
       <c r="R24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,R$9))</f>
-        <v>0.15188804575889153</v>
+        <v>0.22330424761603851</v>
       </c>
       <c r="S24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,S$9))</f>
-        <v>0.19077097705493956</v>
+        <v>0.26990145567593327</v>
       </c>
       <c r="T24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,T$9))</f>
-        <v>0.23641235761388887</v>
+        <v>0.32459797250624622</v>
       </c>
       <c r="U24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,U$9))</f>
-        <v>0.28817192490610039</v>
+        <v>0.38662650908549429</v>
       </c>
       <c r="V24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,V$9))</f>
-        <v>0.34462489594427526</v>
+        <v>0.45427960902892389</v>
       </c>
       <c r="W24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,W$9))</f>
-        <v>0.40363736080748058</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="X24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,X$9))</f>
-        <v>0.46264982567068591</v>
+        <v>0.5957203909710761</v>
       </c>
       <c r="Y24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,Y$9))</f>
-        <v>0.51910279670886073</v>
+        <v>0.6633734909145057</v>
       </c>
       <c r="Z24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,Z$9))</f>
-        <v>0.57086236400107226</v>
+        <v>0.72540202749375371</v>
       </c>
       <c r="AA24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AA$9))</f>
-        <v>0.61650374456002166</v>
+        <v>0.78009854432406667</v>
       </c>
       <c r="AB24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AB$9))</f>
-        <v>0.65538667585606958</v>
+        <v>0.82669575238396142</v>
       </c>
       <c r="AC24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AC$9))</f>
-        <v>0.68755107508754665</v>
+        <v>0.86524148834453662</v>
       </c>
       <c r="AD24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AD$9))</f>
-        <v>0.71351619204678496</v>
+        <v>0.89635801986416774</v>
       </c>
       <c r="AE24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AE$9))</f>
-        <v>0.73406690101782113</v>
+        <v>0.9209859383307738</v>
       </c>
       <c r="AF24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AF$9))</f>
-        <v>0.75007942878887734</v>
+        <v>0.94017531174585334</v>
       </c>
       <c r="AG24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AG$9))</f>
-        <v>0.76240431148265997</v>
+        <v>0.9549454204813117</v>
       </c>
       <c r="AH24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AH$9))</f>
-        <v>0.77180181908136269</v>
+        <v>0.96620737019099567</v>
       </c>
       <c r="AI24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AI$9))</f>
-        <v>0.77891589086257396</v>
+        <v>0.97473285610197735</v>
       </c>
       <c r="AJ24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AJ$9))</f>
-        <v>0.78427208811370919</v>
+        <v>0.98115170955262643</v>
       </c>
       <c r="AK24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AK$9))</f>
-        <v>0.7882882516130808</v>
+        <v>0.98596466989139064</v>
       </c>
       <c r="AL24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AL$9))</f>
-        <v>0.79129037284456261</v>
+        <v>0.98956240450093647</v>
       </c>
     </row>
     <row r="25" spans="1:38">
@@ -16721,8 +19350,7 @@
         <v>5.3709944550863111E-3</v>
       </c>
       <c r="E31" s="20">
-        <f>E24</f>
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F31" s="6" t="str">
         <f>IF(D31=E31,"n/a",IF(OR(C31="battery electric vehicle",C31="natural gas vehicle",C31="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -16734,123 +19362,123 @@
       </c>
       <c r="I31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,I$9))</f>
-        <v>1.7110868567400919E-2</v>
+        <v>1.2678659059418999E-2</v>
       </c>
       <c r="J31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,J$9))</f>
-        <v>2.1136676870263375E-2</v>
+        <v>1.5184585150040118E-2</v>
       </c>
       <c r="K31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,K$9))</f>
-        <v>2.6505737011555695E-2</v>
+        <v>1.8526638938495932E-2</v>
       </c>
       <c r="L31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,L$9))</f>
-        <v>3.3636893212851106E-2</v>
+        <v>2.2965536431060245E-2</v>
       </c>
       <c r="M31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,M$9))</f>
-        <v>4.3056968895275403E-2</v>
+        <v>2.8829206942005366E-2</v>
       </c>
       <c r="N31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,N$9))</f>
-        <v>5.541144975448322E-2</v>
+        <v>3.651944293738426E-2</v>
       </c>
       <c r="O31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,O$9))</f>
-        <v>7.1462431558540776E-2</v>
+        <v>4.6510622610364066E-2</v>
       </c>
       <c r="P31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,P$9))</f>
-        <v>9.2062492989867475E-2</v>
+        <v>5.933344663118359E-2</v>
       </c>
       <c r="Q31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,Q$9))</f>
-        <v>0.11808996509244796</v>
+        <v>7.5534645622301611E-2</v>
       </c>
       <c r="R31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,R$9))</f>
-        <v>0.15033160702334125</v>
+        <v>9.5603949881434322E-2</v>
       </c>
       <c r="S31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,S$9))</f>
-        <v>0.18930791555155554</v>
+        <v>0.11986535060126081</v>
       </c>
       <c r="T31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,T$9))</f>
-        <v>0.23505890373644214</v>
+        <v>0.1483437545239433</v>
       </c>
       <c r="U31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,U$9))</f>
-        <v>0.28694277145999392</v>
+        <v>0.18063966332773254</v>
       </c>
       <c r="V31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,V$9))</f>
-        <v>0.34353131412323407</v>
+        <v>0.21586406916673176</v>
       </c>
       <c r="W31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,W$9))</f>
-        <v>0.40268549722754321</v>
+        <v>0.25268549722754313</v>
       </c>
       <c r="X31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,X$9))</f>
-        <v>0.46183968033185235</v>
+        <v>0.28950692528835459</v>
       </c>
       <c r="Y31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,Y$9))</f>
-        <v>0.51842822299509239</v>
+        <v>0.32473133112735375</v>
       </c>
       <c r="Z31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,Z$9))</f>
-        <v>0.57031209071864419</v>
+        <v>0.35702723993114299</v>
       </c>
       <c r="AA31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AA$9))</f>
-        <v>0.61606307890353074</v>
+        <v>0.38550564385382546</v>
       </c>
       <c r="AB31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AB$9))</f>
-        <v>0.65503938743174506</v>
+        <v>0.40976704457365198</v>
       </c>
       <c r="AC31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AC$9))</f>
-        <v>0.68728102936263846</v>
+        <v>0.42983634883278476</v>
       </c>
       <c r="AD31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AD$9))</f>
-        <v>0.71330850146521885</v>
+        <v>0.4460375478239027</v>
       </c>
       <c r="AE31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AE$9))</f>
-        <v>0.7339085628965456</v>
+        <v>0.45886037184472228</v>
       </c>
       <c r="AF31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AF$9))</f>
-        <v>0.74995954470060322</v>
+        <v>0.46885155151770208</v>
       </c>
       <c r="AG31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AG$9))</f>
-        <v>0.76231402555981098</v>
+        <v>0.47654178751308102</v>
       </c>
       <c r="AH31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AH$9))</f>
-        <v>0.77173410124223529</v>
+        <v>0.48240545802402607</v>
       </c>
       <c r="AI31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AI$9))</f>
-        <v>0.77886525744353063</v>
+        <v>0.48684435551659033</v>
       </c>
       <c r="AJ31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AJ$9))</f>
-        <v>0.78423431758482298</v>
+        <v>0.4901864093050462</v>
       </c>
       <c r="AK31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AK$9))</f>
-        <v>0.78826012588768546</v>
+        <v>0.49269233539566731</v>
       </c>
       <c r="AL31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AL$9))</f>
-        <v>0.79126945670347282</v>
+        <v>0.4945655394926507</v>
       </c>
     </row>
     <row r="32" spans="1:38">
@@ -19674,12 +22302,11 @@
         <v>1</v>
       </c>
       <c r="D52" s="20">
-        <f>MIN(1.25*INDEX('SYVbT-passenger'!$B$5:$H$5,MATCH(Data!$C10,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-passenger'!$B$5:$H$5),1)</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="E52" s="20">
         <f>D52</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="str">
         <f>IF(D52=E52,"n/a",IF(OR(C52="battery electric vehicle",C52="natural gas vehicle",C52="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -19687,127 +22314,127 @@
       </c>
       <c r="H52" s="20">
         <f t="shared" si="27"/>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="I52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,I$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="J52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,J$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="K52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,K$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="L52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,L$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="M52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,M$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="N52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,N$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="O52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,O$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="P52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,P$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="Q52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,Q$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="R52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,R$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="S52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,S$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="T52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,T$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="U52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,U$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="V52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,V$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="W52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,W$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="X52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,X$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="Y52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,Y$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="Z52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,Z$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AA52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,AA$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AB52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,AB$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AC52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,AC$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AD52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,AD$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AE52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,AE$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AF52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,AF$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AG52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,AG$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AH52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,AH$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AI52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,AI$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AJ52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,AJ$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AK52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,AK$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
       <c r="AL52">
         <f>IF($F52="s-curve",$D52+($E52-$D52)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D52:$E52,$D$9:$E$9,AL$9))</f>
-        <v>0.76226911968156119</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:38">
@@ -20097,12 +22724,11 @@
         <v>4</v>
       </c>
       <c r="D55" s="20">
-        <f>MIN(1.25*INDEX('SYVbT-passenger'!$B$5:$H$5,MATCH(Data!$C13,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-passenger'!$B$5:$H$5),1)</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="E55" s="20">
         <f t="shared" si="28"/>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="F55" s="6" t="str">
         <f>IF(D55=E55,"n/a",IF(OR(C55="battery electric vehicle",C55="natural gas vehicle",C55="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -20110,127 +22736,127 @@
       </c>
       <c r="H55" s="20">
         <f t="shared" si="27"/>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="I55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,I$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="J55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,J$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="K55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,K$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="L55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,L$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="M55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,M$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="N55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,N$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="O55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,O$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="P55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,P$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="Q55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,Q$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="R55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,R$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="S55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,S$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="T55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,T$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="U55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,U$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="V55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,V$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="W55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,W$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="X55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,X$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="Y55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,Y$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="Z55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,Z$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AA55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,AA$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AB55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,AB$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AC55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,AC$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AD55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,AD$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AE55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,AE$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AF55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,AF$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AG55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,AG$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AH55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,AH$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AI55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,AI$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AJ55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,AJ$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AK55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,AK$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
       <c r="AL55">
         <f>IF($F55="s-curve",$D55+($E55-$D55)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D55:$E55,$D$9:$E$9,AL$9))</f>
-        <v>0.48773088031843881</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="56" spans="1:38">
@@ -20669,12 +23295,11 @@
         <v>1</v>
       </c>
       <c r="D59">
-        <f>MIN(1.25*INDEX('SYVbT-freight'!$B$5:$H$5,MATCH(Data!$C10,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-freight'!$B$5:$H$5),1)</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="E59">
         <f>D59</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="F59" s="6" t="str">
         <f>IF(D59=E59,"n/a",IF(OR(C59="battery electric vehicle",C59="natural gas vehicle",C59="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -20682,127 +23307,127 @@
       </c>
       <c r="H59" s="20">
         <f t="shared" si="27"/>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="I59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,I$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="J59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,J$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="K59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,K$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="L59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,L$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="M59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,M$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="N59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,N$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="O59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,O$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="P59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,P$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="Q59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,Q$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="R59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,R$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="S59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,S$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="T59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,T$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="U59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,U$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="V59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,V$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="W59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,W$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="X59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,X$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="Y59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,Y$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="Z59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,Z$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AA59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,AA$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AB59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,AB$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AC59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,AC$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AD59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,AD$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AE59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,AE$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AF59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,AF$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AG59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,AG$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AH59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,AH$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AI59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,AI$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AJ59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,AJ$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AK59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,AK$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
       <c r="AL59">
         <f>IF($F59="s-curve",$D59+($E59-$D59)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D59:$E59,$D$9:$E$9,AL$9))</f>
-        <v>0.50990675990675993</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="60" spans="1:38">
@@ -21092,12 +23717,11 @@
         <v>4</v>
       </c>
       <c r="D62">
-        <f>MIN(1.25*INDEX('SYVbT-freight'!$B$5:$H$5,MATCH(Data!$C13,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-freight'!$B$5:$H$5),1)</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="E62">
         <f t="shared" si="29"/>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="str">
         <f>IF(D62=E62,"n/a",IF(OR(C62="battery electric vehicle",C62="natural gas vehicle",C62="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -21105,127 +23729,127 @@
       </c>
       <c r="H62" s="20">
         <f t="shared" si="27"/>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="I62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,I$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="J62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,J$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="K62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,K$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="L62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,L$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="M62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,M$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="N62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,N$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="O62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,O$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="P62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,P$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="Q62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,Q$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="R62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,R$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="S62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,S$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="T62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,T$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="U62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,U$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="V62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,V$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="W62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,W$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="X62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,X$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="Y62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,Y$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="Z62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,Z$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AA62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,AA$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AB62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,AB$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AC62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,AC$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AD62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,AD$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AE62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,AE$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AF62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,AF$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AG62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,AG$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AH62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,AH$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AI62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,AI$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AJ62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,AJ$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AK62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,AK$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
       <c r="AL62">
         <f>IF($F62="s-curve",$D62+($E62-$D62)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D62:$E62,$D$9:$E$9,AL$9))</f>
-        <v>0.74009324009324007</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:38">
@@ -25617,7 +28241,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -25763,43 +28387,43 @@
       </c>
       <c r="B2">
         <f>Data!H10</f>
-        <v>7.5738458244009904E-2</v>
+        <v>7.3490200174101794E-2</v>
       </c>
       <c r="C2">
         <f>Data!I10</f>
-        <v>7.5738458244009904E-2</v>
+        <v>7.3490200174101794E-2</v>
       </c>
       <c r="D2">
         <f>Data!J10</f>
-        <v>0.16254791306372199</v>
+        <v>0.157825313074512</v>
       </c>
       <c r="E2">
         <f>Data!K10</f>
-        <v>0.13456250619976501</v>
+        <v>0.13005309903783399</v>
       </c>
       <c r="F2">
         <f>Data!L10</f>
-        <v>0.17887325579206301</v>
+        <v>0.17042213170193199</v>
       </c>
       <c r="G2">
         <f>Data!M10</f>
-        <v>0.28035657357026</v>
+        <v>0.26665968836382897</v>
       </c>
       <c r="H2">
         <f>Data!N10</f>
-        <v>0.32028525885620801</v>
+        <v>0.30932775069106316</v>
       </c>
       <c r="I2">
         <f>Data!O10</f>
-        <v>0.36021394414215602</v>
+        <v>0.35199581301829735</v>
       </c>
       <c r="J2">
         <f>Data!P10</f>
-        <v>0.40014262942810402</v>
+        <v>0.39466387534553155</v>
       </c>
       <c r="K2">
         <f>Data!Q10</f>
-        <v>0.44007131471405203</v>
+        <v>0.43733193767276574</v>
       </c>
       <c r="L2">
         <f>Data!R10</f>
@@ -25892,127 +28516,127 @@
       </c>
       <c r="B3">
         <f>Data!H11</f>
-        <v>3.3111542696076198E-3</v>
+        <v>3.3619455883161201E-3</v>
       </c>
       <c r="C3">
         <f>Data!I11</f>
-        <v>3.3111542696076198E-3</v>
+        <v>3.3619455883161201E-3</v>
       </c>
       <c r="D3">
         <f>Data!J11</f>
-        <v>3.18875302069616E-3</v>
+        <v>3.2366567758692999E-3</v>
       </c>
       <c r="E3">
         <f>Data!K11</f>
-        <v>3.2416232692108801E-3</v>
+        <v>3.3102715104686301E-3</v>
       </c>
       <c r="F3">
         <f>Data!L11</f>
-        <v>3.2401040027916599E-3</v>
+        <v>3.31078535598989E-3</v>
       </c>
       <c r="G3">
         <f>Data!M11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="H3">
         <f>Data!N11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="I3">
         <f>Data!O11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="J3">
         <f>Data!P11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="K3">
         <f>Data!Q11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="L3">
         <f>Data!R11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="M3">
         <f>Data!S11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="N3">
         <f>Data!T11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="O3">
         <f>Data!U11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="P3">
         <f>Data!V11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="Q3">
         <f>Data!W11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="R3">
         <f>Data!X11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="S3">
         <f>Data!Y11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="T3">
         <f>Data!Z11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="U3">
         <f>Data!AA11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="V3">
         <f>Data!AB11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="W3">
         <f>Data!AC11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="X3">
         <f>Data!AD11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="Y3">
         <f>Data!AE11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="Z3">
         <f>Data!AF11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AA3">
         <f>Data!AG11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AB3">
         <f>Data!AH11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AC3">
         <f>Data!AI11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AD3">
         <f>Data!AJ11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AE3">
         <f>Data!AK11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
       <c r="AF3">
         <f>Data!AL11</f>
-        <v>3.2380317148955899E-3</v>
+        <v>3.30901198145427E-3</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -26150,127 +28774,127 @@
       </c>
       <c r="B5">
         <f>Data!H13</f>
-        <v>0.58713757439567404</v>
+        <v>0.59258194130892095</v>
       </c>
       <c r="C5">
         <f>Data!I13</f>
-        <v>0.58713757439567404</v>
+        <v>0.59258194130892095</v>
       </c>
       <c r="D5">
         <f>Data!J13</f>
-        <v>0.58625646954423505</v>
+        <v>0.59256250147626899</v>
       </c>
       <c r="E5">
         <f>Data!K13</f>
-        <v>0.58587879933822895</v>
+        <v>0.592196165783894</v>
       </c>
       <c r="F5">
         <f>Data!L13</f>
-        <v>0.58568402014887</v>
+        <v>0.592014678526816</v>
       </c>
       <c r="G5">
         <f>Data!M13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="H5">
         <f>Data!N13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="I5">
         <f>Data!O13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="J5">
         <f>Data!P13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="K5">
         <f>Data!Q13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="L5">
         <f>Data!R13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="M5">
         <f>Data!S13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="N5">
         <f>Data!T13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="O5">
         <f>Data!U13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="P5">
         <f>Data!V13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="Q5">
         <f>Data!W13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="R5">
         <f>Data!X13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="S5">
         <f>Data!Y13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="T5">
         <f>Data!Z13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="U5">
         <f>Data!AA13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="V5">
         <f>Data!AB13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="W5">
         <f>Data!AC13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="X5">
         <f>Data!AD13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="Y5">
         <f>Data!AE13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="Z5">
         <f>Data!AF13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AA5">
         <f>Data!AG13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AB5">
         <f>Data!AH13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AC5">
         <f>Data!AI13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AD5">
         <f>Data!AJ13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AE5">
         <f>Data!AK13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
       <c r="AF5">
         <f>Data!AL13</f>
-        <v>0.58477756179805596</v>
+        <v>0.59122138352735099</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -26279,43 +28903,43 @@
       </c>
       <c r="B6">
         <f>Data!H14</f>
-        <v>3.0097006982601999E-2</v>
+        <v>2.68592624324243E-2</v>
       </c>
       <c r="C6">
         <f>Data!I14</f>
-        <v>3.0097006982601999E-2</v>
+        <v>2.68592624324243E-2</v>
       </c>
       <c r="D6">
         <f>Data!J14</f>
-        <v>2.1911439020317398E-2</v>
+        <v>1.94058745124292E-2</v>
       </c>
       <c r="E6">
         <f>Data!K14</f>
-        <v>2.0681798718551799E-2</v>
+        <v>1.8171220012969998E-2</v>
       </c>
       <c r="F6">
         <f>Data!L14</f>
-        <v>1.91330462605762E-2</v>
+        <v>1.64374786444835E-2</v>
       </c>
       <c r="G6">
         <f>Data!M14</f>
-        <v>2.67214247564647E-2</v>
+        <v>2.2877517710931699E-2</v>
       </c>
       <c r="H6">
         <f>Data!N14</f>
-        <v>3.097713980517176E-2</v>
+        <v>2.7902014168745361E-2</v>
       </c>
       <c r="I6">
         <f>Data!O14</f>
-        <v>3.5232854853878823E-2</v>
+        <v>3.2926510626559019E-2</v>
       </c>
       <c r="J6">
         <f>Data!P14</f>
-        <v>3.9488569902585882E-2</v>
+        <v>3.7951007084372677E-2</v>
       </c>
       <c r="K6">
         <f>Data!Q14</f>
-        <v>4.3744284951292942E-2</v>
+        <v>4.2975503542186336E-2</v>
       </c>
       <c r="L6">
         <f>Data!R14</f>
@@ -26408,127 +29032,127 @@
       </c>
       <c r="B7">
         <f>Data!H15</f>
-        <v>0.169435072322971</v>
+        <v>0.171228650249552</v>
       </c>
       <c r="C7">
         <f>Data!I15</f>
-        <v>0.169435072322971</v>
+        <v>0.171228650249552</v>
       </c>
       <c r="D7">
         <f>Data!J15</f>
-        <v>0.15875306561484401</v>
+        <v>0.160575453689589</v>
       </c>
       <c r="E7">
         <f>Data!K15</f>
-        <v>0.158538746497771</v>
+        <v>0.16035867432016401</v>
       </c>
       <c r="F7">
         <f>Data!L15</f>
-        <v>0.15840837270788899</v>
+        <v>0.16022472098401899</v>
       </c>
       <c r="G7">
         <f>Data!M15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="H7">
         <f>Data!N15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="I7">
         <f>Data!O15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="J7">
         <f>Data!P15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="K7">
         <f>Data!Q15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="L7">
         <f>Data!R15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="M7">
         <f>Data!S15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="N7">
         <f>Data!T15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="O7">
         <f>Data!U15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="P7">
         <f>Data!V15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="Q7">
         <f>Data!W15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="R7">
         <f>Data!X15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="S7">
         <f>Data!Y15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="T7">
         <f>Data!Z15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="U7">
         <f>Data!AA15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="V7">
         <f>Data!AB15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="W7">
         <f>Data!AC15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="X7">
         <f>Data!AD15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="Y7">
         <f>Data!AE15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="Z7">
         <f>Data!AF15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AA7">
         <f>Data!AG15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AB7">
         <f>Data!AH15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AC7">
         <f>Data!AI15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AD7">
         <f>Data!AJ15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AE7">
         <f>Data!AK15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
       <c r="AF7">
         <f>Data!AL15</f>
-        <v>0.15795852186818499</v>
+        <v>0.15979463806628899</v>
       </c>
     </row>
     <row r="8" spans="1:32">
@@ -26537,127 +29161,127 @@
       </c>
       <c r="B8">
         <f>Data!H16</f>
-        <v>1.5971754362172401E-2</v>
+        <v>1.3775185340645301E-2</v>
       </c>
       <c r="C8">
         <f>Data!I16</f>
-        <v>1.5971754362172401E-2</v>
+        <v>1.3775185340645301E-2</v>
       </c>
       <c r="D8">
         <f>Data!J16</f>
-        <v>1.7435929211407498E-2</v>
+        <v>1.50499244982964E-2</v>
       </c>
       <c r="E8">
         <f>Data!K16</f>
-        <v>6.9483671683743999E-3</v>
+        <v>5.9981476236627097E-3</v>
       </c>
       <c r="F8">
         <f>Data!L16</f>
-        <v>4.5730323634844599E-3</v>
+        <v>3.9475989042041899E-3</v>
       </c>
       <c r="G8">
         <f>Data!M16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="H8">
         <f>Data!N16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="I8">
         <f>Data!O16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="J8">
         <f>Data!P16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="K8">
         <f>Data!Q16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="L8">
         <f>Data!R16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="M8">
         <f>Data!S16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="N8">
         <f>Data!T16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="O8">
         <f>Data!U16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="P8">
         <f>Data!V16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="Q8">
         <f>Data!W16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="R8">
         <f>Data!X16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="S8">
         <f>Data!Y16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="T8">
         <f>Data!Z16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="U8">
         <f>Data!AA16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="V8">
         <f>Data!AB16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="W8">
         <f>Data!AC16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="X8">
         <f>Data!AD16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="Y8">
         <f>Data!AE16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="Z8">
         <f>Data!AF16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AA8">
         <f>Data!AG16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AB8">
         <f>Data!AH16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AC8">
         <f>Data!AI16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AD8">
         <f>Data!AJ16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AE8">
         <f>Data!AK16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
       <c r="AF8">
         <f>Data!AL16</f>
-        <v>9.4692125755478501E-3</v>
+        <v>8.1683077230845901E-3</v>
       </c>
     </row>
   </sheetData>
@@ -26666,7 +29290,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -26812,127 +29436,127 @@
       </c>
       <c r="B2">
         <f>Data!H17</f>
-        <v>5.3683612196023132E-3</v>
+        <v>0.05</v>
       </c>
       <c r="C2">
         <f>Data!I17</f>
-        <v>2.0063080574076027E-2</v>
+        <v>5.6648314261972879E-2</v>
       </c>
       <c r="D2">
         <f>Data!J17</f>
-        <v>2.5102157025791948E-2</v>
+        <v>5.8928137580334883E-2</v>
       </c>
       <c r="E2">
         <f>Data!K17</f>
-        <v>3.1822572527592123E-2</v>
+        <v>6.1968647109589645E-2</v>
       </c>
       <c r="F2">
         <f>Data!L17</f>
-        <v>4.0748591499212138E-2</v>
+        <v>6.6007035172686288E-2</v>
       </c>
       <c r="G2">
         <f>Data!M17</f>
-        <v>5.2539635178796867E-2</v>
+        <v>7.1341642929905053E-2</v>
       </c>
       <c r="H2">
         <f>Data!N17</f>
-        <v>6.8003653554074228E-2</v>
+        <v>7.833801022564843E-2</v>
       </c>
       <c r="I2">
         <f>Data!O17</f>
-        <v>8.8094556635136961E-2</v>
+        <v>8.7427713422265074E-2</v>
       </c>
       <c r="J2">
         <f>Data!P17</f>
-        <v>0.11387951127112682</v>
+        <v>9.9093569538025811E-2</v>
       </c>
       <c r="K2">
         <f>Data!Q17</f>
-        <v>0.14645791836431907</v>
+        <v>0.11383297920521952</v>
       </c>
       <c r="L2">
         <f>Data!R17</f>
-        <v>0.186814558918491</v>
+        <v>0.13209148571286036</v>
       </c>
       <c r="M2">
         <f>Data!S17</f>
-        <v>0.23560093514502178</v>
+        <v>0.15416384742544209</v>
       </c>
       <c r="N2">
         <f>Data!T17</f>
-        <v>0.29286713111398371</v>
+        <v>0.18007272381874823</v>
       </c>
       <c r="O2">
         <f>Data!U17</f>
-        <v>0.35780981004973877</v>
+        <v>0.20945466219839204</v>
       </c>
       <c r="P2">
         <f>Data!V17</f>
-        <v>0.4286412981184835</v>
+        <v>0.24150086743475346</v>
       </c>
       <c r="Q2">
         <f>Data!W17</f>
-        <v>0.50268418060980113</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="R2">
         <f>Data!X17</f>
-        <v>0.57672706310111888</v>
+        <v>0.30849913256524658</v>
       </c>
       <c r="S2">
         <f>Data!Y17</f>
-        <v>0.64755855116986349</v>
+        <v>0.34054533780160795</v>
       </c>
       <c r="T2">
         <f>Data!Z17</f>
-        <v>0.71250123010561861</v>
+        <v>0.36992727618125176</v>
       </c>
       <c r="U2">
         <f>Data!AA17</f>
-        <v>0.76976742607458049</v>
+        <v>0.3958361525745579</v>
       </c>
       <c r="V2">
         <f>Data!AB17</f>
-        <v>0.8185538023011113</v>
+        <v>0.4179085142871396</v>
       </c>
       <c r="W2">
         <f>Data!AC17</f>
-        <v>0.85891044285528328</v>
+        <v>0.43616702079478054</v>
       </c>
       <c r="X2">
         <f>Data!AD17</f>
-        <v>0.89148884994847555</v>
+        <v>0.45090643046197421</v>
       </c>
       <c r="Y2">
         <f>Data!AE17</f>
-        <v>0.91727380458446539</v>
+        <v>0.46257228657773497</v>
       </c>
       <c r="Z2">
         <f>Data!AF17</f>
-        <v>0.93736470766552815</v>
+        <v>0.47166198977435159</v>
       </c>
       <c r="AA2">
         <f>Data!AG17</f>
-        <v>0.95282872604080548</v>
+        <v>0.47865835707009496</v>
       </c>
       <c r="AB2">
         <f>Data!AH17</f>
-        <v>0.96461976972039021</v>
+        <v>0.48399296482731374</v>
       </c>
       <c r="AC2">
         <f>Data!AI17</f>
-        <v>0.97354578869201014</v>
+        <v>0.48803135289041033</v>
       </c>
       <c r="AD2">
         <f>Data!AJ17</f>
-        <v>0.98026620419381039</v>
+        <v>0.49107186241966516</v>
       </c>
       <c r="AE2">
         <f>Data!AK17</f>
-        <v>0.98530528064552625</v>
+        <v>0.49335168573802712</v>
       </c>
       <c r="AF2">
         <f>Data!AL17</f>
-        <v>0.98907203924614695</v>
+        <v>0.49505587581623306</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -27715,7 +30339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -27861,127 +30485,127 @@
       </c>
       <c r="B2">
         <f>Data!H24</f>
-        <v>7.2747216149611415E-3</v>
+        <v>0.05</v>
       </c>
       <c r="C2">
         <f>Data!I24</f>
-        <v>1.8986470001880411E-2</v>
+        <v>6.4035330108609401E-2</v>
       </c>
       <c r="D2">
         <f>Data!J24</f>
-        <v>2.3002633501252021E-2</v>
+        <v>6.8848290447373631E-2</v>
       </c>
       <c r="E2">
         <f>Data!K24</f>
-        <v>2.8358830752387227E-2</v>
+        <v>7.5267143898022582E-2</v>
       </c>
       <c r="F2">
         <f>Data!L24</f>
-        <v>3.5472902533598569E-2</v>
+        <v>8.3792629809004371E-2</v>
       </c>
       <c r="G2">
         <f>Data!M24</f>
-        <v>4.4870410132301322E-2</v>
+        <v>9.505457951868844E-2</v>
       </c>
       <c r="H2">
         <f>Data!N24</f>
-        <v>5.7195292826083877E-2</v>
+        <v>0.10982468825414668</v>
       </c>
       <c r="I2">
         <f>Data!O24</f>
-        <v>7.3207820597140094E-2</v>
+        <v>0.12901406166922624</v>
       </c>
       <c r="J2">
         <f>Data!P24</f>
-        <v>9.3758529568176208E-2</v>
+        <v>0.15364198013583227</v>
       </c>
       <c r="K2">
         <f>Data!Q24</f>
-        <v>0.11972364652741456</v>
+        <v>0.18475851165546342</v>
       </c>
       <c r="L2">
         <f>Data!R24</f>
-        <v>0.15188804575889153</v>
+        <v>0.22330424761603851</v>
       </c>
       <c r="M2">
         <f>Data!S24</f>
-        <v>0.19077097705493956</v>
+        <v>0.26990145567593327</v>
       </c>
       <c r="N2">
         <f>Data!T24</f>
-        <v>0.23641235761388887</v>
+        <v>0.32459797250624622</v>
       </c>
       <c r="O2">
         <f>Data!U24</f>
-        <v>0.28817192490610039</v>
+        <v>0.38662650908549429</v>
       </c>
       <c r="P2">
         <f>Data!V24</f>
-        <v>0.34462489594427526</v>
+        <v>0.45427960902892389</v>
       </c>
       <c r="Q2">
         <f>Data!W24</f>
-        <v>0.40363736080748058</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="R2">
         <f>Data!X24</f>
-        <v>0.46264982567068591</v>
+        <v>0.5957203909710761</v>
       </c>
       <c r="S2">
         <f>Data!Y24</f>
-        <v>0.51910279670886073</v>
+        <v>0.6633734909145057</v>
       </c>
       <c r="T2">
         <f>Data!Z24</f>
-        <v>0.57086236400107226</v>
+        <v>0.72540202749375371</v>
       </c>
       <c r="U2">
         <f>Data!AA24</f>
-        <v>0.61650374456002166</v>
+        <v>0.78009854432406667</v>
       </c>
       <c r="V2">
         <f>Data!AB24</f>
-        <v>0.65538667585606958</v>
+        <v>0.82669575238396142</v>
       </c>
       <c r="W2">
         <f>Data!AC24</f>
-        <v>0.68755107508754665</v>
+        <v>0.86524148834453662</v>
       </c>
       <c r="X2">
         <f>Data!AD24</f>
-        <v>0.71351619204678496</v>
+        <v>0.89635801986416774</v>
       </c>
       <c r="Y2">
         <f>Data!AE24</f>
-        <v>0.73406690101782113</v>
+        <v>0.9209859383307738</v>
       </c>
       <c r="Z2">
         <f>Data!AF24</f>
-        <v>0.75007942878887734</v>
+        <v>0.94017531174585334</v>
       </c>
       <c r="AA2">
         <f>Data!AG24</f>
-        <v>0.76240431148265997</v>
+        <v>0.9549454204813117</v>
       </c>
       <c r="AB2">
         <f>Data!AH24</f>
-        <v>0.77180181908136269</v>
+        <v>0.96620737019099567</v>
       </c>
       <c r="AC2">
         <f>Data!AI24</f>
-        <v>0.77891589086257396</v>
+        <v>0.97473285610197735</v>
       </c>
       <c r="AD2">
         <f>Data!AJ24</f>
-        <v>0.78427208811370919</v>
+        <v>0.98115170955262643</v>
       </c>
       <c r="AE2">
         <f>Data!AK24</f>
-        <v>0.7882882516130808</v>
+        <v>0.98596466989139064</v>
       </c>
       <c r="AF2">
         <f>Data!AL24</f>
-        <v>0.79129037284456261</v>
+        <v>0.98956240450093647</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -28756,1055 +31380,6 @@
       <c r="AF8">
         <f>Data!AL30</f>
         <v>2.1395689946999558E-3</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:32" ht="45">
-      <c r="A1" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1">
-        <f>Data!H9</f>
-        <v>2020</v>
-      </c>
-      <c r="C1">
-        <f>Data!I9</f>
-        <v>2021</v>
-      </c>
-      <c r="D1">
-        <f>Data!J9</f>
-        <v>2022</v>
-      </c>
-      <c r="E1">
-        <f>Data!K9</f>
-        <v>2023</v>
-      </c>
-      <c r="F1">
-        <f>Data!L9</f>
-        <v>2024</v>
-      </c>
-      <c r="G1">
-        <f>Data!M9</f>
-        <v>2025</v>
-      </c>
-      <c r="H1">
-        <f>Data!N9</f>
-        <v>2026</v>
-      </c>
-      <c r="I1">
-        <f>Data!O9</f>
-        <v>2027</v>
-      </c>
-      <c r="J1">
-        <f>Data!P9</f>
-        <v>2028</v>
-      </c>
-      <c r="K1">
-        <f>Data!Q9</f>
-        <v>2029</v>
-      </c>
-      <c r="L1">
-        <f>Data!R9</f>
-        <v>2030</v>
-      </c>
-      <c r="M1">
-        <f>Data!S9</f>
-        <v>2031</v>
-      </c>
-      <c r="N1">
-        <f>Data!T9</f>
-        <v>2032</v>
-      </c>
-      <c r="O1">
-        <f>Data!U9</f>
-        <v>2033</v>
-      </c>
-      <c r="P1">
-        <f>Data!V9</f>
-        <v>2034</v>
-      </c>
-      <c r="Q1">
-        <f>Data!W9</f>
-        <v>2035</v>
-      </c>
-      <c r="R1">
-        <f>Data!X9</f>
-        <v>2036</v>
-      </c>
-      <c r="S1">
-        <f>Data!Y9</f>
-        <v>2037</v>
-      </c>
-      <c r="T1">
-        <f>Data!Z9</f>
-        <v>2038</v>
-      </c>
-      <c r="U1">
-        <f>Data!AA9</f>
-        <v>2039</v>
-      </c>
-      <c r="V1">
-        <f>Data!AB9</f>
-        <v>2040</v>
-      </c>
-      <c r="W1">
-        <f>Data!AC9</f>
-        <v>2041</v>
-      </c>
-      <c r="X1">
-        <f>Data!AD9</f>
-        <v>2042</v>
-      </c>
-      <c r="Y1">
-        <f>Data!AE9</f>
-        <v>2043</v>
-      </c>
-      <c r="Z1">
-        <f>Data!AF9</f>
-        <v>2044</v>
-      </c>
-      <c r="AA1">
-        <f>Data!AG9</f>
-        <v>2045</v>
-      </c>
-      <c r="AB1">
-        <f>Data!AH9</f>
-        <v>2046</v>
-      </c>
-      <c r="AC1">
-        <f>Data!AI9</f>
-        <v>2047</v>
-      </c>
-      <c r="AD1">
-        <f>Data!AJ9</f>
-        <v>2048</v>
-      </c>
-      <c r="AE1">
-        <f>Data!AK9</f>
-        <v>2049</v>
-      </c>
-      <c r="AF1">
-        <f>Data!AL9</f>
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <f>Data!H31</f>
-        <v>5.3709944550863111E-3</v>
-      </c>
-      <c r="C2">
-        <f>Data!I31</f>
-        <v>1.7110868567400919E-2</v>
-      </c>
-      <c r="D2">
-        <f>Data!J31</f>
-        <v>2.1136676870263375E-2</v>
-      </c>
-      <c r="E2">
-        <f>Data!K31</f>
-        <v>2.6505737011555695E-2</v>
-      </c>
-      <c r="F2">
-        <f>Data!L31</f>
-        <v>3.3636893212851106E-2</v>
-      </c>
-      <c r="G2">
-        <f>Data!M31</f>
-        <v>4.3056968895275403E-2</v>
-      </c>
-      <c r="H2">
-        <f>Data!N31</f>
-        <v>5.541144975448322E-2</v>
-      </c>
-      <c r="I2">
-        <f>Data!O31</f>
-        <v>7.1462431558540776E-2</v>
-      </c>
-      <c r="J2">
-        <f>Data!P31</f>
-        <v>9.2062492989867475E-2</v>
-      </c>
-      <c r="K2">
-        <f>Data!Q31</f>
-        <v>0.11808996509244796</v>
-      </c>
-      <c r="L2">
-        <f>Data!R31</f>
-        <v>0.15033160702334125</v>
-      </c>
-      <c r="M2">
-        <f>Data!S31</f>
-        <v>0.18930791555155554</v>
-      </c>
-      <c r="N2">
-        <f>Data!T31</f>
-        <v>0.23505890373644214</v>
-      </c>
-      <c r="O2">
-        <f>Data!U31</f>
-        <v>0.28694277145999392</v>
-      </c>
-      <c r="P2">
-        <f>Data!V31</f>
-        <v>0.34353131412323407</v>
-      </c>
-      <c r="Q2">
-        <f>Data!W31</f>
-        <v>0.40268549722754321</v>
-      </c>
-      <c r="R2">
-        <f>Data!X31</f>
-        <v>0.46183968033185235</v>
-      </c>
-      <c r="S2">
-        <f>Data!Y31</f>
-        <v>0.51842822299509239</v>
-      </c>
-      <c r="T2">
-        <f>Data!Z31</f>
-        <v>0.57031209071864419</v>
-      </c>
-      <c r="U2">
-        <f>Data!AA31</f>
-        <v>0.61606307890353074</v>
-      </c>
-      <c r="V2">
-        <f>Data!AB31</f>
-        <v>0.65503938743174506</v>
-      </c>
-      <c r="W2">
-        <f>Data!AC31</f>
-        <v>0.68728102936263846</v>
-      </c>
-      <c r="X2">
-        <f>Data!AD31</f>
-        <v>0.71330850146521885</v>
-      </c>
-      <c r="Y2">
-        <f>Data!AE31</f>
-        <v>0.7339085628965456</v>
-      </c>
-      <c r="Z2">
-        <f>Data!AF31</f>
-        <v>0.74995954470060322</v>
-      </c>
-      <c r="AA2">
-        <f>Data!AG31</f>
-        <v>0.76231402555981098</v>
-      </c>
-      <c r="AB2">
-        <f>Data!AH31</f>
-        <v>0.77173410124223529</v>
-      </c>
-      <c r="AC2">
-        <f>Data!AI31</f>
-        <v>0.77886525744353063</v>
-      </c>
-      <c r="AD2">
-        <f>Data!AJ31</f>
-        <v>0.78423431758482298</v>
-      </c>
-      <c r="AE2">
-        <f>Data!AK31</f>
-        <v>0.78826012588768546</v>
-      </c>
-      <c r="AF2">
-        <f>Data!AL31</f>
-        <v>0.79126945670347282</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <f>Data!H32</f>
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <f>Data!I32</f>
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <f>Data!J32</f>
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <f>Data!K32</f>
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <f>Data!L32</f>
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <f>Data!M32</f>
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <f>Data!N32</f>
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <f>Data!O32</f>
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <f>Data!P32</f>
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <f>Data!Q32</f>
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <f>Data!R32</f>
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <f>Data!S32</f>
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <f>Data!T32</f>
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <f>Data!U32</f>
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <f>Data!V32</f>
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <f>Data!W32</f>
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <f>Data!X32</f>
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <f>Data!Y32</f>
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <f>Data!Z32</f>
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <f>Data!AA32</f>
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <f>Data!AB32</f>
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <f>Data!AC32</f>
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <f>Data!AD32</f>
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <f>Data!AE32</f>
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <f>Data!AF32</f>
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <f>Data!AG32</f>
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <f>Data!AH32</f>
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <f>Data!AI32</f>
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <f>Data!AJ32</f>
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <f>Data!AK32</f>
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <f>Data!AL32</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <f>Data!H33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="C4">
-        <f>Data!I33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="D4">
-        <f>Data!J33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="E4">
-        <f>Data!K33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="F4">
-        <f>Data!L33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="G4">
-        <f>Data!M33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="H4">
-        <f>Data!N33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="I4">
-        <f>Data!O33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="J4">
-        <f>Data!P33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="K4">
-        <f>Data!Q33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="L4">
-        <f>Data!R33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="M4">
-        <f>Data!S33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="N4">
-        <f>Data!T33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="O4">
-        <f>Data!U33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="P4">
-        <f>Data!V33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="Q4">
-        <f>Data!W33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="R4">
-        <f>Data!X33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="S4">
-        <f>Data!Y33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="T4">
-        <f>Data!Z33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="U4">
-        <f>Data!AA33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="V4">
-        <f>Data!AB33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="W4">
-        <f>Data!AC33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="X4">
-        <f>Data!AD33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="Y4">
-        <f>Data!AE33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="Z4">
-        <f>Data!AF33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="AA4">
-        <f>Data!AG33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="AB4">
-        <f>Data!AH33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="AC4">
-        <f>Data!AI33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="AD4">
-        <f>Data!AJ33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="AE4">
-        <f>Data!AK33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-      <c r="AF4">
-        <f>Data!AL33</f>
-        <v>1.9195530379555355E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <f>Data!H34</f>
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <f>Data!I34</f>
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <f>Data!J34</f>
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <f>Data!K34</f>
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <f>Data!L34</f>
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <f>Data!M34</f>
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <f>Data!N34</f>
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <f>Data!O34</f>
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <f>Data!P34</f>
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <f>Data!Q34</f>
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <f>Data!R34</f>
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <f>Data!S34</f>
-        <v>3</v>
-      </c>
-      <c r="N5">
-        <f>Data!T34</f>
-        <v>3</v>
-      </c>
-      <c r="O5">
-        <f>Data!U34</f>
-        <v>3</v>
-      </c>
-      <c r="P5">
-        <f>Data!V34</f>
-        <v>3</v>
-      </c>
-      <c r="Q5">
-        <f>Data!W34</f>
-        <v>3</v>
-      </c>
-      <c r="R5">
-        <f>Data!X34</f>
-        <v>3</v>
-      </c>
-      <c r="S5">
-        <f>Data!Y34</f>
-        <v>3</v>
-      </c>
-      <c r="T5">
-        <f>Data!Z34</f>
-        <v>3</v>
-      </c>
-      <c r="U5">
-        <f>Data!AA34</f>
-        <v>3</v>
-      </c>
-      <c r="V5">
-        <f>Data!AB34</f>
-        <v>3</v>
-      </c>
-      <c r="W5">
-        <f>Data!AC34</f>
-        <v>3</v>
-      </c>
-      <c r="X5">
-        <f>Data!AD34</f>
-        <v>3</v>
-      </c>
-      <c r="Y5">
-        <f>Data!AE34</f>
-        <v>3</v>
-      </c>
-      <c r="Z5">
-        <f>Data!AF34</f>
-        <v>3</v>
-      </c>
-      <c r="AA5">
-        <f>Data!AG34</f>
-        <v>3</v>
-      </c>
-      <c r="AB5">
-        <f>Data!AH34</f>
-        <v>3</v>
-      </c>
-      <c r="AC5">
-        <f>Data!AI34</f>
-        <v>3</v>
-      </c>
-      <c r="AD5">
-        <f>Data!AJ34</f>
-        <v>3</v>
-      </c>
-      <c r="AE5">
-        <f>Data!AK34</f>
-        <v>3</v>
-      </c>
-      <c r="AF5">
-        <f>Data!AL34</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <f>Data!H35</f>
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <f>Data!I35</f>
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <f>Data!J35</f>
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <f>Data!K35</f>
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <f>Data!L35</f>
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <f>Data!M35</f>
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <f>Data!N35</f>
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <f>Data!O35</f>
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <f>Data!P35</f>
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <f>Data!Q35</f>
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <f>Data!R35</f>
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <f>Data!S35</f>
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <f>Data!T35</f>
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <f>Data!U35</f>
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <f>Data!V35</f>
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <f>Data!W35</f>
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <f>Data!X35</f>
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <f>Data!Y35</f>
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <f>Data!Z35</f>
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <f>Data!AA35</f>
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <f>Data!AB35</f>
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <f>Data!AC35</f>
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <f>Data!AD35</f>
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <f>Data!AE35</f>
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <f>Data!AF35</f>
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <f>Data!AG35</f>
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <f>Data!AH35</f>
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <f>Data!AI35</f>
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <f>Data!AJ35</f>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f>Data!AK35</f>
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <f>Data!AL35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32">
-      <c r="A7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7">
-        <f>Data!H36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="C7">
-        <f>Data!I36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="D7">
-        <f>Data!J36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="E7">
-        <f>Data!K36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="F7">
-        <f>Data!L36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="G7">
-        <f>Data!M36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="H7">
-        <f>Data!N36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="I7">
-        <f>Data!O36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="J7">
-        <f>Data!P36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="K7">
-        <f>Data!Q36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="L7">
-        <f>Data!R36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="M7">
-        <f>Data!S36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="N7">
-        <f>Data!T36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="O7">
-        <f>Data!U36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="P7">
-        <f>Data!V36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="Q7">
-        <f>Data!W36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="R7">
-        <f>Data!X36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="S7">
-        <f>Data!Y36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="T7">
-        <f>Data!Z36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="U7">
-        <f>Data!AA36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="V7">
-        <f>Data!AB36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="W7">
-        <f>Data!AC36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="X7">
-        <f>Data!AD36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="Y7">
-        <f>Data!AE36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="Z7">
-        <f>Data!AF36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="AA7">
-        <f>Data!AG36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="AB7">
-        <f>Data!AH36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="AC7">
-        <f>Data!AI36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="AD7">
-        <f>Data!AJ36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="AE7">
-        <f>Data!AK36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-      <c r="AF7">
-        <f>Data!AL36</f>
-        <v>4.2398960612661157E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32">
-      <c r="A8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8">
-        <f>Data!H37</f>
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <f>Data!I37</f>
-        <v>6.2640358785329186E-4</v>
-      </c>
-      <c r="D8">
-        <f>Data!J37</f>
-        <v>8.4120834136230764E-4</v>
-      </c>
-      <c r="E8">
-        <f>Data!K37</f>
-        <v>1.1276848830807375E-3</v>
-      </c>
-      <c r="F8">
-        <f>Data!L37</f>
-        <v>1.5081814529160165E-3</v>
-      </c>
-      <c r="G8">
-        <f>Data!M37</f>
-        <v>2.0108077288767171E-3</v>
-      </c>
-      <c r="H8">
-        <f>Data!N37</f>
-        <v>2.6700048431076819E-3</v>
-      </c>
-      <c r="I8">
-        <f>Data!O37</f>
-        <v>3.5264358826946353E-3</v>
-      </c>
-      <c r="J8">
-        <f>Data!P37</f>
-        <v>4.6255918248393289E-3</v>
-      </c>
-      <c r="K8">
-        <f>Data!Q37</f>
-        <v>6.0143377135798244E-3</v>
-      </c>
-      <c r="L8">
-        <f>Data!R37</f>
-        <v>7.7346525986097831E-3</v>
-      </c>
-      <c r="M8">
-        <f>Data!S37</f>
-        <v>9.8143085872323659E-3</v>
-      </c>
-      <c r="N8">
-        <f>Data!T37</f>
-        <v>1.2255440653272574E-2</v>
-      </c>
-      <c r="O8">
-        <f>Data!U37</f>
-        <v>1.5023804315677364E-2</v>
-      </c>
-      <c r="P8">
-        <f>Data!V37</f>
-        <v>1.8043194968125682E-2</v>
-      </c>
-      <c r="Q8">
-        <f>Data!W37</f>
-        <v>2.1199480306330579E-2</v>
-      </c>
-      <c r="R8">
-        <f>Data!X37</f>
-        <v>2.4355765644535475E-2</v>
-      </c>
-      <c r="S8">
-        <f>Data!Y37</f>
-        <v>2.7375156296983789E-2</v>
-      </c>
-      <c r="T8">
-        <f>Data!Z37</f>
-        <v>3.014351995938858E-2</v>
-      </c>
-      <c r="U8">
-        <f>Data!AA37</f>
-        <v>3.258465202542879E-2</v>
-      </c>
-      <c r="V8">
-        <f>Data!AB37</f>
-        <v>3.4664308014051376E-2</v>
-      </c>
-      <c r="W8">
-        <f>Data!AC37</f>
-        <v>3.6384622899081336E-2</v>
-      </c>
-      <c r="X8">
-        <f>Data!AD37</f>
-        <v>3.777336878782183E-2</v>
-      </c>
-      <c r="Y8">
-        <f>Data!AE37</f>
-        <v>3.8872524729966523E-2</v>
-      </c>
-      <c r="Z8">
-        <f>Data!AF37</f>
-        <v>3.972895576955348E-2</v>
-      </c>
-      <c r="AA8">
-        <f>Data!AG37</f>
-        <v>4.0388152883784445E-2</v>
-      </c>
-      <c r="AB8">
-        <f>Data!AH37</f>
-        <v>4.0890779159745143E-2</v>
-      </c>
-      <c r="AC8">
-        <f>Data!AI37</f>
-        <v>4.127127572958042E-2</v>
-      </c>
-      <c r="AD8">
-        <f>Data!AJ37</f>
-        <v>4.1557752271298855E-2</v>
-      </c>
-      <c r="AE8">
-        <f>Data!AK37</f>
-        <v>4.1772557024807866E-2</v>
-      </c>
-      <c r="AF8">
-        <f>Data!AL37</f>
-        <v>4.1933125664813074E-2</v>
       </c>
     </row>
   </sheetData>
@@ -29814,6 +31389,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -29957,15 +31541,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -29973,6 +31548,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39ACE987-BC54-40D9-B8CF-5CB9726AD5E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F78F0F71-EE7E-4036-B654-BDDC7E3F7269}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -29986,14 +31569,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39ACE987-BC54-40D9-B8CF-5CB9726AD5E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3C9C14-9940-445D-BC30-CC5F930CFE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDA3307-2CD3-4DD7-9E13-02826E172248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27810" yWindow="1095" windowWidth="27045" windowHeight="14940" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="105" yWindow="1020" windowWidth="24780" windowHeight="15165" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -969,76 +969,76 @@
                   <c:v>0.26665968836382897</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.30932775069106316</c:v>
+                  <c:v>0.30732775069106316</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.35199581301829735</c:v>
+                  <c:v>0.34799581301829735</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.39466387534553155</c:v>
+                  <c:v>0.38866387534553154</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.43733193767276574</c:v>
+                  <c:v>0.42933193767276573</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.48</c:v>
+                  <c:v>0.47</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.504</c:v>
+                  <c:v>0.49399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.52800000000000002</c:v>
+                  <c:v>0.51800000000000002</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.55200000000000005</c:v>
+                  <c:v>0.54200000000000004</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.57600000000000007</c:v>
+                  <c:v>0.56600000000000006</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.6</c:v>
+                  <c:v>0.59</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.64600000000000002</c:v>
+                  <c:v>0.63800000000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.69200000000000006</c:v>
+                  <c:v>0.68600000000000005</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.7380000000000001</c:v>
+                  <c:v>0.7340000000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.78400000000000014</c:v>
+                  <c:v>0.78200000000000014</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.83</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.94399999999999995</c:v>
+                  <c:v>0.94199999999999995</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.0579999999999998</c:v>
+                  <c:v>1.0539999999999998</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.1719999999999997</c:v>
+                  <c:v>1.1659999999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.2859999999999996</c:v>
+                  <c:v>1.278</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.4</c:v>
+                  <c:v>1.39</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.64</c:v>
+                  <c:v>1.6319999999999999</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.88</c:v>
+                  <c:v>1.8739999999999999</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2.12</c:v>
+                  <c:v>2.1160000000000001</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.3600000000000003</c:v>
+                  <c:v>2.3580000000000001</c:v>
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>2.6</c:v>
@@ -2629,7 +2629,672 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$H$17:$AL$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>7.0544063074398172E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.4079584901821705E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.8217690082670446E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.3058898649436469E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.8719689094453269E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.5334731417562879E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.1030593193881701</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.11207197371038144</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.12257716378808134</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.13480806298329293</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.14902920868037345</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.16553888225045485</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.18467095381410897</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.20679585237428799</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.2323202254775863</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.26168474967806649</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.29535945465707103</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.33383584804654387</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.37761510179865232</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.42719162064128996</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.48303150241407805</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.54554576385492282</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.61505877825632926</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.69177315955181817</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.77573328647560325</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.86679067488305006</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.96457528067354337</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.0684772912113583</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.1776437694307156</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.2909934561611893</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.4072510905610811</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A2F2-4315-AE68-ED008B054E39}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$H$31:$AL$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0" formatCode="0.0000">
+                  <c:v>5.3709944550863111E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.7759246766314107E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.1892147831648752E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.6727268054231088E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.2380939442073279E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.8987662632904812E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0670253609739368E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1570385603052314E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2619583469375369E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.3841135220834784E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.5261461327424669E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.691035241414475E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.882115350526798E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.103086091562989E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.3580088259556035E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.6512847772602481E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.9876083311579586E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.3718883827272901E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.8091303487097355E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.3042720587092277E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.861968629436756E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.486325059290683E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.1805810018505346E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.9467600483618303E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7.785305428056051E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>8.6947341668358144E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9.6713504774003714E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.10709063902446933</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.11799355797925228</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.12931427170136311</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.14092541448449677</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-A2F2-4315-AE68-ED008B054E39}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$H$24:$AL$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>9.7368870468605012E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1020789046319184</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10759170238132029</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11404117684484247</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.121582501064814</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.13039508287153292</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.14068580515101983</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.15269249379044036</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.166687543622766</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.1829815889913021</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.20192704749622634</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.22392129059128393</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.24940910118286383</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.27888396604439047</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.31288762241590307</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.3520071410965428</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.39686869722111495</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.44812707892302284</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.50644994917583175</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.57249595563398969</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.64688603541943279</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.73016774642367688</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.82277321984656737</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.92497237865716797</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.036824344355634</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.158131305861148</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.2884002891684831</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.4268188998171656</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.5722508521568517</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.7232556890554149</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.8781345036966268</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-A2F2-4315-AE68-ED008B054E39}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="346170191"/>
+        <c:axId val="346170671"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="346170191"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="346170671"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="346170671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="346170191"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3185,20 +3850,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>469071</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>59257</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>59258</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>595512</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>51226</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>377798</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3218,6 +4399,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>210912</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>70758</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>217715</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>119744</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D15D62F6-D88F-594B-E5B1-711360C55F9B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4029,123 +5246,123 @@
       </c>
       <c r="C2">
         <f>Data!I31</f>
-        <v>1.2678659059418999E-2</v>
+        <v>7.7759246766314107E-3</v>
       </c>
       <c r="D2">
         <f>Data!J31</f>
-        <v>1.5184585150040118E-2</v>
+        <v>8.1892147831648752E-3</v>
       </c>
       <c r="E2">
         <f>Data!K31</f>
-        <v>1.8526638938495932E-2</v>
+        <v>8.6727268054231088E-3</v>
       </c>
       <c r="F2">
         <f>Data!L31</f>
-        <v>2.2965536431060245E-2</v>
+        <v>9.2380939442073279E-3</v>
       </c>
       <c r="G2">
         <f>Data!M31</f>
-        <v>2.8829206942005366E-2</v>
+        <v>9.8987662632904812E-3</v>
       </c>
       <c r="H2">
         <f>Data!N31</f>
-        <v>3.651944293738426E-2</v>
+        <v>1.0670253609739368E-2</v>
       </c>
       <c r="I2">
         <f>Data!O31</f>
-        <v>4.6510622610364066E-2</v>
+        <v>1.1570385603052314E-2</v>
       </c>
       <c r="J2">
         <f>Data!P31</f>
-        <v>5.933344663118359E-2</v>
+        <v>1.2619583469375369E-2</v>
       </c>
       <c r="K2">
         <f>Data!Q31</f>
-        <v>7.5534645622301611E-2</v>
+        <v>1.3841135220834784E-2</v>
       </c>
       <c r="L2">
         <f>Data!R31</f>
-        <v>9.5603949881434322E-2</v>
+        <v>1.5261461327424669E-2</v>
       </c>
       <c r="M2">
         <f>Data!S31</f>
-        <v>0.11986535060126081</v>
+        <v>1.691035241414475E-2</v>
       </c>
       <c r="N2">
         <f>Data!T31</f>
-        <v>0.1483437545239433</v>
+        <v>1.882115350526798E-2</v>
       </c>
       <c r="O2">
         <f>Data!U31</f>
-        <v>0.18063966332773254</v>
+        <v>2.103086091562989E-2</v>
       </c>
       <c r="P2">
         <f>Data!V31</f>
-        <v>0.21586406916673176</v>
+        <v>2.3580088259556035E-2</v>
       </c>
       <c r="Q2">
         <f>Data!W31</f>
-        <v>0.25268549722754313</v>
+        <v>2.6512847772602481E-2</v>
       </c>
       <c r="R2">
         <f>Data!X31</f>
-        <v>0.28950692528835459</v>
+        <v>2.9876083311579586E-2</v>
       </c>
       <c r="S2">
         <f>Data!Y31</f>
-        <v>0.32473133112735375</v>
+        <v>3.3718883827272901E-2</v>
       </c>
       <c r="T2">
         <f>Data!Z31</f>
-        <v>0.35702723993114299</v>
+        <v>3.8091303487097355E-2</v>
       </c>
       <c r="U2">
         <f>Data!AA31</f>
-        <v>0.38550564385382546</v>
+        <v>4.3042720587092277E-2</v>
       </c>
       <c r="V2">
         <f>Data!AB31</f>
-        <v>0.40976704457365198</v>
+        <v>4.861968629436756E-2</v>
       </c>
       <c r="W2">
         <f>Data!AC31</f>
-        <v>0.42983634883278476</v>
+        <v>5.486325059290683E-2</v>
       </c>
       <c r="X2">
         <f>Data!AD31</f>
-        <v>0.4460375478239027</v>
+        <v>6.1805810018505346E-2</v>
       </c>
       <c r="Y2">
         <f>Data!AE31</f>
-        <v>0.45886037184472228</v>
+        <v>6.9467600483618303E-2</v>
       </c>
       <c r="Z2">
         <f>Data!AF31</f>
-        <v>0.46885155151770208</v>
+        <v>7.785305428056051E-2</v>
       </c>
       <c r="AA2">
         <f>Data!AG31</f>
-        <v>0.47654178751308102</v>
+        <v>8.6947341668358144E-2</v>
       </c>
       <c r="AB2">
         <f>Data!AH31</f>
-        <v>0.48240545802402607</v>
+        <v>9.6713504774003714E-2</v>
       </c>
       <c r="AC2">
         <f>Data!AI31</f>
-        <v>0.48684435551659033</v>
+        <v>0.10709063902446933</v>
       </c>
       <c r="AD2">
         <f>Data!AJ31</f>
-        <v>0.4901864093050462</v>
+        <v>0.11799355797925228</v>
       </c>
       <c r="AE2">
         <f>Data!AK31</f>
-        <v>0.49269233539566731</v>
+        <v>0.12931427170136311</v>
       </c>
       <c r="AF2">
         <f>Data!AL31</f>
-        <v>0.4945655394926507</v>
+        <v>0.14092541448449677</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -4412,127 +5629,127 @@
       </c>
       <c r="B5">
         <f>Data!H34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <f>Data!I34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <f>Data!J34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <f>Data!K34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <f>Data!L34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <f>Data!M34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <f>Data!N34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <f>Data!O34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <f>Data!P34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <f>Data!Q34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <f>Data!R34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <f>Data!S34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N5">
         <f>Data!T34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <f>Data!U34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P5">
         <f>Data!V34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q5">
         <f>Data!W34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R5">
         <f>Data!X34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S5">
         <f>Data!Y34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T5">
         <f>Data!Z34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5">
         <f>Data!AA34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V5">
         <f>Data!AB34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W5">
         <f>Data!AC34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X5">
         <f>Data!AD34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y5">
         <f>Data!AE34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z5">
         <f>Data!AF34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA5">
         <f>Data!AG34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB5">
         <f>Data!AH34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC5">
         <f>Data!AI34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD5">
         <f>Data!AJ34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE5">
         <f>Data!AK34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF5">
         <f>Data!AL34</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -4670,127 +5887,127 @@
       </c>
       <c r="B7">
         <f>Data!H36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
         <f>Data!I36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="D7">
         <f>Data!J36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="E7">
         <f>Data!K36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="F7">
         <f>Data!L36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="G7">
         <f>Data!M36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H7">
         <f>Data!N36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I7">
         <f>Data!O36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="J7">
         <f>Data!P36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K7">
         <f>Data!Q36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="L7">
         <f>Data!R36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="M7">
         <f>Data!S36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="N7">
         <f>Data!T36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="O7">
         <f>Data!U36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="P7">
         <f>Data!V36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Q7">
         <f>Data!W36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="R7">
         <f>Data!X36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="S7">
         <f>Data!Y36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="T7">
         <f>Data!Z36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="U7">
         <f>Data!AA36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="V7">
         <f>Data!AB36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="W7">
         <f>Data!AC36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="X7">
         <f>Data!AD36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Y7">
         <f>Data!AE36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Z7">
         <f>Data!AF36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AA7">
         <f>Data!AG36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AB7">
         <f>Data!AH36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AC7">
         <f>Data!AI36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AD7">
         <f>Data!AJ36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AE7">
         <f>Data!AK36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AF7">
         <f>Data!AL36</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:32">
@@ -4799,127 +6016,127 @@
       </c>
       <c r="B8">
         <f>Data!H37</f>
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="C8">
         <f>Data!I37</f>
-        <v>6.2640358785329186E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="D8">
         <f>Data!J37</f>
-        <v>8.4120834136230764E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="E8">
         <f>Data!K37</f>
-        <v>1.1276848830807375E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="F8">
         <f>Data!L37</f>
-        <v>1.5081814529160165E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="G8">
         <f>Data!M37</f>
-        <v>2.0108077288767171E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="H8">
         <f>Data!N37</f>
-        <v>2.6700048431076819E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="I8">
         <f>Data!O37</f>
-        <v>3.5264358826946353E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="J8">
         <f>Data!P37</f>
-        <v>4.6255918248393289E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="K8">
         <f>Data!Q37</f>
-        <v>6.0143377135798244E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="L8">
         <f>Data!R37</f>
-        <v>7.7346525986097831E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="M8">
         <f>Data!S37</f>
-        <v>9.8143085872323659E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="N8">
         <f>Data!T37</f>
-        <v>1.2255440653272574E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="O8">
         <f>Data!U37</f>
-        <v>1.5023804315677364E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="P8">
         <f>Data!V37</f>
-        <v>1.8043194968125682E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q8">
         <f>Data!W37</f>
-        <v>2.1199480306330579E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="R8">
         <f>Data!X37</f>
-        <v>2.4355765644535475E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="S8">
         <f>Data!Y37</f>
-        <v>2.7375156296983789E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="T8">
         <f>Data!Z37</f>
-        <v>3.014351995938858E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="U8">
         <f>Data!AA37</f>
-        <v>3.258465202542879E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="V8">
         <f>Data!AB37</f>
-        <v>3.4664308014051376E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="W8">
         <f>Data!AC37</f>
-        <v>3.6384622899081336E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="X8">
         <f>Data!AD37</f>
-        <v>3.777336878782183E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Y8">
         <f>Data!AE37</f>
-        <v>3.8872524729966523E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Z8">
         <f>Data!AF37</f>
-        <v>3.972895576955348E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AA8">
         <f>Data!AG37</f>
-        <v>4.0388152883784445E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AB8">
         <f>Data!AH37</f>
-        <v>4.0890779159745143E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AC8">
         <f>Data!AI37</f>
-        <v>4.127127572958042E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AD8">
         <f>Data!AJ37</f>
-        <v>4.1557752271298855E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AE8">
         <f>Data!AK37</f>
-        <v>4.1772557024807866E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AF8">
         <f>Data!AL37</f>
-        <v>4.1933125664813074E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
   </sheetData>
@@ -11372,123 +12589,123 @@
       </c>
       <c r="C2">
         <f>Data!I80</f>
-        <v>1.4774031693273055E-2</v>
+        <v>8.1625711531598966E-3</v>
       </c>
       <c r="D2">
         <f>Data!J80</f>
-        <v>1.984030573407751E-2</v>
+        <v>9.5653186720916755E-3</v>
       </c>
       <c r="E2">
         <f>Data!K80</f>
-        <v>2.6596993576865863E-2</v>
+        <v>1.1206406321842867E-2</v>
       </c>
       <c r="F2">
         <f>Data!L80</f>
-        <v>3.5571189272636181E-2</v>
+        <v>1.3125318337102799E-2</v>
       </c>
       <c r="G2">
         <f>Data!M80</f>
-        <v>4.7425873177566781E-2</v>
+        <v>1.5367705565275549E-2</v>
       </c>
       <c r="H2">
         <f>Data!N80</f>
-        <v>6.2973356056996513E-2</v>
+        <v>1.7986209962091559E-2</v>
       </c>
       <c r="I2">
         <f>Data!O80</f>
-        <v>8.317269649392238E-2</v>
+        <v>2.1041347020468282E-2</v>
       </c>
       <c r="J2">
         <f>Data!P80</f>
-        <v>0.10909682119561293</v>
+        <v>2.4602428402739435E-2</v>
       </c>
       <c r="K2">
         <f>Data!Q80</f>
-        <v>0.14185106490048782</v>
+        <v>2.8748495926539969E-2</v>
       </c>
       <c r="L2">
         <f>Data!R80</f>
-        <v>0.18242552380635635</v>
+        <v>3.356922328148252E-2</v>
       </c>
       <c r="M2">
         <f>Data!S80</f>
-        <v>0.23147521650098238</v>
+        <v>3.9165722796764356E-2</v>
       </c>
       <c r="N2">
         <f>Data!T80</f>
-        <v>0.28905049737499605</v>
+        <v>4.5651170784443723E-2</v>
       </c>
       <c r="O2">
         <f>Data!U80</f>
-        <v>0.35434369377420455</v>
+        <v>5.3151136398063722E-2</v>
       </c>
       <c r="P2">
         <f>Data!V80</f>
-        <v>0.42555748318834102</v>
+        <v>6.1803466263588569E-2</v>
       </c>
       <c r="Q2">
         <f>Data!W80</f>
-        <v>0.5</v>
+        <v>7.1757542263751334E-2</v>
       </c>
       <c r="R2">
         <f>Data!X80</f>
-        <v>0.57444251681165903</v>
+        <v>8.317269649392238E-2</v>
       </c>
       <c r="S2">
         <f>Data!Y80</f>
-        <v>0.6456563062257954</v>
+        <v>9.6215541710692826E-2</v>
       </c>
       <c r="T2">
         <f>Data!Z80</f>
-        <v>0.71094950262500389</v>
+        <v>0.11105596671140756</v>
       </c>
       <c r="U2">
         <f>Data!AA80</f>
-        <v>0.76852478349901754</v>
+        <v>0.12786156631908133</v>
       </c>
       <c r="V2">
         <f>Data!AB80</f>
-        <v>0.81757447619364365</v>
+        <v>0.14679033980138237</v>
       </c>
       <c r="W2">
         <f>Data!AC80</f>
-        <v>0.85814893509951229</v>
+        <v>0.16798161486607552</v>
       </c>
       <c r="X2">
         <f>Data!AD80</f>
-        <v>0.89090317880438707</v>
+        <v>0.19154534856146752</v>
       </c>
       <c r="Y2">
         <f>Data!AE80</f>
-        <v>0.91682730350607766</v>
+        <v>0.2175502235768875</v>
       </c>
       <c r="Z2">
         <f>Data!AF80</f>
-        <v>0.9370266439430035</v>
+        <v>0.2460112835510519</v>
       </c>
       <c r="AA2">
         <f>Data!AG80</f>
-        <v>0.95257412682243336</v>
+        <v>0.27687819487561016</v>
       </c>
       <c r="AB2">
         <f>Data!AH80</f>
-        <v>0.96442881072736386</v>
+        <v>0.31002551887238755</v>
       </c>
       <c r="AC2">
         <f>Data!AI80</f>
-        <v>0.97340300642313404</v>
+        <v>0.34524653939368077</v>
       </c>
       <c r="AD2">
         <f>Data!AJ80</f>
-        <v>0.98015969426592253</v>
+        <v>0.38225212523075103</v>
       </c>
       <c r="AE2">
         <f>Data!AK80</f>
-        <v>0.98522596830672693</v>
+        <v>0.42067574785125056</v>
       </c>
       <c r="AF2">
         <f>Data!AL80</f>
-        <v>0.98901305736940681</v>
+        <v>0.46008511544443426</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -12421,123 +13638,123 @@
       </c>
       <c r="C2">
         <f>Data!I87</f>
-        <v>1.4774031693273055E-2</v>
+        <v>8.1625711531598966E-3</v>
       </c>
       <c r="D2">
         <f>Data!J87</f>
-        <v>1.984030573407751E-2</v>
+        <v>9.5653186720916755E-3</v>
       </c>
       <c r="E2">
         <f>Data!K87</f>
-        <v>2.6596993576865863E-2</v>
+        <v>1.1206406321842867E-2</v>
       </c>
       <c r="F2">
         <f>Data!L87</f>
-        <v>3.5571189272636181E-2</v>
+        <v>1.3125318337102799E-2</v>
       </c>
       <c r="G2">
         <f>Data!M87</f>
-        <v>4.7425873177566781E-2</v>
+        <v>1.5367705565275549E-2</v>
       </c>
       <c r="H2">
         <f>Data!N87</f>
-        <v>6.2973356056996513E-2</v>
+        <v>1.7986209962091559E-2</v>
       </c>
       <c r="I2">
         <f>Data!O87</f>
-        <v>8.317269649392238E-2</v>
+        <v>2.1041347020468282E-2</v>
       </c>
       <c r="J2">
         <f>Data!P87</f>
-        <v>0.10909682119561293</v>
+        <v>2.4602428402739435E-2</v>
       </c>
       <c r="K2">
         <f>Data!Q87</f>
-        <v>0.14185106490048782</v>
+        <v>2.8748495926539969E-2</v>
       </c>
       <c r="L2">
         <f>Data!R87</f>
-        <v>0.18242552380635635</v>
+        <v>3.356922328148252E-2</v>
       </c>
       <c r="M2">
         <f>Data!S87</f>
-        <v>0.23147521650098238</v>
+        <v>3.9165722796764356E-2</v>
       </c>
       <c r="N2">
         <f>Data!T87</f>
-        <v>0.28905049737499605</v>
+        <v>4.5651170784443723E-2</v>
       </c>
       <c r="O2">
         <f>Data!U87</f>
-        <v>0.35434369377420455</v>
+        <v>5.3151136398063722E-2</v>
       </c>
       <c r="P2">
         <f>Data!V87</f>
-        <v>0.42555748318834102</v>
+        <v>6.1803466263588569E-2</v>
       </c>
       <c r="Q2">
         <f>Data!W87</f>
-        <v>0.5</v>
+        <v>7.1757542263751334E-2</v>
       </c>
       <c r="R2">
         <f>Data!X87</f>
-        <v>0.57444251681165903</v>
+        <v>8.317269649392238E-2</v>
       </c>
       <c r="S2">
         <f>Data!Y87</f>
-        <v>0.6456563062257954</v>
+        <v>9.6215541710692826E-2</v>
       </c>
       <c r="T2">
         <f>Data!Z87</f>
-        <v>0.71094950262500389</v>
+        <v>0.11105596671140756</v>
       </c>
       <c r="U2">
         <f>Data!AA87</f>
-        <v>0.76852478349901754</v>
+        <v>0.12786156631908133</v>
       </c>
       <c r="V2">
         <f>Data!AB87</f>
-        <v>0.81757447619364365</v>
+        <v>0.14679033980138237</v>
       </c>
       <c r="W2">
         <f>Data!AC87</f>
-        <v>0.85814893509951229</v>
+        <v>0.16798161486607552</v>
       </c>
       <c r="X2">
         <f>Data!AD87</f>
-        <v>0.89090317880438707</v>
+        <v>0.19154534856146752</v>
       </c>
       <c r="Y2">
         <f>Data!AE87</f>
-        <v>0.91682730350607766</v>
+        <v>0.2175502235768875</v>
       </c>
       <c r="Z2">
         <f>Data!AF87</f>
-        <v>0.9370266439430035</v>
+        <v>0.2460112835510519</v>
       </c>
       <c r="AA2">
         <f>Data!AG87</f>
-        <v>0.95257412682243336</v>
+        <v>0.27687819487561016</v>
       </c>
       <c r="AB2">
         <f>Data!AH87</f>
-        <v>0.96442881072736386</v>
+        <v>0.31002551887238755</v>
       </c>
       <c r="AC2">
         <f>Data!AI87</f>
-        <v>0.97340300642313404</v>
+        <v>0.34524653939368077</v>
       </c>
       <c r="AD2">
         <f>Data!AJ87</f>
-        <v>0.98015969426592253</v>
+        <v>0.38225212523075103</v>
       </c>
       <c r="AE2">
         <f>Data!AK87</f>
-        <v>0.98522596830672693</v>
+        <v>0.42067574785125056</v>
       </c>
       <c r="AF2">
         <f>Data!AL87</f>
-        <v>0.98901305736940681</v>
+        <v>0.46008511544443426</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -16147,7 +17364,7 @@
         <v>62</v>
       </c>
       <c r="I3" s="17">
-        <v>-0.3</v>
+        <v>-0.16</v>
       </c>
       <c r="N3" s="8" t="s">
         <v>62</v>
@@ -16164,7 +17381,7 @@
         <v>63</v>
       </c>
       <c r="I4" s="18">
-        <v>-16</v>
+        <v>-32</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>63</v>
@@ -16415,95 +17632,95 @@
       </c>
       <c r="N10">
         <f>M10+($R$10-$M$10)/($R$9-$M$9)</f>
-        <v>0.30932775069106316</v>
+        <v>0.30732775069106316</v>
       </c>
       <c r="O10">
         <f t="shared" ref="O10:Q10" si="1">N10+($R$10-$M$10)/($R$9-$M$9)</f>
-        <v>0.35199581301829735</v>
+        <v>0.34799581301829735</v>
       </c>
       <c r="P10">
         <f t="shared" si="1"/>
-        <v>0.39466387534553155</v>
+        <v>0.38866387534553154</v>
       </c>
       <c r="Q10">
         <f t="shared" si="1"/>
-        <v>0.43733193767276574</v>
+        <v>0.42933193767276573</v>
       </c>
       <c r="R10" s="31">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="S10">
         <f>R10+($W$10-$R$10)/($W$9-$R$9)</f>
-        <v>0.504</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="T10">
         <f t="shared" ref="T10:V10" si="2">S10+($W$10-$R$10)/($W$9-$R$9)</f>
-        <v>0.52800000000000002</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="U10">
         <f t="shared" si="2"/>
-        <v>0.55200000000000005</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="V10">
         <f t="shared" si="2"/>
-        <v>0.57600000000000007</v>
+        <v>0.56600000000000006</v>
       </c>
       <c r="W10" s="31">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="X10">
         <f t="shared" ref="X10" si="3">W10+($AB$10-$W$10)/($AB$9-$W$9)</f>
-        <v>0.64600000000000002</v>
+        <v>0.63800000000000001</v>
       </c>
       <c r="Y10">
         <f>X10+($AB$10-$W$10)/($AB$9-$W$9)</f>
-        <v>0.69200000000000006</v>
+        <v>0.68600000000000005</v>
       </c>
       <c r="Z10">
         <f t="shared" ref="Z10:AA10" si="4">Y10+($AB$10-$W$10)/($AB$9-$W$9)</f>
-        <v>0.7380000000000001</v>
+        <v>0.7340000000000001</v>
       </c>
       <c r="AA10">
         <f t="shared" si="4"/>
-        <v>0.78400000000000014</v>
+        <v>0.78200000000000014</v>
       </c>
       <c r="AB10" s="31">
         <v>0.83</v>
       </c>
       <c r="AC10">
         <f t="shared" ref="AC10" si="5">AB10+($AG$10-$AB$10)/($AG$9-$AB$9)</f>
-        <v>0.94399999999999995</v>
+        <v>0.94199999999999995</v>
       </c>
       <c r="AD10">
         <f>AC10+($AG$10-$AB$10)/($AG$9-$AB$9)</f>
-        <v>1.0579999999999998</v>
+        <v>1.0539999999999998</v>
       </c>
       <c r="AE10">
         <f t="shared" ref="AE10:AF10" si="6">AD10+($AG$10-$AB$10)/($AG$9-$AB$9)</f>
-        <v>1.1719999999999997</v>
+        <v>1.1659999999999999</v>
       </c>
       <c r="AF10">
         <f t="shared" si="6"/>
-        <v>1.2859999999999996</v>
+        <v>1.278</v>
       </c>
       <c r="AG10" s="31">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AH10">
         <f t="shared" ref="AH10" si="7">AG10+($AL$10-$AG$10)/($AL$9-$AG$9)</f>
-        <v>1.64</v>
+        <v>1.6319999999999999</v>
       </c>
       <c r="AI10">
         <f>AH10+($AL$10-$AG$10)/($AL$9-$AG$9)</f>
-        <v>1.88</v>
+        <v>1.8739999999999999</v>
       </c>
       <c r="AJ10">
         <f t="shared" ref="AJ10:AK10" si="8">AI10+($AL$10-$AG$10)/($AL$9-$AG$9)</f>
-        <v>2.12</v>
+        <v>2.1160000000000001</v>
       </c>
       <c r="AK10">
         <f t="shared" si="8"/>
-        <v>2.3600000000000003</v>
+        <v>2.3580000000000001</v>
       </c>
       <c r="AL10" s="31">
         <v>2.6</v>
@@ -17219,12 +18436,12 @@
         <v>6.6085783977121745E-4</v>
       </c>
       <c r="E16" s="24">
-        <f>E11</f>
-        <v>2.1560593065193183E-3</v>
+        <f>D16</f>
+        <v>6.6085783977121745E-4</v>
       </c>
       <c r="F16" s="7" t="str">
         <f>IF(D16=E16,"n/a",IF(OR(C16="battery electric vehicle",C16="natural gas vehicle",C16="plugin hybrid vehicle",C16="hydrogen vehicle"),"s-curve","linear"))</f>
-        <v>s-curve</v>
+        <v>n/a</v>
       </c>
       <c r="H16" s="20">
         <f t="shared" si="9"/>
@@ -17365,135 +18582,135 @@
         <v>0.05</v>
       </c>
       <c r="E17">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="str">
         <f>IF(D17=E17,"n/a",IF(OR(C17="battery electric vehicle",C17="natural gas vehicle",C17="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>s-curve</v>
       </c>
-      <c r="H17" s="20">
-        <f t="shared" ref="H17:H40" si="23">D17</f>
-        <v>0.05</v>
+      <c r="H17">
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:H$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,H$9))</f>
+        <v>7.0544063074398172E-2</v>
       </c>
       <c r="I17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,I$9))</f>
-        <v>5.6648314261972879E-2</v>
+        <v>7.4079584901821705E-2</v>
       </c>
       <c r="J17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,J$9))</f>
-        <v>5.8928137580334883E-2</v>
+        <v>7.8217690082670446E-2</v>
       </c>
       <c r="K17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,K$9))</f>
-        <v>6.1968647109589645E-2</v>
+        <v>8.3058898649436469E-2</v>
       </c>
       <c r="L17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,L$9))</f>
-        <v>6.6007035172686288E-2</v>
+        <v>8.8719689094453269E-2</v>
       </c>
       <c r="M17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,M$9))</f>
-        <v>7.1341642929905053E-2</v>
+        <v>9.5334731417562879E-2</v>
       </c>
       <c r="N17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,N$9))</f>
-        <v>7.833801022564843E-2</v>
+        <v>0.1030593193881701</v>
       </c>
       <c r="O17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,O$9))</f>
-        <v>8.7427713422265074E-2</v>
+        <v>0.11207197371038144</v>
       </c>
       <c r="P17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,P$9))</f>
-        <v>9.9093569538025811E-2</v>
+        <v>0.12257716378808134</v>
       </c>
       <c r="Q17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,Q$9))</f>
-        <v>0.11383297920521952</v>
+        <v>0.13480806298329293</v>
       </c>
       <c r="R17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,R$9))</f>
-        <v>0.13209148571286036</v>
+        <v>0.14902920868037345</v>
       </c>
       <c r="S17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,S$9))</f>
-        <v>0.15416384742544209</v>
+        <v>0.16553888225045485</v>
       </c>
       <c r="T17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,T$9))</f>
-        <v>0.18007272381874823</v>
+        <v>0.18467095381410897</v>
       </c>
       <c r="U17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,U$9))</f>
-        <v>0.20945466219839204</v>
+        <v>0.20679585237428799</v>
       </c>
       <c r="V17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,V$9))</f>
-        <v>0.24150086743475346</v>
+        <v>0.2323202254775863</v>
       </c>
       <c r="W17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,W$9))</f>
-        <v>0.27500000000000002</v>
+        <v>0.26168474967806649</v>
       </c>
       <c r="X17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,X$9))</f>
-        <v>0.30849913256524658</v>
+        <v>0.29535945465707103</v>
       </c>
       <c r="Y17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,Y$9))</f>
-        <v>0.34054533780160795</v>
+        <v>0.33383584804654387</v>
       </c>
       <c r="Z17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,Z$9))</f>
-        <v>0.36992727618125176</v>
+        <v>0.37761510179865232</v>
       </c>
       <c r="AA17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AA$9))</f>
-        <v>0.3958361525745579</v>
+        <v>0.42719162064128996</v>
       </c>
       <c r="AB17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AB$9))</f>
-        <v>0.4179085142871396</v>
+        <v>0.48303150241407805</v>
       </c>
       <c r="AC17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AC$9))</f>
-        <v>0.43616702079478054</v>
+        <v>0.54554576385492282</v>
       </c>
       <c r="AD17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AD$9))</f>
-        <v>0.45090643046197421</v>
+        <v>0.61505877825632926</v>
       </c>
       <c r="AE17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AE$9))</f>
-        <v>0.46257228657773497</v>
+        <v>0.69177315955181817</v>
       </c>
       <c r="AF17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AF$9))</f>
-        <v>0.47166198977435159</v>
+        <v>0.77573328647560325</v>
       </c>
       <c r="AG17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AG$9))</f>
-        <v>0.47865835707009496</v>
+        <v>0.86679067488305006</v>
       </c>
       <c r="AH17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AH$9))</f>
-        <v>0.48399296482731374</v>
+        <v>0.96457528067354337</v>
       </c>
       <c r="AI17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AI$9))</f>
-        <v>0.48803135289041033</v>
+        <v>1.0684772912113583</v>
       </c>
       <c r="AJ17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AJ$9))</f>
-        <v>0.49107186241966516</v>
+        <v>1.1776437694307156</v>
       </c>
       <c r="AK17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AK$9))</f>
-        <v>0.49335168573802712</v>
+        <v>1.2909934561611893</v>
       </c>
       <c r="AL17">
         <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AL$9))</f>
-        <v>0.49505587581623306</v>
+        <v>1.4072510905610811</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -17512,7 +18729,7 @@
         <v>76</v>
       </c>
       <c r="H18" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="H18:H40" si="23">D18</f>
         <v>6.1283704210113928E-4</v>
       </c>
       <c r="I18">
@@ -17641,12 +18858,11 @@
         <v>3</v>
       </c>
       <c r="D19" s="20">
-        <f>MIN(1.25*INDEX('SYVbT-freight'!$B$2:$H$2,MATCH(Data!$C12,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-freight'!$B$2:$H$2),1)*3</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="E19" s="20">
         <f t="shared" ref="E19:E20" si="24">D19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="F19" s="6" t="str">
         <f>IF(D19=E19,"n/a",IF(OR(C19="battery electric vehicle",C19="natural gas vehicle",C19="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -17654,127 +18870,127 @@
       </c>
       <c r="H19" s="20">
         <f t="shared" si="23"/>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="I19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,I$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="J19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,J$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="K19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,K$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="L19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,L$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="M19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,M$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="N19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,N$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="O19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,O$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="P19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,P$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="Q19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,Q$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="R19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,R$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="S19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,S$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="T19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,T$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="U19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,U$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="V19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,V$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="W19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,W$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="X19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,X$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="Y19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,Y$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="Z19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,Z$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AA19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,AA$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AB19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,AB$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AC19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,AC$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AD19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,AD$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AE19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,AE$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AF19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,AF$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AG19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,AG$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AH19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,AH$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AI19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,AI$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AJ19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,AJ$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AK19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,AK$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AL19">
         <f>IF($F19="s-curve",$D19+($E19-$D19)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D19:$E19,$D$9:$E$9,AL$9))</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -17782,11 +18998,11 @@
         <v>4</v>
       </c>
       <c r="D20" s="20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="20">
         <f t="shared" si="24"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="str">
         <f>IF(D20=E20,"n/a",IF(OR(C20="battery electric vehicle",C20="natural gas vehicle",C20="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -17794,127 +19010,127 @@
       </c>
       <c r="H20" s="20">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,I$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,J$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,K$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,L$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,M$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,N$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,O$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,P$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,Q$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,R$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,S$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,T$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,U$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,V$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,W$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,X$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,Y$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,Z$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,AA$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,AB$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,AC$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,AD$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,AE$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,AF$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,AG$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,AH$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,AI$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,AJ$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,AK$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL20">
         <f>IF($F20="s-curve",$D20+($E20-$D20)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D20:$E20,$D$9:$E$9,AL$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -17939,123 +19155,123 @@
       </c>
       <c r="I21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,I$9))</f>
-        <v>3.6935079233182638E-3</v>
+        <v>2.0406427882899742E-3</v>
       </c>
       <c r="J21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,J$9))</f>
-        <v>4.9600764335193774E-3</v>
+        <v>2.3913296680229189E-3</v>
       </c>
       <c r="K21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,K$9))</f>
-        <v>6.6492483942164659E-3</v>
+        <v>2.8016015804607167E-3</v>
       </c>
       <c r="L21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,L$9))</f>
-        <v>8.8927973181590451E-3</v>
+        <v>3.2813295842756998E-3</v>
       </c>
       <c r="M21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,M$9))</f>
-        <v>1.1856468294391695E-2</v>
+        <v>3.8419263913188873E-3</v>
       </c>
       <c r="N21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,N$9))</f>
-        <v>1.5743339014249128E-2</v>
+        <v>4.4965524905228897E-3</v>
       </c>
       <c r="O21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,O$9))</f>
-        <v>2.0793174123480595E-2</v>
+        <v>5.2603367551170704E-3</v>
       </c>
       <c r="P21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,P$9))</f>
-        <v>2.7274205298903231E-2</v>
+        <v>6.1506071006848587E-3</v>
       </c>
       <c r="Q21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,Q$9))</f>
-        <v>3.5462766225121956E-2</v>
+        <v>7.1871239816349922E-3</v>
       </c>
       <c r="R21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,R$9))</f>
-        <v>4.5606380951589087E-2</v>
+        <v>8.39230582037063E-3</v>
       </c>
       <c r="S21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,S$9))</f>
-        <v>5.7868804125245595E-2</v>
+        <v>9.791430699191089E-3</v>
       </c>
       <c r="T21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,T$9))</f>
-        <v>7.2262624343749013E-2</v>
+        <v>1.1412792696110931E-2</v>
       </c>
       <c r="U21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,U$9))</f>
-        <v>8.8585923443551137E-2</v>
+        <v>1.3287784099515931E-2</v>
       </c>
       <c r="V21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,V$9))</f>
-        <v>0.10638937079708526</v>
+        <v>1.5450866565897142E-2</v>
       </c>
       <c r="W21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,W$9))</f>
-        <v>0.125</v>
+        <v>1.7939385565937833E-2</v>
       </c>
       <c r="X21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,X$9))</f>
-        <v>0.14361062920291476</v>
+        <v>2.0793174123480595E-2</v>
       </c>
       <c r="Y21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,Y$9))</f>
-        <v>0.16141407655644885</v>
+        <v>2.4053885427673206E-2</v>
       </c>
       <c r="Z21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,Z$9))</f>
-        <v>0.17773737565625097</v>
+        <v>2.7763991677851891E-2</v>
       </c>
       <c r="AA21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,AA$9))</f>
-        <v>0.19213119587475438</v>
+        <v>3.1965391579770332E-2</v>
       </c>
       <c r="AB21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,AB$9))</f>
-        <v>0.20439361904841091</v>
+        <v>3.6697584950345592E-2</v>
       </c>
       <c r="AC21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,AC$9))</f>
-        <v>0.21453723377487807</v>
+        <v>4.199540371651888E-2</v>
       </c>
       <c r="AD21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,AD$9))</f>
-        <v>0.22272579470109677</v>
+        <v>4.7886337140366879E-2</v>
       </c>
       <c r="AE21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,AE$9))</f>
-        <v>0.22920682587651942</v>
+        <v>5.4387555894221874E-2</v>
       </c>
       <c r="AF21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,AF$9))</f>
-        <v>0.23425666098575088</v>
+        <v>6.1502820887762974E-2</v>
       </c>
       <c r="AG21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,AG$9))</f>
-        <v>0.23814353170560834</v>
+        <v>6.921954871890254E-2</v>
       </c>
       <c r="AH21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,AH$9))</f>
-        <v>0.24110720268184097</v>
+        <v>7.7506379718096888E-2</v>
       </c>
       <c r="AI21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,AI$9))</f>
-        <v>0.24335075160578351</v>
+        <v>8.6311634848420193E-2</v>
       </c>
       <c r="AJ21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,AJ$9))</f>
-        <v>0.24503992356648063</v>
+        <v>9.5563031307687757E-2</v>
       </c>
       <c r="AK21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,AK$9))</f>
-        <v>0.24630649207668173</v>
+        <v>0.10516893696281264</v>
       </c>
       <c r="AL21">
         <f>IF($F21="s-curve",$D21+($E21-$D21)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D21:$E21,$D$9:$E$9,AL$9))</f>
-        <v>0.2472532643423517</v>
+        <v>0.11502127886110856</v>
       </c>
     </row>
     <row r="22" spans="1:38">
@@ -18063,12 +19279,11 @@
         <v>78</v>
       </c>
       <c r="D22" s="20">
-        <f>MIN(1.25*INDEX('SYVbT-freight'!$B$2:$H$2,MATCH(Data!$C15,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-freight'!$B$2:$H$2),1)</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="E22" s="20">
         <f>D22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="F22" s="6" t="str">
         <f>IF(D22=E22,"n/a",IF(OR(C22="battery electric vehicle",C22="natural gas vehicle",C22="plugin hybrid vehicle",C22="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -18076,127 +19291,127 @@
       </c>
       <c r="H22" s="20">
         <f t="shared" si="23"/>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,I$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="J22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,J$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,K$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="L22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,L$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="M22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,M$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="N22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,N$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="O22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,O$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="P22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,P$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Q22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,Q$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="R22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,R$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="S22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,S$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="T22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,T$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="U22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,U$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="V22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,V$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="W22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,W$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="X22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,X$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Y22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,Y$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Z22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,Z$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AA22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,AA$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AB22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,AB$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AC22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,AC$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AD22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,AD$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AE22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,AE$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AF22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,AF$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AG22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,AG$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AH22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,AH$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AI22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,AI$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AJ22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,AJ$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AK22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,AK$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AL22">
         <f>IF($F22="s-curve",$D22+($E22-$D22)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D22:$E22,$D$9:$E$9,AL$9))</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23" spans="1:38" ht="15.75" thickBot="1">
@@ -18206,140 +19421,139 @@
         <v>79</v>
       </c>
       <c r="D23" s="21">
-        <f>MIN(1.25*INDEX('SYVbT-freight'!$B$2:$H$2,MATCH(Data!$C16,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-freight'!$B$2:$H$2),1)</f>
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="E23" s="24">
-        <f>E18</f>
-        <v>6.1283704210113928E-4</v>
+        <f>D23</f>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="F23" s="7" t="str">
         <f>IF(D23=E23,"n/a",IF(OR(C23="battery electric vehicle",C23="natural gas vehicle",C23="plugin hybrid vehicle",C23="hydrogen vehicle"),"s-curve","linear"))</f>
-        <v>s-curve</v>
+        <v>n/a</v>
       </c>
       <c r="H23" s="20">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="I23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,I$9))</f>
-        <v>9.0540738828139446E-6</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="J23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,J$9))</f>
-        <v>1.2158874280454334E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="K23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,K$9))</f>
-        <v>1.6299622872429478E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="L23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,L$9))</f>
-        <v>2.179934241786213E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="M23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,M$9))</f>
-        <v>2.9064331837203784E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="N23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,N$9))</f>
-        <v>3.85924052571516E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="O23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,O$9))</f>
-        <v>5.0971309302911188E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="P23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,P$9))</f>
-        <v>6.6858573204156302E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,Q$9))</f>
-        <v>8.6931587032511697E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="R23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,R$9))</f>
-        <v>1.1179711841323839E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="S23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,S$9))</f>
-        <v>1.4185658700018285E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="T23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,T$9))</f>
-        <v>1.7714085182915572E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="U23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,U$9))</f>
-        <v>2.1715494117977539E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="V23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,V$9))</f>
-        <v>2.6079738924114821E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="W23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,W$9))</f>
-        <v>3.0641852105056964E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="X23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,X$9))</f>
-        <v>3.5203965285999107E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Y23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,Y$9))</f>
-        <v>3.9568210092136389E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Z23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,Z$9))</f>
-        <v>4.3569619027198356E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AA23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,AA$9))</f>
-        <v>4.709804551009564E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AB23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,AB$9))</f>
-        <v>5.010399236879009E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AC23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,AC$9))</f>
-        <v>5.2590545506862765E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AD23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,AD$9))</f>
-        <v>5.4597846889698301E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AE23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,AE$9))</f>
-        <v>5.6186573279822817E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AF23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,AF$9))</f>
-        <v>5.7424463684398771E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AG23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,AG$9))</f>
-        <v>5.8377271026393554E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AH23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,AH$9))</f>
-        <v>5.9103769968327712E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AI23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,AI$9))</f>
-        <v>5.9653741922870976E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AJ23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,AJ$9))</f>
-        <v>6.0067816782068497E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AK23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,AK$9))</f>
-        <v>6.0378296821832537E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AL23">
         <f>IF($F23="s-curve",$D23+($E23-$D23)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D23:$E23,$D$9:$E$9,AL$9))</f>
-        <v>6.0610383667767168E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="24" spans="1:38">
@@ -18353,138 +19567,138 @@
         <v>1</v>
       </c>
       <c r="D24" s="20">
-        <v>0.05</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E24" s="26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" s="6" t="str">
         <f>IF(D24=E24,"n/a",IF(OR(C24="battery electric vehicle",C24="natural gas vehicle",C24="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>s-curve</v>
       </c>
-      <c r="H24" s="20">
-        <f t="shared" si="23"/>
-        <v>0.05</v>
+      <c r="H24">
+        <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:H$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,H$9))</f>
+        <v>9.7368870468605012E-2</v>
       </c>
       <c r="I24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,I$9))</f>
-        <v>6.4035330108609401E-2</v>
+        <v>0.1020789046319184</v>
       </c>
       <c r="J24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,J$9))</f>
-        <v>6.8848290447373631E-2</v>
+        <v>0.10759170238132029</v>
       </c>
       <c r="K24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,K$9))</f>
-        <v>7.5267143898022582E-2</v>
+        <v>0.11404117684484247</v>
       </c>
       <c r="L24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,L$9))</f>
-        <v>8.3792629809004371E-2</v>
+        <v>0.121582501064814</v>
       </c>
       <c r="M24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,M$9))</f>
-        <v>9.505457951868844E-2</v>
+        <v>0.13039508287153292</v>
       </c>
       <c r="N24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,N$9))</f>
-        <v>0.10982468825414668</v>
+        <v>0.14068580515101983</v>
       </c>
       <c r="O24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,O$9))</f>
-        <v>0.12901406166922624</v>
+        <v>0.15269249379044036</v>
       </c>
       <c r="P24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,P$9))</f>
-        <v>0.15364198013583227</v>
+        <v>0.166687543622766</v>
       </c>
       <c r="Q24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,Q$9))</f>
-        <v>0.18475851165546342</v>
+        <v>0.1829815889913021</v>
       </c>
       <c r="R24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,R$9))</f>
-        <v>0.22330424761603851</v>
+        <v>0.20192704749622634</v>
       </c>
       <c r="S24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,S$9))</f>
-        <v>0.26990145567593327</v>
+        <v>0.22392129059128393</v>
       </c>
       <c r="T24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,T$9))</f>
-        <v>0.32459797250624622</v>
+        <v>0.24940910118286383</v>
       </c>
       <c r="U24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,U$9))</f>
-        <v>0.38662650908549429</v>
+        <v>0.27888396604439047</v>
       </c>
       <c r="V24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,V$9))</f>
-        <v>0.45427960902892389</v>
+        <v>0.31288762241590307</v>
       </c>
       <c r="W24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,W$9))</f>
-        <v>0.52500000000000002</v>
+        <v>0.3520071410965428</v>
       </c>
       <c r="X24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,X$9))</f>
-        <v>0.5957203909710761</v>
+        <v>0.39686869722111495</v>
       </c>
       <c r="Y24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,Y$9))</f>
-        <v>0.6633734909145057</v>
+        <v>0.44812707892302284</v>
       </c>
       <c r="Z24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,Z$9))</f>
-        <v>0.72540202749375371</v>
+        <v>0.50644994917583175</v>
       </c>
       <c r="AA24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AA$9))</f>
-        <v>0.78009854432406667</v>
+        <v>0.57249595563398969</v>
       </c>
       <c r="AB24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AB$9))</f>
-        <v>0.82669575238396142</v>
+        <v>0.64688603541943279</v>
       </c>
       <c r="AC24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AC$9))</f>
-        <v>0.86524148834453662</v>
+        <v>0.73016774642367688</v>
       </c>
       <c r="AD24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AD$9))</f>
-        <v>0.89635801986416774</v>
+        <v>0.82277321984656737</v>
       </c>
       <c r="AE24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AE$9))</f>
-        <v>0.9209859383307738</v>
+        <v>0.92497237865716797</v>
       </c>
       <c r="AF24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AF$9))</f>
-        <v>0.94017531174585334</v>
+        <v>1.036824344355634</v>
       </c>
       <c r="AG24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AG$9))</f>
-        <v>0.9549454204813117</v>
+        <v>1.158131305861148</v>
       </c>
       <c r="AH24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AH$9))</f>
-        <v>0.96620737019099567</v>
+        <v>1.2884002891684831</v>
       </c>
       <c r="AI24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AI$9))</f>
-        <v>0.97473285610197735</v>
+        <v>1.4268188998171656</v>
       </c>
       <c r="AJ24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AJ$9))</f>
-        <v>0.98115170955262643</v>
+        <v>1.5722508521568517</v>
       </c>
       <c r="AK24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AK$9))</f>
-        <v>0.98596466989139064</v>
+        <v>1.7232556890554149</v>
       </c>
       <c r="AL24">
         <f>IF($F24="s-curve",$D24+($E24-$D24)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D24:$E24,$D$9:$E$9,AL$9))</f>
-        <v>0.98956240450093647</v>
+        <v>1.8781345036966268</v>
       </c>
     </row>
     <row r="25" spans="1:38">
@@ -18633,12 +19847,11 @@
         <v>3</v>
       </c>
       <c r="D26" s="20">
-        <f>MIN(1.25*INDEX('SYVbT-passenger'!$B$3:$H$3,MATCH(Data!$C12,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-passenger'!$B$3:$H$3),1)*3</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="E26" s="20">
         <f t="shared" ref="E26:E29" si="25">D26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="str">
         <f>IF(D26=E26,"n/a",IF(OR(C26="battery electric vehicle",C26="natural gas vehicle",C26="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -18646,127 +19859,127 @@
       </c>
       <c r="H26" s="20">
         <f t="shared" si="23"/>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,I$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,J$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="K26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,K$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="L26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,L$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="M26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,M$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="N26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,N$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="O26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,O$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="P26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,P$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="Q26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,Q$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="R26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,R$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="S26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,S$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="T26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,T$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="U26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,U$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="V26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,V$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="W26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,W$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="X26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,X$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="Y26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,Y$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="Z26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,Z$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AA26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,AA$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AB26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,AB$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AC26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,AC$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AD26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,AD$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AE26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,AE$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AF26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,AF$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AG26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,AG$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AH26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,AH$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AI26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,AI$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AJ26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,AJ$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AK26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,AK$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AL26">
         <f>IF($F26="s-curve",$D26+($E26-$D26)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D26:$E26,$D$9:$E$9,AL$9))</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:38">
@@ -18774,12 +19987,11 @@
         <v>4</v>
       </c>
       <c r="D27" s="20">
-        <f>MIN(1.25*INDEX('SYVbT-passenger'!$B$3:$H$3,MATCH(Data!$C13,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-passenger'!$B$3:$H$3),1)*3</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="E27" s="20">
         <f t="shared" si="25"/>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="str">
         <f>IF(D27=E27,"n/a",IF(OR(C27="battery electric vehicle",C27="natural gas vehicle",C27="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -18787,127 +19999,127 @@
       </c>
       <c r="H27" s="20">
         <f t="shared" si="23"/>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,I$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,J$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="K27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,K$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="L27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,L$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="M27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,M$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="N27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,N$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="O27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,O$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="P27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,P$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="Q27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,Q$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="R27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,R$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="S27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,S$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="T27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,T$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="U27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,U$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="V27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,V$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="W27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,W$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="X27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,X$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="Y27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,Y$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="Z27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,Z$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AA27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,AA$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AB27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,AB$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AC27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,AC$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AD27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,AD$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AE27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,AE$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AF27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,AF$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AG27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,AG$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AH27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,AH$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AI27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,AI$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AJ27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,AJ$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AK27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,AK$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AL27">
         <f>IF($F27="s-curve",$D27+($E27-$D27)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D27:$E27,$D$9:$E$9,AL$9))</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:38">
@@ -18915,12 +20127,11 @@
         <v>5</v>
       </c>
       <c r="D28" s="20">
-        <f>MIN(1.25*INDEX('SYVbT-passenger'!$B$3:$H$3,MATCH(Data!$C14,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-passenger'!$B$3:$H$3),1)</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="E28" s="20">
         <f t="shared" si="25"/>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="F28" s="6" t="str">
         <f>IF(D28=E28,"n/a",IF(OR(C28="battery electric vehicle",C28="natural gas vehicle",C28="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -18928,127 +20139,127 @@
       </c>
       <c r="H28" s="20">
         <f t="shared" si="23"/>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,I$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="J28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,J$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,K$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="L28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,L$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="M28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,M$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="N28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,N$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="O28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,O$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="P28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,P$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Q28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,Q$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="R28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,R$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="S28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,S$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="T28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,T$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="U28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,U$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="V28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,V$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="W28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,W$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="X28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,X$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Y28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,Y$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Z28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,Z$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AA28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,AA$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AB28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,AB$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AC28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,AC$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AD28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,AD$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AE28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,AE$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AF28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,AF$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AG28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,AG$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AH28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,AH$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AI28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,AI$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AJ28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,AJ$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AK28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,AK$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AL28">
         <f>IF($F28="s-curve",$D28+($E28-$D28)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D28:$E28,$D$9:$E$9,AL$9))</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="29" spans="1:38">
@@ -19056,12 +20267,11 @@
         <v>78</v>
       </c>
       <c r="D29" s="20">
-        <f>MIN(1.25*INDEX('SYVbT-passenger'!$B$3:$H$3,MATCH(Data!$C15,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-passenger'!$B$3:$H$3),1)</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="E29" s="20">
         <f t="shared" si="25"/>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="F29" s="6" t="str">
         <f>IF(D29=E29,"n/a",IF(OR(C29="battery electric vehicle",C29="natural gas vehicle",C29="plugin hybrid vehicle",C29="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -19069,127 +20279,127 @@
       </c>
       <c r="H29" s="20">
         <f t="shared" si="23"/>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="I29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,I$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="J29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,J$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="K29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,K$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="L29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,L$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="M29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,M$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="N29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,N$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="O29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,O$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="P29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,P$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="Q29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,Q$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="R29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,R$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="S29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,S$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="T29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,T$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="U29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,U$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="V29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,V$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="W29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,W$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="X29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,X$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="Y29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,Y$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="Z29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,Z$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AA29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,AA$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AB29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,AB$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AC29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,AC$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AD29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,AD$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AE29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,AE$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AF29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,AF$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AG29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,AG$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AH29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,AH$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AI29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,AI$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AJ29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,AJ$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AK29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,AK$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AL29">
         <f>IF($F29="s-curve",$D29+($E29-$D29)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D29:$E29,$D$9:$E$9,AL$9))</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30" spans="1:38" ht="15.75" thickBot="1">
@@ -19199,8 +20409,7 @@
         <v>79</v>
       </c>
       <c r="D30" s="21">
-        <f>MIN(1.25*INDEX('SYVbT-passenger'!$B$3:$H$3,MATCH(Data!$C16,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-passenger'!$B$3:$H$3),1)</f>
-        <v>6.6083849891288092E-4</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="E30" s="24">
         <f>E25</f>
@@ -19212,127 +20421,127 @@
       </c>
       <c r="H30" s="20">
         <f t="shared" si="23"/>
-        <v>6.6083849891288092E-4</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="I30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,I$9))</f>
-        <v>6.8292800627355835E-4</v>
+        <v>7.1188467263558208E-4</v>
       </c>
       <c r="J30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,J$9))</f>
-        <v>6.9050288495521941E-4</v>
+        <v>7.139270677020466E-4</v>
       </c>
       <c r="K30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,K$9))</f>
-        <v>7.0060519886219654E-4</v>
+        <v>7.163164850948787E-4</v>
       </c>
       <c r="L30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,L$9))</f>
-        <v>7.140230367275464E-4</v>
+        <v>7.1911041371000887E-4</v>
       </c>
       <c r="M30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,M$9))</f>
-        <v>7.3174765874089315E-4</v>
+        <v>7.223753210080882E-4</v>
       </c>
       <c r="N30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,N$9))</f>
-        <v>7.549935976041178E-4</v>
+        <v>7.2618785347697127E-4</v>
       </c>
       <c r="O30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,O$9))</f>
-        <v>7.851947971497683E-4</v>
+        <v>7.306361214447901E-4</v>
       </c>
       <c r="P30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,P$9))</f>
-        <v>8.2395545201406335E-4</v>
+        <v>7.358210424289796E-4</v>
       </c>
       <c r="Q30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,Q$9))</f>
-        <v>8.7292821195079028E-4</v>
+        <v>7.4185770101618375E-4</v>
       </c>
       <c r="R30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,R$9))</f>
-        <v>9.3359342692151347E-4</v>
+        <v>7.4887666175831567E-4</v>
       </c>
       <c r="S30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,S$9))</f>
-        <v>1.0069304530164447E-3</v>
+        <v>7.5702514382313302E-4</v>
       </c>
       <c r="T30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,T$9))</f>
-        <v>1.0930145779908538E-3</v>
+        <v>7.6646793149167617E-4</v>
       </c>
       <c r="U30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,U$9))</f>
-        <v>1.1906382038504885E-3</v>
+        <v>7.7738785297517719E-4</v>
       </c>
       <c r="V30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,V$9))</f>
-        <v>1.2971140499908186E-3</v>
+        <v>7.8998561243814067E-4</v>
       </c>
       <c r="W30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,W$9))</f>
-        <v>1.4084173527857645E-3</v>
+        <v>8.0447870933516956E-4</v>
       </c>
       <c r="X30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,X$9))</f>
-        <v>1.5197206555807102E-3</v>
+        <v>8.2109913059272201E-4</v>
       </c>
       <c r="Y30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,Y$9))</f>
-        <v>1.62619650172104E-3</v>
+        <v>8.4008946375237572E-4</v>
       </c>
       <c r="Z30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,Z$9))</f>
-        <v>1.7238201275806748E-3</v>
+        <v>8.6169706625861841E-4</v>
       </c>
       <c r="AA30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,AA$9))</f>
-        <v>1.8099042525550838E-3</v>
+        <v>8.8616595553801553E-4</v>
       </c>
       <c r="AB30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,AB$9))</f>
-        <v>1.8832412786500153E-3</v>
+        <v>9.1372617792494671E-4</v>
       </c>
       <c r="AC30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,AC$9))</f>
-        <v>1.9439064936207385E-3</v>
+        <v>9.4458059403339993E-4</v>
       </c>
       <c r="AD30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,AD$9))</f>
-        <v>1.9928792535574653E-3</v>
+        <v>9.7888930090860526E-4</v>
       </c>
       <c r="AE30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,AE$9))</f>
-        <v>2.0316399084217606E-3</v>
+        <v>1.016752300285689E-3</v>
       </c>
       <c r="AF30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,AF$9))</f>
-        <v>2.0618411079674111E-3</v>
+        <v>1.0581914956455567E-3</v>
       </c>
       <c r="AG30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,AG$9))</f>
-        <v>2.0850870468306359E-3</v>
+        <v>1.1031336014453823E-3</v>
       </c>
       <c r="AH30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,AH$9))</f>
-        <v>2.1028116688439824E-3</v>
+        <v>1.1513959794455754E-3</v>
       </c>
       <c r="AI30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,AI$9))</f>
-        <v>2.1162295067093319E-3</v>
+        <v>1.2026776517192247E-3</v>
       </c>
       <c r="AJ30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,AJ$9))</f>
-        <v>2.1263318206163092E-3</v>
+        <v>1.25655764432318E-3</v>
       </c>
       <c r="AK30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,AK$9))</f>
-        <v>2.1339066992979703E-3</v>
+        <v>1.3125022931047108E-3</v>
       </c>
       <c r="AL30">
         <f>IF($F30="s-curve",$D30+($E30-$D30)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D30:$E30,$D$9:$E$9,AL$9))</f>
-        <v>2.1395689946999558E-3</v>
+        <v>1.3698821828272024E-3</v>
       </c>
     </row>
     <row r="31" spans="1:38">
@@ -19350,7 +20559,7 @@
         <v>5.3709944550863111E-3</v>
       </c>
       <c r="E31" s="20">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F31" s="6" t="str">
         <f>IF(D31=E31,"n/a",IF(OR(C31="battery electric vehicle",C31="natural gas vehicle",C31="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -19362,123 +20571,123 @@
       </c>
       <c r="I31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,I$9))</f>
-        <v>1.2678659059418999E-2</v>
+        <v>7.7759246766314107E-3</v>
       </c>
       <c r="J31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,J$9))</f>
-        <v>1.5184585150040118E-2</v>
+        <v>8.1892147831648752E-3</v>
       </c>
       <c r="K31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,K$9))</f>
-        <v>1.8526638938495932E-2</v>
+        <v>8.6727268054231088E-3</v>
       </c>
       <c r="L31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,L$9))</f>
-        <v>2.2965536431060245E-2</v>
+        <v>9.2380939442073279E-3</v>
       </c>
       <c r="M31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,M$9))</f>
-        <v>2.8829206942005366E-2</v>
+        <v>9.8987662632904812E-3</v>
       </c>
       <c r="N31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,N$9))</f>
-        <v>3.651944293738426E-2</v>
+        <v>1.0670253609739368E-2</v>
       </c>
       <c r="O31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,O$9))</f>
-        <v>4.6510622610364066E-2</v>
+        <v>1.1570385603052314E-2</v>
       </c>
       <c r="P31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,P$9))</f>
-        <v>5.933344663118359E-2</v>
+        <v>1.2619583469375369E-2</v>
       </c>
       <c r="Q31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,Q$9))</f>
-        <v>7.5534645622301611E-2</v>
+        <v>1.3841135220834784E-2</v>
       </c>
       <c r="R31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,R$9))</f>
-        <v>9.5603949881434322E-2</v>
+        <v>1.5261461327424669E-2</v>
       </c>
       <c r="S31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,S$9))</f>
-        <v>0.11986535060126081</v>
+        <v>1.691035241414475E-2</v>
       </c>
       <c r="T31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,T$9))</f>
-        <v>0.1483437545239433</v>
+        <v>1.882115350526798E-2</v>
       </c>
       <c r="U31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,U$9))</f>
-        <v>0.18063966332773254</v>
+        <v>2.103086091562989E-2</v>
       </c>
       <c r="V31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,V$9))</f>
-        <v>0.21586406916673176</v>
+        <v>2.3580088259556035E-2</v>
       </c>
       <c r="W31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,W$9))</f>
-        <v>0.25268549722754313</v>
+        <v>2.6512847772602481E-2</v>
       </c>
       <c r="X31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,X$9))</f>
-        <v>0.28950692528835459</v>
+        <v>2.9876083311579586E-2</v>
       </c>
       <c r="Y31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,Y$9))</f>
-        <v>0.32473133112735375</v>
+        <v>3.3718883827272901E-2</v>
       </c>
       <c r="Z31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,Z$9))</f>
-        <v>0.35702723993114299</v>
+        <v>3.8091303487097355E-2</v>
       </c>
       <c r="AA31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AA$9))</f>
-        <v>0.38550564385382546</v>
+        <v>4.3042720587092277E-2</v>
       </c>
       <c r="AB31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AB$9))</f>
-        <v>0.40976704457365198</v>
+        <v>4.861968629436756E-2</v>
       </c>
       <c r="AC31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AC$9))</f>
-        <v>0.42983634883278476</v>
+        <v>5.486325059290683E-2</v>
       </c>
       <c r="AD31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AD$9))</f>
-        <v>0.4460375478239027</v>
+        <v>6.1805810018505346E-2</v>
       </c>
       <c r="AE31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AE$9))</f>
-        <v>0.45886037184472228</v>
+        <v>6.9467600483618303E-2</v>
       </c>
       <c r="AF31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AF$9))</f>
-        <v>0.46885155151770208</v>
+        <v>7.785305428056051E-2</v>
       </c>
       <c r="AG31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AG$9))</f>
-        <v>0.47654178751308102</v>
+        <v>8.6947341668358144E-2</v>
       </c>
       <c r="AH31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AH$9))</f>
-        <v>0.48240545802402607</v>
+        <v>9.6713504774003714E-2</v>
       </c>
       <c r="AI31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AI$9))</f>
-        <v>0.48684435551659033</v>
+        <v>0.10709063902446933</v>
       </c>
       <c r="AJ31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AJ$9))</f>
-        <v>0.4901864093050462</v>
+        <v>0.11799355797925228</v>
       </c>
       <c r="AK31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AK$9))</f>
-        <v>0.49269233539566731</v>
+        <v>0.12931427170136311</v>
       </c>
       <c r="AL31">
         <f>IF($F31="s-curve",$D31+($E31-$D31)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D31:$E31,$D$9:$E$9,AL$9))</f>
-        <v>0.4945655394926507</v>
+        <v>0.14092541448449677</v>
       </c>
     </row>
     <row r="32" spans="1:38">
@@ -19768,12 +20977,11 @@
         <v>4</v>
       </c>
       <c r="D34" s="20">
-        <f>MIN(1.25*INDEX('SYVbT-freight'!$B$3:$H$3,MATCH(Data!$C13,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-freight'!$B$3:$H$3),1)*3</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" s="20">
         <f t="shared" si="26"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="str">
         <f>IF(D34=E34,"n/a",IF(OR(C34="battery electric vehicle",C34="natural gas vehicle",C34="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -19781,127 +20989,127 @@
       </c>
       <c r="H34" s="20">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,I$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,J$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,K$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,L$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,M$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,N$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,O$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,P$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,Q$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,R$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,S$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,T$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,U$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,V$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,W$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,X$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,Y$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,Z$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,AA$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,AB$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,AC$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,AD$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,AE$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,AF$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,AG$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,AH$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,AI$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,AJ$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,AK$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL34">
         <f>IF($F34="s-curve",$D34+($E34-$D34)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D34:$E34,$D$9:$E$9,AL$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:38">
@@ -20050,12 +21258,11 @@
         <v>78</v>
       </c>
       <c r="D36" s="20">
-        <f>MIN(1.25*INDEX('SYVbT-freight'!$B$3:$H$3,MATCH(Data!$C15,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-freight'!$B$3:$H$3),1)</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="E36" s="20">
         <f t="shared" si="26"/>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="F36" s="6" t="str">
         <f>IF(D36=E36,"n/a",IF(OR(C36="battery electric vehicle",C36="natural gas vehicle",C36="plugin hybrid vehicle",C36="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -20063,127 +21270,127 @@
       </c>
       <c r="H36" s="20">
         <f t="shared" si="23"/>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,I$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="J36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,J$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,K$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="L36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,L$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="M36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,M$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="N36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,N$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="O36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,O$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="P36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,P$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Q36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,Q$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="R36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,R$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="S36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,S$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="T36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,T$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="U36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,U$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="V36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,V$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="W36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,W$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="X36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,X$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Y36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,Y$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Z36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,Z$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AA36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,AA$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AB36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,AB$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AC36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,AC$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AD36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,AD$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AE36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,AE$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AF36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,AF$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AG36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,AG$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AH36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,AH$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AI36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,AI$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AJ36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,AJ$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AK36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,AK$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AL36">
         <f>IF($F36="s-curve",$D36+($E36-$D36)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D36:$E36,$D$9:$E$9,AL$9))</f>
-        <v>4.2398960612661157E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="37" spans="1:38" ht="15.75" thickBot="1">
@@ -20193,140 +21400,139 @@
         <v>79</v>
       </c>
       <c r="D37" s="21">
-        <f>MIN(1.25*INDEX('SYVbT-freight'!$B$3:$H$3,MATCH(Data!$C16,'SYVbT-passenger'!$B$1:$H$1,0))/SUM('SYVbT-freight'!$B$3:$H$3),1)</f>
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="E37" s="24">
-        <f>E36</f>
-        <v>4.2398960612661157E-2</v>
+        <f>D37</f>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="F37" s="7" t="str">
         <f>IF(D37=E37,"n/a",IF(OR(C37="battery electric vehicle",C37="natural gas vehicle",C37="plugin hybrid vehicle",C37="hydrogen vehicle"),"s-curve","linear"))</f>
-        <v>s-curve</v>
+        <v>n/a</v>
       </c>
       <c r="H37" s="20">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="I37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,I$9))</f>
-        <v>6.2640358785329186E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="J37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,J$9))</f>
-        <v>8.4120834136230764E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="K37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,K$9))</f>
-        <v>1.1276848830807375E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="L37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,L$9))</f>
-        <v>1.5081814529160165E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="M37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,M$9))</f>
-        <v>2.0108077288767171E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="N37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,N$9))</f>
-        <v>2.6700048431076819E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="O37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,O$9))</f>
-        <v>3.5264358826946353E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="P37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,P$9))</f>
-        <v>4.6255918248393289E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,Q$9))</f>
-        <v>6.0143377135798244E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="R37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,R$9))</f>
-        <v>7.7346525986097831E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="S37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,S$9))</f>
-        <v>9.8143085872323659E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="T37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,T$9))</f>
-        <v>1.2255440653272574E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="U37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,U$9))</f>
-        <v>1.5023804315677364E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="V37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,V$9))</f>
-        <v>1.8043194968125682E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="W37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,W$9))</f>
-        <v>2.1199480306330579E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="X37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,X$9))</f>
-        <v>2.4355765644535475E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Y37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,Y$9))</f>
-        <v>2.7375156296983789E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Z37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,Z$9))</f>
-        <v>3.014351995938858E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AA37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,AA$9))</f>
-        <v>3.258465202542879E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AB37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,AB$9))</f>
-        <v>3.4664308014051376E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AC37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,AC$9))</f>
-        <v>3.6384622899081336E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AD37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,AD$9))</f>
-        <v>3.777336878782183E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AE37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,AE$9))</f>
-        <v>3.8872524729966523E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AF37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,AF$9))</f>
-        <v>3.972895576955348E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AG37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,AG$9))</f>
-        <v>4.0388152883784445E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AH37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,AH$9))</f>
-        <v>4.0890779159745143E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AI37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,AI$9))</f>
-        <v>4.127127572958042E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AJ37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,AJ$9))</f>
-        <v>4.1557752271298855E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AK37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,AK$9))</f>
-        <v>4.1772557024807866E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AL37">
         <f>IF($F37="s-curve",$D37+($E37-$D37)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D37:$E37,$D$9:$E$9,AL$9))</f>
-        <v>4.1933125664813074E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="38" spans="1:38">
@@ -26279,123 +27485,123 @@
       </c>
       <c r="I80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,I$9))</f>
-        <v>1.4774031693273055E-2</v>
+        <v>8.1625711531598966E-3</v>
       </c>
       <c r="J80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,J$9))</f>
-        <v>1.984030573407751E-2</v>
+        <v>9.5653186720916755E-3</v>
       </c>
       <c r="K80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,K$9))</f>
-        <v>2.6596993576865863E-2</v>
+        <v>1.1206406321842867E-2</v>
       </c>
       <c r="L80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,L$9))</f>
-        <v>3.5571189272636181E-2</v>
+        <v>1.3125318337102799E-2</v>
       </c>
       <c r="M80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,M$9))</f>
-        <v>4.7425873177566781E-2</v>
+        <v>1.5367705565275549E-2</v>
       </c>
       <c r="N80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,N$9))</f>
-        <v>6.2973356056996513E-2</v>
+        <v>1.7986209962091559E-2</v>
       </c>
       <c r="O80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,O$9))</f>
-        <v>8.317269649392238E-2</v>
+        <v>2.1041347020468282E-2</v>
       </c>
       <c r="P80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,P$9))</f>
-        <v>0.10909682119561293</v>
+        <v>2.4602428402739435E-2</v>
       </c>
       <c r="Q80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,Q$9))</f>
-        <v>0.14185106490048782</v>
+        <v>2.8748495926539969E-2</v>
       </c>
       <c r="R80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,R$9))</f>
-        <v>0.18242552380635635</v>
+        <v>3.356922328148252E-2</v>
       </c>
       <c r="S80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,S$9))</f>
-        <v>0.23147521650098238</v>
+        <v>3.9165722796764356E-2</v>
       </c>
       <c r="T80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,T$9))</f>
-        <v>0.28905049737499605</v>
+        <v>4.5651170784443723E-2</v>
       </c>
       <c r="U80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,U$9))</f>
-        <v>0.35434369377420455</v>
+        <v>5.3151136398063722E-2</v>
       </c>
       <c r="V80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,V$9))</f>
-        <v>0.42555748318834102</v>
+        <v>6.1803466263588569E-2</v>
       </c>
       <c r="W80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,W$9))</f>
-        <v>0.5</v>
+        <v>7.1757542263751334E-2</v>
       </c>
       <c r="X80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,X$9))</f>
-        <v>0.57444251681165903</v>
+        <v>8.317269649392238E-2</v>
       </c>
       <c r="Y80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,Y$9))</f>
-        <v>0.6456563062257954</v>
+        <v>9.6215541710692826E-2</v>
       </c>
       <c r="Z80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,Z$9))</f>
-        <v>0.71094950262500389</v>
+        <v>0.11105596671140756</v>
       </c>
       <c r="AA80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AA$9))</f>
-        <v>0.76852478349901754</v>
+        <v>0.12786156631908133</v>
       </c>
       <c r="AB80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AB$9))</f>
-        <v>0.81757447619364365</v>
+        <v>0.14679033980138237</v>
       </c>
       <c r="AC80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AC$9))</f>
-        <v>0.85814893509951229</v>
+        <v>0.16798161486607552</v>
       </c>
       <c r="AD80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AD$9))</f>
-        <v>0.89090317880438707</v>
+        <v>0.19154534856146752</v>
       </c>
       <c r="AE80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AE$9))</f>
-        <v>0.91682730350607766</v>
+        <v>0.2175502235768875</v>
       </c>
       <c r="AF80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AF$9))</f>
-        <v>0.9370266439430035</v>
+        <v>0.2460112835510519</v>
       </c>
       <c r="AG80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AG$9))</f>
-        <v>0.95257412682243336</v>
+        <v>0.27687819487561016</v>
       </c>
       <c r="AH80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AH$9))</f>
-        <v>0.96442881072736386</v>
+        <v>0.31002551887238755</v>
       </c>
       <c r="AI80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AI$9))</f>
-        <v>0.97340300642313404</v>
+        <v>0.34524653939368077</v>
       </c>
       <c r="AJ80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AJ$9))</f>
-        <v>0.98015969426592253</v>
+        <v>0.38225212523075103</v>
       </c>
       <c r="AK80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AK$9))</f>
-        <v>0.98522596830672693</v>
+        <v>0.42067574785125056</v>
       </c>
       <c r="AL80">
         <f>IF($F80="s-curve",$D80+($E80-$D80)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D80:$E80,$D$9:$E$9,AL$9))</f>
-        <v>0.98901305736940681</v>
+        <v>0.46008511544443426</v>
       </c>
     </row>
     <row r="81" spans="1:38">
@@ -27267,123 +28473,123 @@
       </c>
       <c r="I87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,I$9))</f>
-        <v>1.4774031693273055E-2</v>
+        <v>8.1625711531598966E-3</v>
       </c>
       <c r="J87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,J$9))</f>
-        <v>1.984030573407751E-2</v>
+        <v>9.5653186720916755E-3</v>
       </c>
       <c r="K87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,K$9))</f>
-        <v>2.6596993576865863E-2</v>
+        <v>1.1206406321842867E-2</v>
       </c>
       <c r="L87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,L$9))</f>
-        <v>3.5571189272636181E-2</v>
+        <v>1.3125318337102799E-2</v>
       </c>
       <c r="M87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,M$9))</f>
-        <v>4.7425873177566781E-2</v>
+        <v>1.5367705565275549E-2</v>
       </c>
       <c r="N87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,N$9))</f>
-        <v>6.2973356056996513E-2</v>
+        <v>1.7986209962091559E-2</v>
       </c>
       <c r="O87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,O$9))</f>
-        <v>8.317269649392238E-2</v>
+        <v>2.1041347020468282E-2</v>
       </c>
       <c r="P87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,P$9))</f>
-        <v>0.10909682119561293</v>
+        <v>2.4602428402739435E-2</v>
       </c>
       <c r="Q87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,Q$9))</f>
-        <v>0.14185106490048782</v>
+        <v>2.8748495926539969E-2</v>
       </c>
       <c r="R87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,R$9))</f>
-        <v>0.18242552380635635</v>
+        <v>3.356922328148252E-2</v>
       </c>
       <c r="S87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,S$9))</f>
-        <v>0.23147521650098238</v>
+        <v>3.9165722796764356E-2</v>
       </c>
       <c r="T87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,T$9))</f>
-        <v>0.28905049737499605</v>
+        <v>4.5651170784443723E-2</v>
       </c>
       <c r="U87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,U$9))</f>
-        <v>0.35434369377420455</v>
+        <v>5.3151136398063722E-2</v>
       </c>
       <c r="V87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,V$9))</f>
-        <v>0.42555748318834102</v>
+        <v>6.1803466263588569E-2</v>
       </c>
       <c r="W87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,W$9))</f>
-        <v>0.5</v>
+        <v>7.1757542263751334E-2</v>
       </c>
       <c r="X87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,X$9))</f>
-        <v>0.57444251681165903</v>
+        <v>8.317269649392238E-2</v>
       </c>
       <c r="Y87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,Y$9))</f>
-        <v>0.6456563062257954</v>
+        <v>9.6215541710692826E-2</v>
       </c>
       <c r="Z87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,Z$9))</f>
-        <v>0.71094950262500389</v>
+        <v>0.11105596671140756</v>
       </c>
       <c r="AA87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,AA$9))</f>
-        <v>0.76852478349901754</v>
+        <v>0.12786156631908133</v>
       </c>
       <c r="AB87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,AB$9))</f>
-        <v>0.81757447619364365</v>
+        <v>0.14679033980138237</v>
       </c>
       <c r="AC87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,AC$9))</f>
-        <v>0.85814893509951229</v>
+        <v>0.16798161486607552</v>
       </c>
       <c r="AD87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,AD$9))</f>
-        <v>0.89090317880438707</v>
+        <v>0.19154534856146752</v>
       </c>
       <c r="AE87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,AE$9))</f>
-        <v>0.91682730350607766</v>
+        <v>0.2175502235768875</v>
       </c>
       <c r="AF87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,AF$9))</f>
-        <v>0.9370266439430035</v>
+        <v>0.2460112835510519</v>
       </c>
       <c r="AG87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,AG$9))</f>
-        <v>0.95257412682243336</v>
+        <v>0.27687819487561016</v>
       </c>
       <c r="AH87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,AH$9))</f>
-        <v>0.96442881072736386</v>
+        <v>0.31002551887238755</v>
       </c>
       <c r="AI87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,AI$9))</f>
-        <v>0.97340300642313404</v>
+        <v>0.34524653939368077</v>
       </c>
       <c r="AJ87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,AJ$9))</f>
-        <v>0.98015969426592253</v>
+        <v>0.38225212523075103</v>
       </c>
       <c r="AK87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,AK$9))</f>
-        <v>0.98522596830672693</v>
+        <v>0.42067574785125056</v>
       </c>
       <c r="AL87">
         <f>IF($F87="s-curve",$D87+($E87-$D87)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D87:$E87,$D$9:$E$9,AL$9))</f>
-        <v>0.98901305736940681</v>
+        <v>0.46008511544443426</v>
       </c>
     </row>
     <row r="88" spans="1:38">
@@ -28411,59 +29617,59 @@
       </c>
       <c r="H2">
         <f>Data!N10</f>
-        <v>0.30932775069106316</v>
+        <v>0.30732775069106316</v>
       </c>
       <c r="I2">
         <f>Data!O10</f>
-        <v>0.35199581301829735</v>
+        <v>0.34799581301829735</v>
       </c>
       <c r="J2">
         <f>Data!P10</f>
-        <v>0.39466387534553155</v>
+        <v>0.38866387534553154</v>
       </c>
       <c r="K2">
         <f>Data!Q10</f>
-        <v>0.43733193767276574</v>
+        <v>0.42933193767276573</v>
       </c>
       <c r="L2">
         <f>Data!R10</f>
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="M2">
         <f>Data!S10</f>
-        <v>0.504</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="N2">
         <f>Data!T10</f>
-        <v>0.52800000000000002</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="O2">
         <f>Data!U10</f>
-        <v>0.55200000000000005</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="P2">
         <f>Data!V10</f>
-        <v>0.57600000000000007</v>
+        <v>0.56600000000000006</v>
       </c>
       <c r="Q2">
         <f>Data!W10</f>
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="R2">
         <f>Data!X10</f>
-        <v>0.64600000000000002</v>
+        <v>0.63800000000000001</v>
       </c>
       <c r="S2">
         <f>Data!Y10</f>
-        <v>0.69200000000000006</v>
+        <v>0.68600000000000005</v>
       </c>
       <c r="T2">
         <f>Data!Z10</f>
-        <v>0.7380000000000001</v>
+        <v>0.7340000000000001</v>
       </c>
       <c r="U2">
         <f>Data!AA10</f>
-        <v>0.78400000000000014</v>
+        <v>0.78200000000000014</v>
       </c>
       <c r="V2">
         <f>Data!AB10</f>
@@ -28471,39 +29677,39 @@
       </c>
       <c r="W2">
         <f>Data!AC10</f>
-        <v>0.94399999999999995</v>
+        <v>0.94199999999999995</v>
       </c>
       <c r="X2">
         <f>Data!AD10</f>
-        <v>1.0579999999999998</v>
+        <v>1.0539999999999998</v>
       </c>
       <c r="Y2">
         <f>Data!AE10</f>
-        <v>1.1719999999999997</v>
+        <v>1.1659999999999999</v>
       </c>
       <c r="Z2">
         <f>Data!AF10</f>
-        <v>1.2859999999999996</v>
+        <v>1.278</v>
       </c>
       <c r="AA2">
         <f>Data!AG10</f>
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB2">
         <f>Data!AH10</f>
-        <v>1.64</v>
+        <v>1.6319999999999999</v>
       </c>
       <c r="AC2">
         <f>Data!AI10</f>
-        <v>1.88</v>
+        <v>1.8739999999999999</v>
       </c>
       <c r="AD2">
         <f>Data!AJ10</f>
-        <v>2.12</v>
+        <v>2.1160000000000001</v>
       </c>
       <c r="AE2">
         <f>Data!AK10</f>
-        <v>2.3600000000000003</v>
+        <v>2.3580000000000001</v>
       </c>
       <c r="AF2">
         <f>Data!AL10</f>
@@ -29436,127 +30642,127 @@
       </c>
       <c r="B2">
         <f>Data!H17</f>
-        <v>0.05</v>
+        <v>7.0544063074398172E-2</v>
       </c>
       <c r="C2">
         <f>Data!I17</f>
-        <v>5.6648314261972879E-2</v>
+        <v>7.4079584901821705E-2</v>
       </c>
       <c r="D2">
         <f>Data!J17</f>
-        <v>5.8928137580334883E-2</v>
+        <v>7.8217690082670446E-2</v>
       </c>
       <c r="E2">
         <f>Data!K17</f>
-        <v>6.1968647109589645E-2</v>
+        <v>8.3058898649436469E-2</v>
       </c>
       <c r="F2">
         <f>Data!L17</f>
-        <v>6.6007035172686288E-2</v>
+        <v>8.8719689094453269E-2</v>
       </c>
       <c r="G2">
         <f>Data!M17</f>
-        <v>7.1341642929905053E-2</v>
+        <v>9.5334731417562879E-2</v>
       </c>
       <c r="H2">
         <f>Data!N17</f>
-        <v>7.833801022564843E-2</v>
+        <v>0.1030593193881701</v>
       </c>
       <c r="I2">
         <f>Data!O17</f>
-        <v>8.7427713422265074E-2</v>
+        <v>0.11207197371038144</v>
       </c>
       <c r="J2">
         <f>Data!P17</f>
-        <v>9.9093569538025811E-2</v>
+        <v>0.12257716378808134</v>
       </c>
       <c r="K2">
         <f>Data!Q17</f>
-        <v>0.11383297920521952</v>
+        <v>0.13480806298329293</v>
       </c>
       <c r="L2">
         <f>Data!R17</f>
-        <v>0.13209148571286036</v>
+        <v>0.14902920868037345</v>
       </c>
       <c r="M2">
         <f>Data!S17</f>
-        <v>0.15416384742544209</v>
+        <v>0.16553888225045485</v>
       </c>
       <c r="N2">
         <f>Data!T17</f>
-        <v>0.18007272381874823</v>
+        <v>0.18467095381410897</v>
       </c>
       <c r="O2">
         <f>Data!U17</f>
-        <v>0.20945466219839204</v>
+        <v>0.20679585237428799</v>
       </c>
       <c r="P2">
         <f>Data!V17</f>
-        <v>0.24150086743475346</v>
+        <v>0.2323202254775863</v>
       </c>
       <c r="Q2">
         <f>Data!W17</f>
-        <v>0.27500000000000002</v>
+        <v>0.26168474967806649</v>
       </c>
       <c r="R2">
         <f>Data!X17</f>
-        <v>0.30849913256524658</v>
+        <v>0.29535945465707103</v>
       </c>
       <c r="S2">
         <f>Data!Y17</f>
-        <v>0.34054533780160795</v>
+        <v>0.33383584804654387</v>
       </c>
       <c r="T2">
         <f>Data!Z17</f>
-        <v>0.36992727618125176</v>
+        <v>0.37761510179865232</v>
       </c>
       <c r="U2">
         <f>Data!AA17</f>
-        <v>0.3958361525745579</v>
+        <v>0.42719162064128996</v>
       </c>
       <c r="V2">
         <f>Data!AB17</f>
-        <v>0.4179085142871396</v>
+        <v>0.48303150241407805</v>
       </c>
       <c r="W2">
         <f>Data!AC17</f>
-        <v>0.43616702079478054</v>
+        <v>0.54554576385492282</v>
       </c>
       <c r="X2">
         <f>Data!AD17</f>
-        <v>0.45090643046197421</v>
+        <v>0.61505877825632926</v>
       </c>
       <c r="Y2">
         <f>Data!AE17</f>
-        <v>0.46257228657773497</v>
+        <v>0.69177315955181817</v>
       </c>
       <c r="Z2">
         <f>Data!AF17</f>
-        <v>0.47166198977435159</v>
+        <v>0.77573328647560325</v>
       </c>
       <c r="AA2">
         <f>Data!AG17</f>
-        <v>0.47865835707009496</v>
+        <v>0.86679067488305006</v>
       </c>
       <c r="AB2">
         <f>Data!AH17</f>
-        <v>0.48399296482731374</v>
+        <v>0.96457528067354337</v>
       </c>
       <c r="AC2">
         <f>Data!AI17</f>
-        <v>0.48803135289041033</v>
+        <v>1.0684772912113583</v>
       </c>
       <c r="AD2">
         <f>Data!AJ17</f>
-        <v>0.49107186241966516</v>
+        <v>1.1776437694307156</v>
       </c>
       <c r="AE2">
         <f>Data!AK17</f>
-        <v>0.49335168573802712</v>
+        <v>1.2909934561611893</v>
       </c>
       <c r="AF2">
         <f>Data!AL17</f>
-        <v>0.49505587581623306</v>
+        <v>1.4072510905610811</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -29694,127 +30900,127 @@
       </c>
       <c r="B4">
         <f>Data!H19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="C4">
         <f>Data!I19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="D4">
         <f>Data!J19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="E4">
         <f>Data!K19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="F4">
         <f>Data!L19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G4">
         <f>Data!M19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="H4">
         <f>Data!N19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="I4">
         <f>Data!O19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="J4">
         <f>Data!P19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="K4">
         <f>Data!Q19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="L4">
         <f>Data!R19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="M4">
         <f>Data!S19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="N4">
         <f>Data!T19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="O4">
         <f>Data!U19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="P4">
         <f>Data!V19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="Q4">
         <f>Data!W19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="R4">
         <f>Data!X19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="S4">
         <f>Data!Y19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="T4">
         <f>Data!Z19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="U4">
         <f>Data!AA19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="V4">
         <f>Data!AB19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="W4">
         <f>Data!AC19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="X4">
         <f>Data!AD19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="Y4">
         <f>Data!AE19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="Z4">
         <f>Data!AF19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AA4">
         <f>Data!AG19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AB4">
         <f>Data!AH19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AC4">
         <f>Data!AI19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AD4">
         <f>Data!AJ19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AE4">
         <f>Data!AK19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AF4">
         <f>Data!AL19</f>
-        <v>1.9186119393907859E-2</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -29823,127 +31029,127 @@
       </c>
       <c r="B5">
         <f>Data!H20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <f>Data!I20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <f>Data!J20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <f>Data!K20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <f>Data!L20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <f>Data!M20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <f>Data!N20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <f>Data!O20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <f>Data!P20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <f>Data!Q20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <f>Data!R20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <f>Data!S20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N5">
         <f>Data!T20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <f>Data!U20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P5">
         <f>Data!V20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q5">
         <f>Data!W20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R5">
         <f>Data!X20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S5">
         <f>Data!Y20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T5">
         <f>Data!Z20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5">
         <f>Data!AA20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V5">
         <f>Data!AB20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W5">
         <f>Data!AC20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X5">
         <f>Data!AD20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y5">
         <f>Data!AE20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z5">
         <f>Data!AF20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA5">
         <f>Data!AG20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB5">
         <f>Data!AH20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC5">
         <f>Data!AI20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD5">
         <f>Data!AJ20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE5">
         <f>Data!AK20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF5">
         <f>Data!AL20</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -29956,123 +31162,123 @@
       </c>
       <c r="C6">
         <f>Data!I21</f>
-        <v>3.6935079233182638E-3</v>
+        <v>2.0406427882899742E-3</v>
       </c>
       <c r="D6">
         <f>Data!J21</f>
-        <v>4.9600764335193774E-3</v>
+        <v>2.3913296680229189E-3</v>
       </c>
       <c r="E6">
         <f>Data!K21</f>
-        <v>6.6492483942164659E-3</v>
+        <v>2.8016015804607167E-3</v>
       </c>
       <c r="F6">
         <f>Data!L21</f>
-        <v>8.8927973181590451E-3</v>
+        <v>3.2813295842756998E-3</v>
       </c>
       <c r="G6">
         <f>Data!M21</f>
-        <v>1.1856468294391695E-2</v>
+        <v>3.8419263913188873E-3</v>
       </c>
       <c r="H6">
         <f>Data!N21</f>
-        <v>1.5743339014249128E-2</v>
+        <v>4.4965524905228897E-3</v>
       </c>
       <c r="I6">
         <f>Data!O21</f>
-        <v>2.0793174123480595E-2</v>
+        <v>5.2603367551170704E-3</v>
       </c>
       <c r="J6">
         <f>Data!P21</f>
-        <v>2.7274205298903231E-2</v>
+        <v>6.1506071006848587E-3</v>
       </c>
       <c r="K6">
         <f>Data!Q21</f>
-        <v>3.5462766225121956E-2</v>
+        <v>7.1871239816349922E-3</v>
       </c>
       <c r="L6">
         <f>Data!R21</f>
-        <v>4.5606380951589087E-2</v>
+        <v>8.39230582037063E-3</v>
       </c>
       <c r="M6">
         <f>Data!S21</f>
-        <v>5.7868804125245595E-2</v>
+        <v>9.791430699191089E-3</v>
       </c>
       <c r="N6">
         <f>Data!T21</f>
-        <v>7.2262624343749013E-2</v>
+        <v>1.1412792696110931E-2</v>
       </c>
       <c r="O6">
         <f>Data!U21</f>
-        <v>8.8585923443551137E-2</v>
+        <v>1.3287784099515931E-2</v>
       </c>
       <c r="P6">
         <f>Data!V21</f>
-        <v>0.10638937079708526</v>
+        <v>1.5450866565897142E-2</v>
       </c>
       <c r="Q6">
         <f>Data!W21</f>
-        <v>0.125</v>
+        <v>1.7939385565937833E-2</v>
       </c>
       <c r="R6">
         <f>Data!X21</f>
-        <v>0.14361062920291476</v>
+        <v>2.0793174123480595E-2</v>
       </c>
       <c r="S6">
         <f>Data!Y21</f>
-        <v>0.16141407655644885</v>
+        <v>2.4053885427673206E-2</v>
       </c>
       <c r="T6">
         <f>Data!Z21</f>
-        <v>0.17773737565625097</v>
+        <v>2.7763991677851891E-2</v>
       </c>
       <c r="U6">
         <f>Data!AA21</f>
-        <v>0.19213119587475438</v>
+        <v>3.1965391579770332E-2</v>
       </c>
       <c r="V6">
         <f>Data!AB21</f>
-        <v>0.20439361904841091</v>
+        <v>3.6697584950345592E-2</v>
       </c>
       <c r="W6">
         <f>Data!AC21</f>
-        <v>0.21453723377487807</v>
+        <v>4.199540371651888E-2</v>
       </c>
       <c r="X6">
         <f>Data!AD21</f>
-        <v>0.22272579470109677</v>
+        <v>4.7886337140366879E-2</v>
       </c>
       <c r="Y6">
         <f>Data!AE21</f>
-        <v>0.22920682587651942</v>
+        <v>5.4387555894221874E-2</v>
       </c>
       <c r="Z6">
         <f>Data!AF21</f>
-        <v>0.23425666098575088</v>
+        <v>6.1502820887762974E-2</v>
       </c>
       <c r="AA6">
         <f>Data!AG21</f>
-        <v>0.23814353170560834</v>
+        <v>6.921954871890254E-2</v>
       </c>
       <c r="AB6">
         <f>Data!AH21</f>
-        <v>0.24110720268184097</v>
+        <v>7.7506379718096888E-2</v>
       </c>
       <c r="AC6">
         <f>Data!AI21</f>
-        <v>0.24335075160578351</v>
+        <v>8.6311634848420193E-2</v>
       </c>
       <c r="AD6">
         <f>Data!AJ21</f>
-        <v>0.24503992356648063</v>
+        <v>9.5563031307687757E-2</v>
       </c>
       <c r="AE6">
         <f>Data!AK21</f>
-        <v>0.24630649207668173</v>
+        <v>0.10516893696281264</v>
       </c>
       <c r="AF6">
         <f>Data!AL21</f>
-        <v>0.2472532643423517</v>
+        <v>0.11502127886110856</v>
       </c>
     </row>
     <row r="7" spans="1:32">
@@ -30081,127 +31287,127 @@
       </c>
       <c r="B7">
         <f>Data!H22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
         <f>Data!I22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="D7">
         <f>Data!J22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="E7">
         <f>Data!K22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="F7">
         <f>Data!L22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="G7">
         <f>Data!M22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H7">
         <f>Data!N22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I7">
         <f>Data!O22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="J7">
         <f>Data!P22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K7">
         <f>Data!Q22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="L7">
         <f>Data!R22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="M7">
         <f>Data!S22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="N7">
         <f>Data!T22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="O7">
         <f>Data!U22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="P7">
         <f>Data!V22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Q7">
         <f>Data!W22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="R7">
         <f>Data!X22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="S7">
         <f>Data!Y22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="T7">
         <f>Data!Z22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="U7">
         <f>Data!AA22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="V7">
         <f>Data!AB22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="W7">
         <f>Data!AC22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="X7">
         <f>Data!AD22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Y7">
         <f>Data!AE22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Z7">
         <f>Data!AF22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AA7">
         <f>Data!AG22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AB7">
         <f>Data!AH22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AC7">
         <f>Data!AI22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AD7">
         <f>Data!AJ22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AE7">
         <f>Data!AK22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AF7">
         <f>Data!AL22</f>
-        <v>4.237817368977314E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:32">
@@ -30210,127 +31416,127 @@
       </c>
       <c r="B8">
         <f>Data!H23</f>
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="C8">
         <f>Data!I23</f>
-        <v>9.0540738828139446E-6</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="D8">
         <f>Data!J23</f>
-        <v>1.2158874280454334E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="E8">
         <f>Data!K23</f>
-        <v>1.6299622872429478E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="F8">
         <f>Data!L23</f>
-        <v>2.179934241786213E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="G8">
         <f>Data!M23</f>
-        <v>2.9064331837203784E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="H8">
         <f>Data!N23</f>
-        <v>3.85924052571516E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="I8">
         <f>Data!O23</f>
-        <v>5.0971309302911188E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="J8">
         <f>Data!P23</f>
-        <v>6.6858573204156302E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="K8">
         <f>Data!Q23</f>
-        <v>8.6931587032511697E-5</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="L8">
         <f>Data!R23</f>
-        <v>1.1179711841323839E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="M8">
         <f>Data!S23</f>
-        <v>1.4185658700018285E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="N8">
         <f>Data!T23</f>
-        <v>1.7714085182915572E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="O8">
         <f>Data!U23</f>
-        <v>2.1715494117977539E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="P8">
         <f>Data!V23</f>
-        <v>2.6079738924114821E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q8">
         <f>Data!W23</f>
-        <v>3.0641852105056964E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="R8">
         <f>Data!X23</f>
-        <v>3.5203965285999107E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="S8">
         <f>Data!Y23</f>
-        <v>3.9568210092136389E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="T8">
         <f>Data!Z23</f>
-        <v>4.3569619027198356E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="U8">
         <f>Data!AA23</f>
-        <v>4.709804551009564E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="V8">
         <f>Data!AB23</f>
-        <v>5.010399236879009E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="W8">
         <f>Data!AC23</f>
-        <v>5.2590545506862765E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="X8">
         <f>Data!AD23</f>
-        <v>5.4597846889698301E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Y8">
         <f>Data!AE23</f>
-        <v>5.6186573279822817E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Z8">
         <f>Data!AF23</f>
-        <v>5.7424463684398771E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AA8">
         <f>Data!AG23</f>
-        <v>5.8377271026393554E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AB8">
         <f>Data!AH23</f>
-        <v>5.9103769968327712E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AC8">
         <f>Data!AI23</f>
-        <v>5.9653741922870976E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AD8">
         <f>Data!AJ23</f>
-        <v>6.0067816782068497E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AE8">
         <f>Data!AK23</f>
-        <v>6.0378296821832537E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AF8">
         <f>Data!AL23</f>
-        <v>6.0610383667767168E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
   </sheetData>
@@ -30485,127 +31691,127 @@
       </c>
       <c r="B2">
         <f>Data!H24</f>
-        <v>0.05</v>
+        <v>9.7368870468605012E-2</v>
       </c>
       <c r="C2">
         <f>Data!I24</f>
-        <v>6.4035330108609401E-2</v>
+        <v>0.1020789046319184</v>
       </c>
       <c r="D2">
         <f>Data!J24</f>
-        <v>6.8848290447373631E-2</v>
+        <v>0.10759170238132029</v>
       </c>
       <c r="E2">
         <f>Data!K24</f>
-        <v>7.5267143898022582E-2</v>
+        <v>0.11404117684484247</v>
       </c>
       <c r="F2">
         <f>Data!L24</f>
-        <v>8.3792629809004371E-2</v>
+        <v>0.121582501064814</v>
       </c>
       <c r="G2">
         <f>Data!M24</f>
-        <v>9.505457951868844E-2</v>
+        <v>0.13039508287153292</v>
       </c>
       <c r="H2">
         <f>Data!N24</f>
-        <v>0.10982468825414668</v>
+        <v>0.14068580515101983</v>
       </c>
       <c r="I2">
         <f>Data!O24</f>
-        <v>0.12901406166922624</v>
+        <v>0.15269249379044036</v>
       </c>
       <c r="J2">
         <f>Data!P24</f>
-        <v>0.15364198013583227</v>
+        <v>0.166687543622766</v>
       </c>
       <c r="K2">
         <f>Data!Q24</f>
-        <v>0.18475851165546342</v>
+        <v>0.1829815889913021</v>
       </c>
       <c r="L2">
         <f>Data!R24</f>
-        <v>0.22330424761603851</v>
+        <v>0.20192704749622634</v>
       </c>
       <c r="M2">
         <f>Data!S24</f>
-        <v>0.26990145567593327</v>
+        <v>0.22392129059128393</v>
       </c>
       <c r="N2">
         <f>Data!T24</f>
-        <v>0.32459797250624622</v>
+        <v>0.24940910118286383</v>
       </c>
       <c r="O2">
         <f>Data!U24</f>
-        <v>0.38662650908549429</v>
+        <v>0.27888396604439047</v>
       </c>
       <c r="P2">
         <f>Data!V24</f>
-        <v>0.45427960902892389</v>
+        <v>0.31288762241590307</v>
       </c>
       <c r="Q2">
         <f>Data!W24</f>
-        <v>0.52500000000000002</v>
+        <v>0.3520071410965428</v>
       </c>
       <c r="R2">
         <f>Data!X24</f>
-        <v>0.5957203909710761</v>
+        <v>0.39686869722111495</v>
       </c>
       <c r="S2">
         <f>Data!Y24</f>
-        <v>0.6633734909145057</v>
+        <v>0.44812707892302284</v>
       </c>
       <c r="T2">
         <f>Data!Z24</f>
-        <v>0.72540202749375371</v>
+        <v>0.50644994917583175</v>
       </c>
       <c r="U2">
         <f>Data!AA24</f>
-        <v>0.78009854432406667</v>
+        <v>0.57249595563398969</v>
       </c>
       <c r="V2">
         <f>Data!AB24</f>
-        <v>0.82669575238396142</v>
+        <v>0.64688603541943279</v>
       </c>
       <c r="W2">
         <f>Data!AC24</f>
-        <v>0.86524148834453662</v>
+        <v>0.73016774642367688</v>
       </c>
       <c r="X2">
         <f>Data!AD24</f>
-        <v>0.89635801986416774</v>
+        <v>0.82277321984656737</v>
       </c>
       <c r="Y2">
         <f>Data!AE24</f>
-        <v>0.9209859383307738</v>
+        <v>0.92497237865716797</v>
       </c>
       <c r="Z2">
         <f>Data!AF24</f>
-        <v>0.94017531174585334</v>
+        <v>1.036824344355634</v>
       </c>
       <c r="AA2">
         <f>Data!AG24</f>
-        <v>0.9549454204813117</v>
+        <v>1.158131305861148</v>
       </c>
       <c r="AB2">
         <f>Data!AH24</f>
-        <v>0.96620737019099567</v>
+        <v>1.2884002891684831</v>
       </c>
       <c r="AC2">
         <f>Data!AI24</f>
-        <v>0.97473285610197735</v>
+        <v>1.4268188998171656</v>
       </c>
       <c r="AD2">
         <f>Data!AJ24</f>
-        <v>0.98115170955262643</v>
+        <v>1.5722508521568517</v>
       </c>
       <c r="AE2">
         <f>Data!AK24</f>
-        <v>0.98596466989139064</v>
+        <v>1.7232556890554149</v>
       </c>
       <c r="AF2">
         <f>Data!AL24</f>
-        <v>0.98956240450093647</v>
+        <v>1.8781345036966268</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -30743,127 +31949,127 @@
       </c>
       <c r="B4">
         <f>Data!H26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <f>Data!I26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <f>Data!J26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>Data!K26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <f>Data!L26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <f>Data!M26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <f>Data!N26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <f>Data!O26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <f>Data!P26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <f>Data!Q26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <f>Data!R26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="M4">
         <f>Data!S26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="N4">
         <f>Data!T26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="O4">
         <f>Data!U26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="P4">
         <f>Data!V26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="Q4">
         <f>Data!W26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <f>Data!X26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="S4">
         <f>Data!Y26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="T4">
         <f>Data!Z26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="U4">
         <f>Data!AA26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="V4">
         <f>Data!AB26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="W4">
         <f>Data!AC26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="X4">
         <f>Data!AD26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="Y4">
         <f>Data!AE26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="Z4">
         <f>Data!AF26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AA4">
         <f>Data!AG26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AB4">
         <f>Data!AH26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AC4">
         <f>Data!AI26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AD4">
         <f>Data!AJ26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AE4">
         <f>Data!AK26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
       <c r="AF4">
         <f>Data!AL26</f>
-        <v>2.0708630477691714</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -30872,127 +32078,127 @@
       </c>
       <c r="B5">
         <f>Data!H27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <f>Data!I27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <f>Data!J27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <f>Data!K27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <f>Data!L27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <f>Data!M27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <f>Data!N27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <f>Data!O27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <f>Data!P27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <f>Data!Q27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <f>Data!R27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <f>Data!S27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="N5">
         <f>Data!T27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <f>Data!U27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="P5">
         <f>Data!V27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="Q5">
         <f>Data!W27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="R5">
         <f>Data!X27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="S5">
         <f>Data!Y27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="T5">
         <f>Data!Z27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="U5">
         <f>Data!AA27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="V5">
         <f>Data!AB27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="W5">
         <f>Data!AC27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="X5">
         <f>Data!AD27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="Y5">
         <f>Data!AE27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="Z5">
         <f>Data!AF27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AA5">
         <f>Data!AG27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AB5">
         <f>Data!AH27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AC5">
         <f>Data!AI27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AD5">
         <f>Data!AJ27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AE5">
         <f>Data!AK27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
       <c r="AF5">
         <f>Data!AL27</f>
-        <v>1.1886920057569821</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -31001,127 +32207,127 @@
       </c>
       <c r="B6">
         <f>Data!H28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="C6">
         <f>Data!I28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="D6">
         <f>Data!J28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="E6">
         <f>Data!K28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="F6">
         <f>Data!L28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="G6">
         <f>Data!M28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H6">
         <f>Data!N28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I6">
         <f>Data!O28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="J6">
         <f>Data!P28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K6">
         <f>Data!Q28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="L6">
         <f>Data!R28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="M6">
         <f>Data!S28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="N6">
         <f>Data!T28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="O6">
         <f>Data!U28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="P6">
         <f>Data!V28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Q6">
         <f>Data!W28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="R6">
         <f>Data!X28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="S6">
         <f>Data!Y28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="T6">
         <f>Data!Z28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="U6">
         <f>Data!AA28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="V6">
         <f>Data!AB28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="W6">
         <f>Data!AC28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="X6">
         <f>Data!AD28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Y6">
         <f>Data!AE28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="Z6">
         <f>Data!AF28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AA6">
         <f>Data!AG28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AB6">
         <f>Data!AH28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AC6">
         <f>Data!AI28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AD6">
         <f>Data!AJ28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AE6">
         <f>Data!AK28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AF6">
         <f>Data!AL28</f>
-        <v>4.0868310546055435E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:32">
@@ -31130,127 +32336,127 @@
       </c>
       <c r="B7">
         <f>Data!H29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="C7">
         <f>Data!I29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="D7">
         <f>Data!J29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="E7">
         <f>Data!K29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="F7">
         <f>Data!L29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="G7">
         <f>Data!M29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="H7">
         <f>Data!N29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="I7">
         <f>Data!O29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="J7">
         <f>Data!P29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="K7">
         <f>Data!Q29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="L7">
         <f>Data!R29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="M7">
         <f>Data!S29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="N7">
         <f>Data!T29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="O7">
         <f>Data!U29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="P7">
         <f>Data!V29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="Q7">
         <f>Data!W29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="R7">
         <f>Data!X29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="S7">
         <f>Data!Y29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="T7">
         <f>Data!Z29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="U7">
         <f>Data!AA29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="V7">
         <f>Data!AB29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="W7">
         <f>Data!AC29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="X7">
         <f>Data!AD29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="Y7">
         <f>Data!AE29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="Z7">
         <f>Data!AF29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AA7">
         <f>Data!AG29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AB7">
         <f>Data!AH29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AC7">
         <f>Data!AI29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AD7">
         <f>Data!AJ29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AE7">
         <f>Data!AK29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
       <c r="AF7">
         <f>Data!AL29</f>
-        <v>0.11252178195802712</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8" spans="1:32">
@@ -31259,127 +32465,127 @@
       </c>
       <c r="B8">
         <f>Data!H30</f>
-        <v>6.6083849891288092E-4</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="C8">
         <f>Data!I30</f>
-        <v>6.8292800627355835E-4</v>
+        <v>7.1188467263558208E-4</v>
       </c>
       <c r="D8">
         <f>Data!J30</f>
-        <v>6.9050288495521941E-4</v>
+        <v>7.139270677020466E-4</v>
       </c>
       <c r="E8">
         <f>Data!K30</f>
-        <v>7.0060519886219654E-4</v>
+        <v>7.163164850948787E-4</v>
       </c>
       <c r="F8">
         <f>Data!L30</f>
-        <v>7.140230367275464E-4</v>
+        <v>7.1911041371000887E-4</v>
       </c>
       <c r="G8">
         <f>Data!M30</f>
-        <v>7.3174765874089315E-4</v>
+        <v>7.223753210080882E-4</v>
       </c>
       <c r="H8">
         <f>Data!N30</f>
-        <v>7.549935976041178E-4</v>
+        <v>7.2618785347697127E-4</v>
       </c>
       <c r="I8">
         <f>Data!O30</f>
-        <v>7.851947971497683E-4</v>
+        <v>7.306361214447901E-4</v>
       </c>
       <c r="J8">
         <f>Data!P30</f>
-        <v>8.2395545201406335E-4</v>
+        <v>7.358210424289796E-4</v>
       </c>
       <c r="K8">
         <f>Data!Q30</f>
-        <v>8.7292821195079028E-4</v>
+        <v>7.4185770101618375E-4</v>
       </c>
       <c r="L8">
         <f>Data!R30</f>
-        <v>9.3359342692151347E-4</v>
+        <v>7.4887666175831567E-4</v>
       </c>
       <c r="M8">
         <f>Data!S30</f>
-        <v>1.0069304530164447E-3</v>
+        <v>7.5702514382313302E-4</v>
       </c>
       <c r="N8">
         <f>Data!T30</f>
-        <v>1.0930145779908538E-3</v>
+        <v>7.6646793149167617E-4</v>
       </c>
       <c r="O8">
         <f>Data!U30</f>
-        <v>1.1906382038504885E-3</v>
+        <v>7.7738785297517719E-4</v>
       </c>
       <c r="P8">
         <f>Data!V30</f>
-        <v>1.2971140499908186E-3</v>
+        <v>7.8998561243814067E-4</v>
       </c>
       <c r="Q8">
         <f>Data!W30</f>
-        <v>1.4084173527857645E-3</v>
+        <v>8.0447870933516956E-4</v>
       </c>
       <c r="R8">
         <f>Data!X30</f>
-        <v>1.5197206555807102E-3</v>
+        <v>8.2109913059272201E-4</v>
       </c>
       <c r="S8">
         <f>Data!Y30</f>
-        <v>1.62619650172104E-3</v>
+        <v>8.4008946375237572E-4</v>
       </c>
       <c r="T8">
         <f>Data!Z30</f>
-        <v>1.7238201275806748E-3</v>
+        <v>8.6169706625861841E-4</v>
       </c>
       <c r="U8">
         <f>Data!AA30</f>
-        <v>1.8099042525550838E-3</v>
+        <v>8.8616595553801553E-4</v>
       </c>
       <c r="V8">
         <f>Data!AB30</f>
-        <v>1.8832412786500153E-3</v>
+        <v>9.1372617792494671E-4</v>
       </c>
       <c r="W8">
         <f>Data!AC30</f>
-        <v>1.9439064936207385E-3</v>
+        <v>9.4458059403339993E-4</v>
       </c>
       <c r="X8">
         <f>Data!AD30</f>
-        <v>1.9928792535574653E-3</v>
+        <v>9.7888930090860526E-4</v>
       </c>
       <c r="Y8">
         <f>Data!AE30</f>
-        <v>2.0316399084217606E-3</v>
+        <v>1.016752300285689E-3</v>
       </c>
       <c r="Z8">
         <f>Data!AF30</f>
-        <v>2.0618411079674111E-3</v>
+        <v>1.0581914956455567E-3</v>
       </c>
       <c r="AA8">
         <f>Data!AG30</f>
-        <v>2.0850870468306359E-3</v>
+        <v>1.1031336014453823E-3</v>
       </c>
       <c r="AB8">
         <f>Data!AH30</f>
-        <v>2.1028116688439824E-3</v>
+        <v>1.1513959794455754E-3</v>
       </c>
       <c r="AC8">
         <f>Data!AI30</f>
-        <v>2.1162295067093319E-3</v>
+        <v>1.2026776517192247E-3</v>
       </c>
       <c r="AD8">
         <f>Data!AJ30</f>
-        <v>2.1263318206163092E-3</v>
+        <v>1.25655764432318E-3</v>
       </c>
       <c r="AE8">
         <f>Data!AK30</f>
-        <v>2.1339066992979703E-3</v>
+        <v>1.3125022931047108E-3</v>
       </c>
       <c r="AF8">
         <f>Data!AL30</f>
-        <v>2.1395689946999558E-3</v>
+        <v>1.3698821828272024E-3</v>
       </c>
     </row>
   </sheetData>
@@ -31389,15 +32595,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -31541,21 +32738,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39ACE987-BC54-40D9-B8CF-5CB9726AD5E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F78F0F71-EE7E-4036-B654-BDDC7E3F7269}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31573,7 +32771,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78A831F0-D33B-4743-B389-F44D66A91D94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -31587,4 +32785,12 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39ACE987-BC54-40D9-B8CF-5CB9726AD5E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\South Korea\Models\eps-southkorea\InputData\trans\TTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4853292D-52BA-492B-99CB-EF3D764FCABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B86671-EEDB-464B-AA2C-AD1665841050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="404">
   <si>
     <t>Source:</t>
   </si>
@@ -1322,6 +1322,9 @@
   </si>
   <si>
     <t>outputs shareweights to replace "recalculated_shareweights" tab in this file as needed</t>
+  </si>
+  <si>
+    <t>Dedicated sigmoidal curve for LDVs freight BEV only (added for ICCT calibration 2026-08-19)</t>
   </si>
 </sst>
 </file>
@@ -3563,97 +3566,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>0.18467095381410897</c:v>
+                  <c:v>0.13959946601801937</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.20679585237428799</c:v>
+                  <c:v>0.14165766710981109</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2323202254775863</c:v>
+                  <c:v>0.14407055156915388</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.26168474967806649</c:v>
+                  <c:v>0.14689874732237662</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29535945465707103</c:v>
+                  <c:v>0.15021306078032395</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.33383584804654387</c:v>
+                  <c:v>0.15409611633610562</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.37761510179865232</c:v>
+                  <c:v>0.15864423385246806</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.42719162064128996</c:v>
+                  <c:v>0.1639695686619507</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.48303150241407805</c:v>
+                  <c:v>0.17020253698757215</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.54554576385492282</c:v>
+                  <c:v>0.17749454585047661</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.61505877825632926</c:v>
+                  <c:v>0.18602103949908258</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.69177315955181817</c:v>
+                  <c:v>0.19598486290874539</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.77573328647560325</c:v>
+                  <c:v>0.20761992534555765</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.86679067488305006</c:v>
+                  <c:v>0.22119512135074879</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.96457528067354337</c:v>
+                  <c:v>0.23701843036473241</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.0684772912113583</c:v>
+                  <c:v>0.25544106679998774</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.1776437694307156</c:v>
+                  <c:v>0.27686148672893945</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.2909934561611893</c:v>
+                  <c:v>0.30172897267514276</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.4072510905610811</c:v>
+                  <c:v>0.33054641226359727</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.5250000000000001</c:v>
+                  <c:v>0.36387175947115635</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.6427489094389189</c:v>
+                  <c:v>0.40231752199562953</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.7590065438388109</c:v>
+                  <c:v>0.4465474632947527</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.8723562305692845</c:v>
+                  <c:v>0.49726955960109476</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.981522708788642</c:v>
+                  <c:v>0.55522413803729254</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.0854247193264568</c:v>
+                  <c:v>0.62116608248546845</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2.18320932511695</c:v>
+                  <c:v>0.69584008378220608</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2.2742667135243968</c:v>
+                  <c:v>0.77994819587346254</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2.3582268404481819</c:v>
+                  <c:v>0.87410950749592009</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2.4349412217436712</c:v>
+                  <c:v>0.97881260179802487</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.5044542361450772</c:v>
+                  <c:v>1.094362663441542</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2.5669684975859219</c:v>
+                  <c:v>1.2208265373307441</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6529,9 +6532,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B89"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="56.140625" customWidth="1"/>
+    <col min="2" max="2" width="56.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6900,12 +6903,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="45">
+    <row r="1" spans="1:32" ht="29">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -7040,127 +7043,127 @@
       </c>
       <c r="B2">
         <f>Data!H17</f>
-        <v>0.18467095381410897</v>
+        <v>0.13959946601801937</v>
       </c>
       <c r="C2">
         <f>Data!I17</f>
-        <v>0.20679585237428799</v>
+        <v>0.14165766710981109</v>
       </c>
       <c r="D2">
         <f>Data!J17</f>
-        <v>0.2323202254775863</v>
+        <v>0.14407055156915388</v>
       </c>
       <c r="E2">
         <f>Data!K17</f>
-        <v>0.26168474967806649</v>
+        <v>0.14689874732237662</v>
       </c>
       <c r="F2">
         <f>Data!L17</f>
-        <v>0.29535945465707103</v>
+        <v>0.15021306078032395</v>
       </c>
       <c r="G2">
         <f>Data!M17</f>
-        <v>0.33383584804654387</v>
+        <v>0.15409611633610562</v>
       </c>
       <c r="H2">
         <f>Data!N17</f>
-        <v>0.37761510179865232</v>
+        <v>0.15864423385246806</v>
       </c>
       <c r="I2">
         <f>Data!O17</f>
-        <v>0.42719162064128996</v>
+        <v>0.1639695686619507</v>
       </c>
       <c r="J2">
         <f>Data!P17</f>
-        <v>0.48303150241407805</v>
+        <v>0.17020253698757215</v>
       </c>
       <c r="K2">
         <f>Data!Q17</f>
-        <v>0.54554576385492282</v>
+        <v>0.17749454585047661</v>
       </c>
       <c r="L2">
         <f>Data!R17</f>
-        <v>0.61505877825632926</v>
+        <v>0.18602103949908258</v>
       </c>
       <c r="M2">
         <f>Data!S17</f>
-        <v>0.69177315955181817</v>
+        <v>0.19598486290874539</v>
       </c>
       <c r="N2">
         <f>Data!T17</f>
-        <v>0.77573328647560325</v>
+        <v>0.20761992534555765</v>
       </c>
       <c r="O2">
         <f>Data!U17</f>
-        <v>0.86679067488305006</v>
+        <v>0.22119512135074879</v>
       </c>
       <c r="P2">
         <f>Data!V17</f>
-        <v>0.96457528067354337</v>
+        <v>0.23701843036473241</v>
       </c>
       <c r="Q2">
         <f>Data!W17</f>
-        <v>1.0684772912113583</v>
+        <v>0.25544106679998774</v>
       </c>
       <c r="R2">
         <f>Data!X17</f>
-        <v>1.1776437694307156</v>
+        <v>0.27686148672893945</v>
       </c>
       <c r="S2">
         <f>Data!Y17</f>
-        <v>1.2909934561611893</v>
+        <v>0.30172897267514276</v>
       </c>
       <c r="T2">
         <f>Data!Z17</f>
-        <v>1.4072510905610811</v>
+        <v>0.33054641226359727</v>
       </c>
       <c r="U2">
         <f>Data!AA17</f>
-        <v>1.5250000000000001</v>
+        <v>0.36387175947115635</v>
       </c>
       <c r="V2">
         <f>Data!AB17</f>
-        <v>1.6427489094389189</v>
+        <v>0.40231752199562953</v>
       </c>
       <c r="W2">
         <f>Data!AC17</f>
-        <v>1.7590065438388109</v>
+        <v>0.4465474632947527</v>
       </c>
       <c r="X2">
         <f>Data!AD17</f>
-        <v>1.8723562305692845</v>
+        <v>0.49726955960109476</v>
       </c>
       <c r="Y2">
         <f>Data!AE17</f>
-        <v>1.981522708788642</v>
+        <v>0.55522413803729254</v>
       </c>
       <c r="Z2">
         <f>Data!AF17</f>
-        <v>2.0854247193264568</v>
+        <v>0.62116608248546845</v>
       </c>
       <c r="AA2">
         <f>Data!AG17</f>
-        <v>2.18320932511695</v>
+        <v>0.69584008378220608</v>
       </c>
       <c r="AB2">
         <f>Data!AH17</f>
-        <v>2.2742667135243968</v>
+        <v>0.77994819587346254</v>
       </c>
       <c r="AC2">
         <f>Data!AI17</f>
-        <v>2.3582268404481819</v>
+        <v>0.87410950749592009</v>
       </c>
       <c r="AD2">
         <f>Data!AJ17</f>
-        <v>2.4349412217436712</v>
+        <v>0.97881260179802487</v>
       </c>
       <c r="AE2">
         <f>Data!AK17</f>
-        <v>2.5044542361450772</v>
+        <v>1.094362663441542</v>
       </c>
       <c r="AF2">
         <f>Data!AL17</f>
-        <v>2.5669684975859219</v>
+        <v>1.2208265373307441</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -7949,12 +7952,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="45">
+    <row r="1" spans="1:32" ht="29">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -8998,12 +9001,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="45">
+    <row r="1" spans="1:32" ht="29">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -10047,12 +10050,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="45">
+    <row r="1" spans="1:32" ht="29">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -11096,12 +11099,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="45">
+    <row r="1" spans="1:32" ht="29">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -12145,12 +12148,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="45">
+    <row r="1" spans="1:32" ht="29">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -13194,12 +13197,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="45">
+    <row r="1" spans="1:32" ht="29">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -14243,12 +14246,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="45">
+    <row r="1" spans="1:32" ht="29">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -15292,12 +15295,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="45">
+    <row r="1" spans="1:32" ht="29">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -16341,12 +16344,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="45">
+    <row r="1" spans="1:32" ht="29">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -17387,18 +17390,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="6" max="8" width="23.140625" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="24.453125" customWidth="1"/>
+    <col min="3" max="3" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="18.1796875" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" customWidth="1"/>
+    <col min="6" max="8" width="23.1796875" customWidth="1"/>
+    <col min="10" max="10" width="14.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30">
+    <row r="1" spans="1:10" ht="29">
       <c r="A1" s="23" t="s">
         <v>81</v>
       </c>
@@ -17604,12 +17607,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="45">
+    <row r="1" spans="1:32" ht="29">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -18650,19 +18653,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="6" max="8" width="23.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="24.453125" customWidth="1"/>
+    <col min="3" max="3" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="18.1796875" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" customWidth="1"/>
+    <col min="6" max="8" width="23.1796875" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30">
+    <row r="1" spans="1:10" ht="29">
       <c r="A1" s="23" t="s">
         <v>81</v>
       </c>
@@ -18856,7 +18859,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A97B2F-5092-4096-B175-EDA36800D0EC}">
   <dimension ref="A2:X284"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="1:24">
       <c r="A2" s="33" t="s">
@@ -20252,12 +20255,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0949E7F5-D122-4C59-A6D3-7F5B0E744BE5}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="76" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21097,9 +21100,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C98A0B0-4AA3-4C7F-A6AE-244E743CFDDD}">
   <dimension ref="B2:AF35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="74.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:32">
@@ -22600,11 +22603,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD9F80A-1DD4-4EFC-BD0A-42EC00E11F1F}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -23446,15 +23449,15 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AL93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.1796875" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" customWidth="1"/>
     <col min="6" max="6" width="18" style="6" customWidth="1"/>
-    <col min="8" max="9" width="9.140625" customWidth="1"/>
+    <col min="8" max="9" width="9.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38">
@@ -23475,6 +23478,9 @@
       <c r="P1" s="16"/>
       <c r="Q1" s="16"/>
       <c r="R1" s="16"/>
+      <c r="T1" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="2" spans="1:38">
       <c r="A2" t="s">
@@ -23492,6 +23498,12 @@
       <c r="O2" s="17">
         <v>1</v>
       </c>
+      <c r="T2" t="s">
+        <v>61</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:38">
       <c r="A3" t="s">
@@ -23509,8 +23521,14 @@
       <c r="O3" s="17">
         <v>-0.3</v>
       </c>
-    </row>
-    <row r="4" spans="1:38" ht="15.75" thickBot="1">
+      <c r="T3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U3">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" ht="15" thickBot="1">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -23525,6 +23543,12 @@
       </c>
       <c r="O4" s="18">
         <v>-11</v>
+      </c>
+      <c r="T4" t="s">
+        <v>63</v>
+      </c>
+      <c r="U4">
+        <v>-38</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -23532,7 +23556,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="30">
+    <row r="6" spans="1:38" ht="29">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -23560,7 +23584,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:38" ht="45">
+    <row r="8" spans="1:38" ht="43.5">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -24567,7 +24591,7 @@
         <v>0.15947005332295699</v>
       </c>
     </row>
-    <row r="16" spans="1:38" ht="15.75" thickBot="1">
+    <row r="16" spans="1:38" ht="15" thickBot="1">
       <c r="A16" s="21"/>
       <c r="B16" s="21"/>
       <c r="C16" s="21" t="s">
@@ -24721,138 +24745,138 @@
         <v>1</v>
       </c>
       <c r="D17" s="20">
-        <v>0.05</v>
+        <v>0.12770000000000001</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4.5711000000000004</v>
       </c>
       <c r="F17" s="6" t="str">
         <f>IF(D17=E17,"n/a",IF(OR(C17="battery electric vehicle",C17="natural gas vehicle",C17="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>s-curve</v>
       </c>
       <c r="H17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:H$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,H$9))</f>
-        <v>0.18467095381410897</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:H$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,H$9))</f>
+        <v>0.13959946601801937</v>
       </c>
       <c r="I17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,I$9))</f>
-        <v>0.20679585237428799</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:I$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,I$9))</f>
+        <v>0.14165766710981109</v>
       </c>
       <c r="J17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,J$9))</f>
-        <v>0.2323202254775863</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:J$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,J$9))</f>
+        <v>0.14407055156915388</v>
       </c>
       <c r="K17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,K$9))</f>
-        <v>0.26168474967806649</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:K$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,K$9))</f>
+        <v>0.14689874732237662</v>
       </c>
       <c r="L17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,L$9))</f>
-        <v>0.29535945465707103</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:L$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,L$9))</f>
+        <v>0.15021306078032395</v>
       </c>
       <c r="M17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,M$9))</f>
-        <v>0.33383584804654387</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:M$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,M$9))</f>
+        <v>0.15409611633610562</v>
       </c>
       <c r="N17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,N$9))</f>
-        <v>0.37761510179865232</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:N$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,N$9))</f>
+        <v>0.15864423385246806</v>
       </c>
       <c r="O17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,O$9))</f>
-        <v>0.42719162064128996</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:O$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,O$9))</f>
+        <v>0.1639695686619507</v>
       </c>
       <c r="P17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,P$9))</f>
-        <v>0.48303150241407805</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:P$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,P$9))</f>
+        <v>0.17020253698757215</v>
       </c>
       <c r="Q17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,Q$9))</f>
-        <v>0.54554576385492282</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:Q$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,Q$9))</f>
+        <v>0.17749454585047661</v>
       </c>
       <c r="R17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,R$9))</f>
-        <v>0.61505877825632926</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:R$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,R$9))</f>
+        <v>0.18602103949908258</v>
       </c>
       <c r="S17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,S$9))</f>
-        <v>0.69177315955181817</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:S$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,S$9))</f>
+        <v>0.19598486290874539</v>
       </c>
       <c r="T17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,T$9))</f>
-        <v>0.77573328647560325</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:T$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,T$9))</f>
+        <v>0.20761992534555765</v>
       </c>
       <c r="U17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,U$9))</f>
-        <v>0.86679067488305006</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:U$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,U$9))</f>
+        <v>0.22119512135074879</v>
       </c>
       <c r="V17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,V$9))</f>
-        <v>0.96457528067354337</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:V$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,V$9))</f>
+        <v>0.23701843036473241</v>
       </c>
       <c r="W17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,W$9))</f>
-        <v>1.0684772912113583</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:W$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,W$9))</f>
+        <v>0.25544106679998774</v>
       </c>
       <c r="X17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,X$9))</f>
-        <v>1.1776437694307156</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:X$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,X$9))</f>
+        <v>0.27686148672893945</v>
       </c>
       <c r="Y17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,Y$9))</f>
-        <v>1.2909934561611893</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:Y$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,Y$9))</f>
+        <v>0.30172897267514276</v>
       </c>
       <c r="Z17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,Z$9))</f>
-        <v>1.4072510905610811</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:Z$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,Z$9))</f>
+        <v>0.33054641226359727</v>
       </c>
       <c r="AA17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AA$9))</f>
-        <v>1.5250000000000001</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:AA$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,AA$9))</f>
+        <v>0.36387175947115635</v>
       </c>
       <c r="AB17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AB$9))</f>
-        <v>1.6427489094389189</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:AB$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,AB$9))</f>
+        <v>0.40231752199562953</v>
       </c>
       <c r="AC17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AC$9))</f>
-        <v>1.7590065438388109</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:AC$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,AC$9))</f>
+        <v>0.4465474632947527</v>
       </c>
       <c r="AD17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AD$9))</f>
-        <v>1.8723562305692845</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:AD$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,AD$9))</f>
+        <v>0.49726955960109476</v>
       </c>
       <c r="AE17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AE$9))</f>
-        <v>1.981522708788642</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:AE$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,AE$9))</f>
+        <v>0.55522413803729254</v>
       </c>
       <c r="AF17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AF$9))</f>
-        <v>2.0854247193264568</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:AF$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,AF$9))</f>
+        <v>0.62116608248546845</v>
       </c>
       <c r="AG17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AG$9))</f>
-        <v>2.18320932511695</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:AG$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,AG$9))</f>
+        <v>0.69584008378220608</v>
       </c>
       <c r="AH17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AH$9))</f>
-        <v>2.2742667135243968</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:AH$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,AH$9))</f>
+        <v>0.77994819587346254</v>
       </c>
       <c r="AI17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AI$9))</f>
-        <v>2.3582268404481819</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:AI$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,AI$9))</f>
+        <v>0.87410950749592009</v>
       </c>
       <c r="AJ17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AJ$9))</f>
-        <v>2.4349412217436712</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:AJ$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,AJ$9))</f>
+        <v>0.97881260179802487</v>
       </c>
       <c r="AK17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AK$9))</f>
-        <v>2.5044542361450772</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:AK$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,AK$9))</f>
+        <v>1.094362663441542</v>
       </c>
       <c r="AL17">
-        <f>IF($F17="s-curve",$D17+($E17-$D17)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D17:$E17,$D$9:$E$9,AL$9))</f>
-        <v>2.5669684975859219</v>
+        <f>IF($F17="s-curve",$D17+($E17-$D17)*$U$2/(1+EXP($U$3*(COUNT($H$9:AL$9)+$U$4))),TREND($D17:$E17,$D$9:$E$9,AL$9))</f>
+        <v>1.2208265373307441</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -25556,7 +25580,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="23" spans="1:38" ht="15.75" thickBot="1">
+    <row r="23" spans="1:38" ht="15" thickBot="1">
       <c r="A23" s="21"/>
       <c r="B23" s="21"/>
       <c r="C23" s="21" t="s">
@@ -26544,7 +26568,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="30" spans="1:38" ht="15.75" thickBot="1">
+    <row r="30" spans="1:38" ht="15" thickBot="1">
       <c r="A30" s="21"/>
       <c r="B30" s="21"/>
       <c r="C30" s="21" t="s">
@@ -27535,7 +27559,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="37" spans="1:38" ht="15.75" thickBot="1">
+    <row r="37" spans="1:38" ht="15" thickBot="1">
       <c r="A37" s="21"/>
       <c r="B37" s="21"/>
       <c r="C37" s="21" t="s">
@@ -28517,7 +28541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" ht="15.75" thickBot="1">
+    <row r="44" spans="1:38" ht="15" thickBot="1">
       <c r="A44" s="21"/>
       <c r="B44" s="21"/>
       <c r="C44" s="21" t="s">
@@ -29498,7 +29522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:38" ht="15.75" thickBot="1">
+    <row r="51" spans="1:38" ht="15" thickBot="1">
       <c r="A51" s="21"/>
       <c r="B51" s="21"/>
       <c r="C51" s="21" t="s">
@@ -30489,7 +30513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:38" ht="15.75" thickBot="1">
+    <row r="58" spans="1:38" ht="15" thickBot="1">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21" t="s">
@@ -31482,7 +31506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:38" ht="15.75" thickBot="1">
+    <row r="65" spans="1:38" ht="15" thickBot="1">
       <c r="A65" s="21"/>
       <c r="B65" s="21"/>
       <c r="C65" s="21" t="s">
@@ -32465,7 +32489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:38" ht="15.75" thickBot="1">
+    <row r="72" spans="1:38" ht="15" thickBot="1">
       <c r="A72" s="21"/>
       <c r="B72" s="21"/>
       <c r="C72" s="21" t="s">
@@ -33458,7 +33482,7 @@
         <v>1.6666577778251849E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:38" ht="15.75" thickBot="1">
+    <row r="79" spans="1:38" ht="15" thickBot="1">
       <c r="A79" s="21"/>
       <c r="B79" s="21"/>
       <c r="C79" s="21" t="s">
@@ -34445,7 +34469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:38" ht="15.75" thickBot="1">
+    <row r="86" spans="1:38" ht="15" thickBot="1">
       <c r="A86" s="21"/>
       <c r="B86" s="21"/>
       <c r="C86" s="21" t="s">
@@ -35439,7 +35463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:38" ht="15.75" thickBot="1">
+    <row r="93" spans="1:38" ht="15" thickBot="1">
       <c r="A93" s="21"/>
       <c r="B93" s="21"/>
       <c r="C93" s="21" t="s">
@@ -35595,12 +35619,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="45">
+    <row r="1" spans="1:32" ht="29">
       <c r="A1" s="23" t="s">
         <v>80</v>
       </c>
@@ -36639,12 +36663,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -36792,15 +36813,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39ACE987-BC54-40D9-B8CF-5CB9726AD5E1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78A831F0-D33B-4743-B389-F44D66A91D94}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -36824,17 +36856,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78A831F0-D33B-4743-B389-F44D66A91D94}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39ACE987-BC54-40D9-B8CF-5CB9726AD5E1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>